--- a/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
+++ b/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\dashboard_pacotes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{663E5105-0416-4D48-8CD5-718B9BEDF228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CA0E44-56A7-445A-BB8A-61FEE0E23381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ORIGINAL" sheetId="1" r:id="rId1"/>
@@ -1501,10 +1501,6 @@
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
-      <c r="E9" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F9" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1526,10 +1522,6 @@
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
-      <c r="E10" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F10" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1551,10 +1543,6 @@
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
-      <c r="E11" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F11" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1576,10 +1564,6 @@
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
-      <c r="E12" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F12" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1601,10 +1585,6 @@
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
-      <c r="E13" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F13" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1626,10 +1606,6 @@
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
-      <c r="E14" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F14" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1651,10 +1627,6 @@
       <c r="B15" s="28"/>
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
-      <c r="E15" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F15" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1676,10 +1648,6 @@
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
-      <c r="E16" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F16" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1701,10 +1669,6 @@
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
-      <c r="E17" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F17" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1726,10 +1690,6 @@
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
-      <c r="E18" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F18" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1751,10 +1711,6 @@
       <c r="B19" s="28"/>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
-      <c r="E19" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F19" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1776,10 +1732,6 @@
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
       <c r="D20" s="28"/>
-      <c r="E20" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F20" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1801,10 +1753,6 @@
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
-      <c r="E21" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F21" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1826,10 +1774,6 @@
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
       <c r="D22" s="28"/>
-      <c r="E22" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F22" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1851,10 +1795,6 @@
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
-      <c r="E23" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F23" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1876,10 +1816,6 @@
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
-      <c r="E24" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F24" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1901,10 +1837,6 @@
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
-      <c r="E25" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F25" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1926,10 +1858,6 @@
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
       <c r="D26" s="28"/>
-      <c r="E26" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F26" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1951,10 +1879,6 @@
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
-      <c r="E27" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F27" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -1976,10 +1900,6 @@
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
       <c r="D28" s="28"/>
-      <c r="E28" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F28" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2001,10 +1921,6 @@
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
-      <c r="E29" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F29" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2026,10 +1942,6 @@
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
-      <c r="E30" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F30" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2051,10 +1963,6 @@
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
-      <c r="E31" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F31" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2076,10 +1984,6 @@
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
       <c r="D32" s="28"/>
-      <c r="E32" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F32" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2101,10 +2005,6 @@
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
-      <c r="E33" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F33" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2126,10 +2026,6 @@
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
-      <c r="E34" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F34" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2151,10 +2047,6 @@
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
-      <c r="E35" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F35" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2176,10 +2068,6 @@
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
-      <c r="E36" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F36" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2201,10 +2089,6 @@
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
-      <c r="E37" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F37" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2226,10 +2110,6 @@
       <c r="B38" s="28"/>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
-      <c r="E38" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F38" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2251,10 +2131,6 @@
       <c r="B39" s="28"/>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
-      <c r="E39" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F39" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2276,10 +2152,6 @@
       <c r="B40" s="28"/>
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
-      <c r="E40" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F40" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2301,10 +2173,6 @@
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
       <c r="D41" s="28"/>
-      <c r="E41" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F41" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2326,10 +2194,6 @@
       <c r="B42" s="28"/>
       <c r="C42" s="28"/>
       <c r="D42" s="28"/>
-      <c r="E42" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F42" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2351,10 +2215,6 @@
       <c r="B43" s="28"/>
       <c r="C43" s="28"/>
       <c r="D43" s="28"/>
-      <c r="E43" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F43" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2376,10 +2236,6 @@
       <c r="B44" s="28"/>
       <c r="C44" s="28"/>
       <c r="D44" s="28"/>
-      <c r="E44" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F44" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2401,10 +2257,6 @@
       <c r="B45" s="28"/>
       <c r="C45" s="28"/>
       <c r="D45" s="28"/>
-      <c r="E45" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F45" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2426,10 +2278,6 @@
       <c r="B46" s="28"/>
       <c r="C46" s="28"/>
       <c r="D46" s="28"/>
-      <c r="E46" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F46" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2451,10 +2299,6 @@
       <c r="B47" s="28"/>
       <c r="C47" s="28"/>
       <c r="D47" s="28"/>
-      <c r="E47" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F47" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2476,10 +2320,6 @@
       <c r="B48" s="28"/>
       <c r="C48" s="28"/>
       <c r="D48" s="28"/>
-      <c r="E48" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F48" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2501,10 +2341,6 @@
       <c r="B49" s="28"/>
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
-      <c r="E49" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F49" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2526,10 +2362,6 @@
       <c r="B50" s="28"/>
       <c r="C50" s="28"/>
       <c r="D50" s="28"/>
-      <c r="E50" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F50" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2551,10 +2383,6 @@
       <c r="B51" s="28"/>
       <c r="C51" s="28"/>
       <c r="D51" s="28"/>
-      <c r="E51" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F51" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2576,10 +2404,6 @@
       <c r="B52" s="28"/>
       <c r="C52" s="28"/>
       <c r="D52" s="28"/>
-      <c r="E52" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F52" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2601,10 +2425,6 @@
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
       <c r="D53" s="28"/>
-      <c r="E53" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F53" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2626,10 +2446,6 @@
       <c r="B54" s="28"/>
       <c r="C54" s="28"/>
       <c r="D54" s="28"/>
-      <c r="E54" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F54" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2651,10 +2467,6 @@
       <c r="B55" s="28"/>
       <c r="C55" s="28"/>
       <c r="D55" s="28"/>
-      <c r="E55" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F55" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2676,10 +2488,6 @@
       <c r="B56" s="28"/>
       <c r="C56" s="28"/>
       <c r="D56" s="28"/>
-      <c r="E56" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F56" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2701,10 +2509,6 @@
       <c r="B57" s="28"/>
       <c r="C57" s="28"/>
       <c r="D57" s="28"/>
-      <c r="E57" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F57" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2726,10 +2530,6 @@
       <c r="B58" s="28"/>
       <c r="C58" s="28"/>
       <c r="D58" s="28"/>
-      <c r="E58" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F58" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2751,10 +2551,6 @@
       <c r="B59" s="28"/>
       <c r="C59" s="28"/>
       <c r="D59" s="28"/>
-      <c r="E59" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F59" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2776,10 +2572,6 @@
       <c r="B60" s="28"/>
       <c r="C60" s="28"/>
       <c r="D60" s="28"/>
-      <c r="E60" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F60" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2801,10 +2593,6 @@
       <c r="B61" s="28"/>
       <c r="C61" s="28"/>
       <c r="D61" s="28"/>
-      <c r="E61" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F61" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2826,10 +2614,6 @@
       <c r="B62" s="28"/>
       <c r="C62" s="28"/>
       <c r="D62" s="28"/>
-      <c r="E62" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F62" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2851,10 +2635,6 @@
       <c r="B63" s="28"/>
       <c r="C63" s="28"/>
       <c r="D63" s="28"/>
-      <c r="E63" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F63" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2876,10 +2656,6 @@
       <c r="B64" s="28"/>
       <c r="C64" s="28"/>
       <c r="D64" s="28"/>
-      <c r="E64" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F64" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2901,10 +2677,6 @@
       <c r="B65" s="28"/>
       <c r="C65" s="28"/>
       <c r="D65" s="28"/>
-      <c r="E65" t="str">
-        <f t="shared" si="0"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F65" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -2926,24 +2698,20 @@
       <c r="B66" s="28"/>
       <c r="C66" s="28"/>
       <c r="D66" s="28"/>
-      <c r="E66" t="str">
-        <f t="shared" ref="E66:E129" si="5">IF(D66="","Em trânsito","Recebido")</f>
-        <v>Em trânsito</v>
-      </c>
       <c r="F66" s="29" t="str">
-        <f t="shared" ref="F66:F129" ca="1" si="6">IF(B66="","",IF(E66="Recebido",D66-B66,TODAY()-B66))</f>
+        <f t="shared" ref="F66:F129" ca="1" si="5">IF(B66="","",IF(E66="Recebido",D66-B66,TODAY()-B66))</f>
         <v/>
       </c>
       <c r="G66" s="29" t="str">
-        <f t="shared" ref="G66:G129" ca="1" si="7">IF(C66="","",IF(E66="Recebido",D66-C66,TODAY()-C66))</f>
+        <f t="shared" ref="G66:G129" ca="1" si="6">IF(C66="","",IF(E66="Recebido",D66-C66,TODAY()-C66))</f>
         <v/>
       </c>
       <c r="H66" s="29" t="str">
-        <f t="shared" ref="H66:H129" si="8">IF(OR(B66="",C66=""),"",C66-B66)</f>
+        <f t="shared" ref="H66:H129" si="7">IF(OR(B66="",C66=""),"",C66-B66)</f>
         <v/>
       </c>
       <c r="I66" s="29" t="str">
-        <f t="shared" ref="I66:I129" si="9">IF(OR(C66="",D66=""),"",D66-C66)</f>
+        <f t="shared" ref="I66:I129" si="8">IF(OR(C66="",D66=""),"",D66-C66)</f>
         <v/>
       </c>
     </row>
@@ -2951,24 +2719,20 @@
       <c r="B67" s="28"/>
       <c r="C67" s="28"/>
       <c r="D67" s="28"/>
-      <c r="E67" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F67" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G67" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G67" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H67" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I67" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I67" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2976,24 +2740,20 @@
       <c r="B68" s="28"/>
       <c r="C68" s="28"/>
       <c r="D68" s="28"/>
-      <c r="E68" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F68" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G68" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G68" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H68" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I68" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I68" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3001,24 +2761,20 @@
       <c r="B69" s="28"/>
       <c r="C69" s="28"/>
       <c r="D69" s="28"/>
-      <c r="E69" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F69" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G69" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G69" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H69" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I69" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I69" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3026,24 +2782,20 @@
       <c r="B70" s="28"/>
       <c r="C70" s="28"/>
       <c r="D70" s="28"/>
-      <c r="E70" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F70" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G70" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G70" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H70" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I70" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I70" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3051,24 +2803,20 @@
       <c r="B71" s="28"/>
       <c r="C71" s="28"/>
       <c r="D71" s="28"/>
-      <c r="E71" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F71" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G71" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G71" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H71" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I71" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I71" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3076,24 +2824,20 @@
       <c r="B72" s="28"/>
       <c r="C72" s="28"/>
       <c r="D72" s="28"/>
-      <c r="E72" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F72" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G72" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G72" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H72" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I72" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I72" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3101,24 +2845,20 @@
       <c r="B73" s="28"/>
       <c r="C73" s="28"/>
       <c r="D73" s="28"/>
-      <c r="E73" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F73" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G73" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G73" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H73" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I73" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I73" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3126,24 +2866,20 @@
       <c r="B74" s="28"/>
       <c r="C74" s="28"/>
       <c r="D74" s="28"/>
-      <c r="E74" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F74" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G74" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G74" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H74" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I74" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I74" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3151,24 +2887,20 @@
       <c r="B75" s="28"/>
       <c r="C75" s="28"/>
       <c r="D75" s="28"/>
-      <c r="E75" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F75" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G75" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G75" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H75" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I75" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I75" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3176,24 +2908,20 @@
       <c r="B76" s="28"/>
       <c r="C76" s="28"/>
       <c r="D76" s="28"/>
-      <c r="E76" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F76" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G76" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G76" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H76" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I76" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I76" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3201,24 +2929,20 @@
       <c r="B77" s="28"/>
       <c r="C77" s="28"/>
       <c r="D77" s="28"/>
-      <c r="E77" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F77" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G77" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G77" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H77" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I77" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I77" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3226,24 +2950,20 @@
       <c r="B78" s="28"/>
       <c r="C78" s="28"/>
       <c r="D78" s="28"/>
-      <c r="E78" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F78" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G78" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G78" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H78" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I78" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I78" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3251,24 +2971,20 @@
       <c r="B79" s="28"/>
       <c r="C79" s="28"/>
       <c r="D79" s="28"/>
-      <c r="E79" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F79" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G79" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G79" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H79" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I79" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I79" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3276,24 +2992,20 @@
       <c r="B80" s="28"/>
       <c r="C80" s="28"/>
       <c r="D80" s="28"/>
-      <c r="E80" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F80" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G80" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G80" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H80" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I80" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I80" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3301,24 +3013,20 @@
       <c r="B81" s="28"/>
       <c r="C81" s="28"/>
       <c r="D81" s="28"/>
-      <c r="E81" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F81" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G81" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G81" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H81" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I81" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I81" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3326,24 +3034,20 @@
       <c r="B82" s="28"/>
       <c r="C82" s="28"/>
       <c r="D82" s="28"/>
-      <c r="E82" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F82" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G82" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G82" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H82" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I82" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I82" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3351,24 +3055,20 @@
       <c r="B83" s="28"/>
       <c r="C83" s="28"/>
       <c r="D83" s="28"/>
-      <c r="E83" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F83" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G83" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G83" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H83" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I83" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I83" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3376,24 +3076,20 @@
       <c r="B84" s="28"/>
       <c r="C84" s="28"/>
       <c r="D84" s="28"/>
-      <c r="E84" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F84" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G84" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G84" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H84" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I84" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I84" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3401,24 +3097,20 @@
       <c r="B85" s="28"/>
       <c r="C85" s="28"/>
       <c r="D85" s="28"/>
-      <c r="E85" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F85" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G85" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G85" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H85" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I85" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I85" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3426,24 +3118,20 @@
       <c r="B86" s="28"/>
       <c r="C86" s="28"/>
       <c r="D86" s="28"/>
-      <c r="E86" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F86" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G86" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G86" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H86" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I86" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I86" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3451,24 +3139,20 @@
       <c r="B87" s="28"/>
       <c r="C87" s="28"/>
       <c r="D87" s="28"/>
-      <c r="E87" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F87" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G87" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G87" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H87" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I87" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I87" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3476,24 +3160,20 @@
       <c r="B88" s="28"/>
       <c r="C88" s="28"/>
       <c r="D88" s="28"/>
-      <c r="E88" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F88" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G88" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G88" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H88" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I88" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I88" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3501,24 +3181,20 @@
       <c r="B89" s="28"/>
       <c r="C89" s="28"/>
       <c r="D89" s="28"/>
-      <c r="E89" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F89" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G89" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G89" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H89" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I89" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I89" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3526,24 +3202,20 @@
       <c r="B90" s="28"/>
       <c r="C90" s="28"/>
       <c r="D90" s="28"/>
-      <c r="E90" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F90" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G90" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G90" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H90" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I90" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I90" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3551,24 +3223,20 @@
       <c r="B91" s="28"/>
       <c r="C91" s="28"/>
       <c r="D91" s="28"/>
-      <c r="E91" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F91" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G91" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G91" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H91" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I91" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I91" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3576,24 +3244,20 @@
       <c r="B92" s="28"/>
       <c r="C92" s="28"/>
       <c r="D92" s="28"/>
-      <c r="E92" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F92" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G92" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G92" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H92" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I92" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I92" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3601,24 +3265,20 @@
       <c r="B93" s="28"/>
       <c r="C93" s="28"/>
       <c r="D93" s="28"/>
-      <c r="E93" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F93" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G93" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G93" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H93" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I93" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I93" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3626,24 +3286,20 @@
       <c r="B94" s="28"/>
       <c r="C94" s="28"/>
       <c r="D94" s="28"/>
-      <c r="E94" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F94" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G94" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G94" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H94" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I94" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I94" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3651,24 +3307,20 @@
       <c r="B95" s="28"/>
       <c r="C95" s="28"/>
       <c r="D95" s="28"/>
-      <c r="E95" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F95" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G95" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G95" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H95" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I95" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I95" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3676,24 +3328,20 @@
       <c r="B96" s="28"/>
       <c r="C96" s="28"/>
       <c r="D96" s="28"/>
-      <c r="E96" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F96" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G96" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G96" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H96" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I96" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I96" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3701,24 +3349,20 @@
       <c r="B97" s="28"/>
       <c r="C97" s="28"/>
       <c r="D97" s="28"/>
-      <c r="E97" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F97" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G97" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G97" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H97" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I97" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I97" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3726,24 +3370,20 @@
       <c r="B98" s="28"/>
       <c r="C98" s="28"/>
       <c r="D98" s="28"/>
-      <c r="E98" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F98" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G98" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G98" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H98" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I98" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I98" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3751,24 +3391,20 @@
       <c r="B99" s="28"/>
       <c r="C99" s="28"/>
       <c r="D99" s="28"/>
-      <c r="E99" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F99" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G99" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G99" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H99" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I99" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I99" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3776,24 +3412,20 @@
       <c r="B100" s="28"/>
       <c r="C100" s="28"/>
       <c r="D100" s="28"/>
-      <c r="E100" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F100" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G100" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G100" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H100" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I100" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I100" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3801,24 +3433,20 @@
       <c r="B101" s="28"/>
       <c r="C101" s="28"/>
       <c r="D101" s="28"/>
-      <c r="E101" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F101" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G101" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G101" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H101" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I101" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I101" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3826,24 +3454,20 @@
       <c r="B102" s="28"/>
       <c r="C102" s="28"/>
       <c r="D102" s="28"/>
-      <c r="E102" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F102" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G102" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G102" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H102" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I102" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I102" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3851,24 +3475,20 @@
       <c r="B103" s="28"/>
       <c r="C103" s="28"/>
       <c r="D103" s="28"/>
-      <c r="E103" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F103" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G103" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G103" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H103" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I103" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I103" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3876,24 +3496,20 @@
       <c r="B104" s="28"/>
       <c r="C104" s="28"/>
       <c r="D104" s="28"/>
-      <c r="E104" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F104" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G104" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G104" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H104" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I104" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I104" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3901,24 +3517,20 @@
       <c r="B105" s="28"/>
       <c r="C105" s="28"/>
       <c r="D105" s="28"/>
-      <c r="E105" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F105" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G105" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G105" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H105" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I105" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I105" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3926,24 +3538,20 @@
       <c r="B106" s="28"/>
       <c r="C106" s="28"/>
       <c r="D106" s="28"/>
-      <c r="E106" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F106" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G106" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G106" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H106" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I106" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I106" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3951,24 +3559,20 @@
       <c r="B107" s="28"/>
       <c r="C107" s="28"/>
       <c r="D107" s="28"/>
-      <c r="E107" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F107" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G107" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G107" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H107" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I107" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I107" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3976,24 +3580,20 @@
       <c r="B108" s="28"/>
       <c r="C108" s="28"/>
       <c r="D108" s="28"/>
-      <c r="E108" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F108" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G108" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G108" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H108" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I108" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I108" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4001,24 +3601,20 @@
       <c r="B109" s="28"/>
       <c r="C109" s="28"/>
       <c r="D109" s="28"/>
-      <c r="E109" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F109" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G109" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G109" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H109" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I109" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I109" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4026,24 +3622,20 @@
       <c r="B110" s="28"/>
       <c r="C110" s="28"/>
       <c r="D110" s="28"/>
-      <c r="E110" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F110" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G110" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G110" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H110" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I110" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I110" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4051,24 +3643,20 @@
       <c r="B111" s="28"/>
       <c r="C111" s="28"/>
       <c r="D111" s="28"/>
-      <c r="E111" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F111" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G111" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G111" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H111" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I111" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I111" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4076,24 +3664,20 @@
       <c r="B112" s="28"/>
       <c r="C112" s="28"/>
       <c r="D112" s="28"/>
-      <c r="E112" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F112" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G112" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G112" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H112" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I112" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I112" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4101,24 +3685,20 @@
       <c r="B113" s="28"/>
       <c r="C113" s="28"/>
       <c r="D113" s="28"/>
-      <c r="E113" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F113" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G113" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G113" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H113" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I113" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I113" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4126,24 +3706,20 @@
       <c r="B114" s="28"/>
       <c r="C114" s="28"/>
       <c r="D114" s="28"/>
-      <c r="E114" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F114" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G114" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G114" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H114" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I114" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I114" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4151,24 +3727,20 @@
       <c r="B115" s="28"/>
       <c r="C115" s="28"/>
       <c r="D115" s="28"/>
-      <c r="E115" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F115" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G115" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G115" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H115" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I115" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I115" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4176,24 +3748,20 @@
       <c r="B116" s="28"/>
       <c r="C116" s="28"/>
       <c r="D116" s="28"/>
-      <c r="E116" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F116" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G116" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G116" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H116" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I116" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I116" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4201,24 +3769,20 @@
       <c r="B117" s="28"/>
       <c r="C117" s="28"/>
       <c r="D117" s="28"/>
-      <c r="E117" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F117" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G117" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G117" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H117" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I117" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I117" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4226,24 +3790,20 @@
       <c r="B118" s="28"/>
       <c r="C118" s="28"/>
       <c r="D118" s="28"/>
-      <c r="E118" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F118" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G118" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G118" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H118" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I118" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I118" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4251,24 +3811,20 @@
       <c r="B119" s="28"/>
       <c r="C119" s="28"/>
       <c r="D119" s="28"/>
-      <c r="E119" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F119" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G119" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G119" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H119" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I119" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I119" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4276,24 +3832,20 @@
       <c r="B120" s="28"/>
       <c r="C120" s="28"/>
       <c r="D120" s="28"/>
-      <c r="E120" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F120" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G120" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G120" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H120" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I120" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I120" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4301,24 +3853,20 @@
       <c r="B121" s="28"/>
       <c r="C121" s="28"/>
       <c r="D121" s="28"/>
-      <c r="E121" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F121" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G121" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G121" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H121" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I121" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I121" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4326,24 +3874,20 @@
       <c r="B122" s="28"/>
       <c r="C122" s="28"/>
       <c r="D122" s="28"/>
-      <c r="E122" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F122" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G122" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G122" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H122" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I122" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I122" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4351,24 +3895,20 @@
       <c r="B123" s="28"/>
       <c r="C123" s="28"/>
       <c r="D123" s="28"/>
-      <c r="E123" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F123" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G123" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G123" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H123" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I123" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I123" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4376,24 +3916,20 @@
       <c r="B124" s="28"/>
       <c r="C124" s="28"/>
       <c r="D124" s="28"/>
-      <c r="E124" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F124" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G124" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G124" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H124" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I124" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I124" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4401,24 +3937,20 @@
       <c r="B125" s="28"/>
       <c r="C125" s="28"/>
       <c r="D125" s="28"/>
-      <c r="E125" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F125" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G125" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G125" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H125" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I125" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I125" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4426,24 +3958,20 @@
       <c r="B126" s="28"/>
       <c r="C126" s="28"/>
       <c r="D126" s="28"/>
-      <c r="E126" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F126" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G126" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G126" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H126" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I126" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I126" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4451,24 +3979,20 @@
       <c r="B127" s="28"/>
       <c r="C127" s="28"/>
       <c r="D127" s="28"/>
-      <c r="E127" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F127" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G127" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G127" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H127" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I127" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I127" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4476,24 +4000,20 @@
       <c r="B128" s="28"/>
       <c r="C128" s="28"/>
       <c r="D128" s="28"/>
-      <c r="E128" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F128" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G128" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G128" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H128" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I128" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I128" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4501,24 +4021,20 @@
       <c r="B129" s="28"/>
       <c r="C129" s="28"/>
       <c r="D129" s="28"/>
-      <c r="E129" t="str">
-        <f t="shared" si="5"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F129" s="29" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="G129" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="G129" s="29" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
       <c r="H129" s="29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="I129" s="29" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I129" s="29" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4526,24 +4042,20 @@
       <c r="B130" s="28"/>
       <c r="C130" s="28"/>
       <c r="D130" s="28"/>
-      <c r="E130" t="str">
-        <f t="shared" ref="E130:E193" si="10">IF(D130="","Em trânsito","Recebido")</f>
-        <v>Em trânsito</v>
-      </c>
       <c r="F130" s="29" t="str">
-        <f t="shared" ref="F130:F193" ca="1" si="11">IF(B130="","",IF(E130="Recebido",D130-B130,TODAY()-B130))</f>
+        <f t="shared" ref="F130:F193" ca="1" si="9">IF(B130="","",IF(E130="Recebido",D130-B130,TODAY()-B130))</f>
         <v/>
       </c>
       <c r="G130" s="29" t="str">
-        <f t="shared" ref="G130:G193" ca="1" si="12">IF(C130="","",IF(E130="Recebido",D130-C130,TODAY()-C130))</f>
+        <f t="shared" ref="G130:G193" ca="1" si="10">IF(C130="","",IF(E130="Recebido",D130-C130,TODAY()-C130))</f>
         <v/>
       </c>
       <c r="H130" s="29" t="str">
-        <f t="shared" ref="H130:H193" si="13">IF(OR(B130="",C130=""),"",C130-B130)</f>
+        <f t="shared" ref="H130:H193" si="11">IF(OR(B130="",C130=""),"",C130-B130)</f>
         <v/>
       </c>
       <c r="I130" s="29" t="str">
-        <f t="shared" ref="I130:I193" si="14">IF(OR(C130="",D130=""),"",D130-C130)</f>
+        <f t="shared" ref="I130:I193" si="12">IF(OR(C130="",D130=""),"",D130-C130)</f>
         <v/>
       </c>
     </row>
@@ -4551,24 +4063,20 @@
       <c r="B131" s="28"/>
       <c r="C131" s="28"/>
       <c r="D131" s="28"/>
-      <c r="E131" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F131" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G131" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H131" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I131" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4576,24 +4084,20 @@
       <c r="B132" s="28"/>
       <c r="C132" s="28"/>
       <c r="D132" s="28"/>
-      <c r="E132" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F132" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G132" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H132" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I132" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4601,24 +4105,20 @@
       <c r="B133" s="28"/>
       <c r="C133" s="28"/>
       <c r="D133" s="28"/>
-      <c r="E133" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F133" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G133" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H133" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I133" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4626,24 +4126,20 @@
       <c r="B134" s="28"/>
       <c r="C134" s="28"/>
       <c r="D134" s="28"/>
-      <c r="E134" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F134" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G134" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H134" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I134" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4651,24 +4147,20 @@
       <c r="B135" s="28"/>
       <c r="C135" s="28"/>
       <c r="D135" s="28"/>
-      <c r="E135" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F135" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G135" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H135" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I135" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4676,24 +4168,20 @@
       <c r="B136" s="28"/>
       <c r="C136" s="28"/>
       <c r="D136" s="28"/>
-      <c r="E136" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F136" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G136" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H136" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I136" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4701,24 +4189,20 @@
       <c r="B137" s="28"/>
       <c r="C137" s="28"/>
       <c r="D137" s="28"/>
-      <c r="E137" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F137" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G137" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H137" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I137" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4726,24 +4210,20 @@
       <c r="B138" s="28"/>
       <c r="C138" s="28"/>
       <c r="D138" s="28"/>
-      <c r="E138" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F138" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G138" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H138" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I138" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4751,24 +4231,20 @@
       <c r="B139" s="28"/>
       <c r="C139" s="28"/>
       <c r="D139" s="28"/>
-      <c r="E139" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F139" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G139" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H139" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I139" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4776,24 +4252,20 @@
       <c r="B140" s="28"/>
       <c r="C140" s="28"/>
       <c r="D140" s="28"/>
-      <c r="E140" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F140" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G140" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H140" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I140" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4801,24 +4273,20 @@
       <c r="B141" s="28"/>
       <c r="C141" s="28"/>
       <c r="D141" s="28"/>
-      <c r="E141" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F141" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G141" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H141" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I141" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4826,24 +4294,20 @@
       <c r="B142" s="28"/>
       <c r="C142" s="28"/>
       <c r="D142" s="28"/>
-      <c r="E142" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F142" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G142" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H142" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I142" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4851,24 +4315,20 @@
       <c r="B143" s="28"/>
       <c r="C143" s="28"/>
       <c r="D143" s="28"/>
-      <c r="E143" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F143" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G143" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H143" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I143" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4876,24 +4336,20 @@
       <c r="B144" s="28"/>
       <c r="C144" s="28"/>
       <c r="D144" s="28"/>
-      <c r="E144" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F144" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G144" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H144" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I144" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4901,24 +4357,20 @@
       <c r="B145" s="28"/>
       <c r="C145" s="28"/>
       <c r="D145" s="28"/>
-      <c r="E145" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F145" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G145" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H145" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I145" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4926,24 +4378,20 @@
       <c r="B146" s="28"/>
       <c r="C146" s="28"/>
       <c r="D146" s="28"/>
-      <c r="E146" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F146" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G146" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H146" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I146" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4951,24 +4399,20 @@
       <c r="B147" s="28"/>
       <c r="C147" s="28"/>
       <c r="D147" s="28"/>
-      <c r="E147" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F147" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G147" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H147" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I147" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -4976,24 +4420,20 @@
       <c r="B148" s="28"/>
       <c r="C148" s="28"/>
       <c r="D148" s="28"/>
-      <c r="E148" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F148" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G148" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H148" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I148" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5001,24 +4441,20 @@
       <c r="B149" s="28"/>
       <c r="C149" s="28"/>
       <c r="D149" s="28"/>
-      <c r="E149" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F149" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G149" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H149" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I149" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5026,24 +4462,20 @@
       <c r="B150" s="28"/>
       <c r="C150" s="28"/>
       <c r="D150" s="28"/>
-      <c r="E150" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F150" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G150" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H150" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I150" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5051,24 +4483,20 @@
       <c r="B151" s="28"/>
       <c r="C151" s="28"/>
       <c r="D151" s="28"/>
-      <c r="E151" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F151" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G151" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H151" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I151" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5076,24 +4504,20 @@
       <c r="B152" s="28"/>
       <c r="C152" s="28"/>
       <c r="D152" s="28"/>
-      <c r="E152" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F152" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G152" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H152" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I152" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5101,24 +4525,20 @@
       <c r="B153" s="28"/>
       <c r="C153" s="28"/>
       <c r="D153" s="28"/>
-      <c r="E153" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F153" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G153" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H153" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I153" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5126,24 +4546,20 @@
       <c r="B154" s="28"/>
       <c r="C154" s="28"/>
       <c r="D154" s="28"/>
-      <c r="E154" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F154" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G154" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H154" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I154" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5151,24 +4567,20 @@
       <c r="B155" s="28"/>
       <c r="C155" s="28"/>
       <c r="D155" s="28"/>
-      <c r="E155" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F155" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G155" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H155" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I155" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5176,24 +4588,20 @@
       <c r="B156" s="28"/>
       <c r="C156" s="28"/>
       <c r="D156" s="28"/>
-      <c r="E156" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F156" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G156" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H156" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I156" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5201,24 +4609,20 @@
       <c r="B157" s="28"/>
       <c r="C157" s="28"/>
       <c r="D157" s="28"/>
-      <c r="E157" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F157" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G157" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H157" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I157" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5226,24 +4630,20 @@
       <c r="B158" s="28"/>
       <c r="C158" s="28"/>
       <c r="D158" s="28"/>
-      <c r="E158" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F158" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G158" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H158" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I158" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5251,24 +4651,20 @@
       <c r="B159" s="28"/>
       <c r="C159" s="28"/>
       <c r="D159" s="28"/>
-      <c r="E159" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F159" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G159" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H159" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I159" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5276,24 +4672,20 @@
       <c r="B160" s="28"/>
       <c r="C160" s="28"/>
       <c r="D160" s="28"/>
-      <c r="E160" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F160" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G160" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H160" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I160" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5301,24 +4693,20 @@
       <c r="B161" s="28"/>
       <c r="C161" s="28"/>
       <c r="D161" s="28"/>
-      <c r="E161" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F161" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G161" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H161" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I161" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5326,24 +4714,20 @@
       <c r="B162" s="28"/>
       <c r="C162" s="28"/>
       <c r="D162" s="28"/>
-      <c r="E162" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F162" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G162" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H162" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I162" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5351,24 +4735,20 @@
       <c r="B163" s="28"/>
       <c r="C163" s="28"/>
       <c r="D163" s="28"/>
-      <c r="E163" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F163" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G163" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H163" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I163" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5376,24 +4756,20 @@
       <c r="B164" s="28"/>
       <c r="C164" s="28"/>
       <c r="D164" s="28"/>
-      <c r="E164" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F164" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G164" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H164" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I164" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5401,24 +4777,20 @@
       <c r="B165" s="28"/>
       <c r="C165" s="28"/>
       <c r="D165" s="28"/>
-      <c r="E165" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F165" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G165" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H165" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I165" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5426,24 +4798,20 @@
       <c r="B166" s="28"/>
       <c r="C166" s="28"/>
       <c r="D166" s="28"/>
-      <c r="E166" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F166" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G166" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H166" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I166" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5451,24 +4819,20 @@
       <c r="B167" s="28"/>
       <c r="C167" s="28"/>
       <c r="D167" s="28"/>
-      <c r="E167" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F167" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G167" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H167" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I167" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5476,24 +4840,20 @@
       <c r="B168" s="28"/>
       <c r="C168" s="28"/>
       <c r="D168" s="28"/>
-      <c r="E168" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F168" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G168" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H168" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I168" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5501,24 +4861,20 @@
       <c r="B169" s="28"/>
       <c r="C169" s="28"/>
       <c r="D169" s="28"/>
-      <c r="E169" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F169" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G169" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H169" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I169" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5526,24 +4882,20 @@
       <c r="B170" s="28"/>
       <c r="C170" s="28"/>
       <c r="D170" s="28"/>
-      <c r="E170" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F170" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G170" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H170" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I170" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5551,24 +4903,20 @@
       <c r="B171" s="28"/>
       <c r="C171" s="28"/>
       <c r="D171" s="28"/>
-      <c r="E171" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F171" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G171" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H171" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I171" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5576,24 +4924,20 @@
       <c r="B172" s="28"/>
       <c r="C172" s="28"/>
       <c r="D172" s="28"/>
-      <c r="E172" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F172" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G172" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H172" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I172" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5601,24 +4945,20 @@
       <c r="B173" s="28"/>
       <c r="C173" s="28"/>
       <c r="D173" s="28"/>
-      <c r="E173" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F173" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G173" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H173" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I173" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5626,24 +4966,20 @@
       <c r="B174" s="28"/>
       <c r="C174" s="28"/>
       <c r="D174" s="28"/>
-      <c r="E174" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F174" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G174" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H174" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I174" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5651,24 +4987,20 @@
       <c r="B175" s="28"/>
       <c r="C175" s="28"/>
       <c r="D175" s="28"/>
-      <c r="E175" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F175" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G175" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H175" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I175" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5676,24 +5008,20 @@
       <c r="B176" s="28"/>
       <c r="C176" s="28"/>
       <c r="D176" s="28"/>
-      <c r="E176" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F176" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G176" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H176" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I176" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5701,24 +5029,20 @@
       <c r="B177" s="28"/>
       <c r="C177" s="28"/>
       <c r="D177" s="28"/>
-      <c r="E177" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F177" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G177" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H177" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I177" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5726,24 +5050,20 @@
       <c r="B178" s="28"/>
       <c r="C178" s="28"/>
       <c r="D178" s="28"/>
-      <c r="E178" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F178" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G178" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H178" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I178" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5751,24 +5071,20 @@
       <c r="B179" s="28"/>
       <c r="C179" s="28"/>
       <c r="D179" s="28"/>
-      <c r="E179" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F179" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G179" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H179" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I179" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5776,24 +5092,20 @@
       <c r="B180" s="28"/>
       <c r="C180" s="28"/>
       <c r="D180" s="28"/>
-      <c r="E180" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F180" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G180" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H180" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I180" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5801,24 +5113,20 @@
       <c r="B181" s="28"/>
       <c r="C181" s="28"/>
       <c r="D181" s="28"/>
-      <c r="E181" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F181" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G181" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H181" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I181" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5826,24 +5134,20 @@
       <c r="B182" s="28"/>
       <c r="C182" s="28"/>
       <c r="D182" s="28"/>
-      <c r="E182" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F182" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G182" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H182" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I182" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5851,24 +5155,20 @@
       <c r="B183" s="28"/>
       <c r="C183" s="28"/>
       <c r="D183" s="28"/>
-      <c r="E183" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F183" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G183" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H183" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I183" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5876,24 +5176,20 @@
       <c r="B184" s="28"/>
       <c r="C184" s="28"/>
       <c r="D184" s="28"/>
-      <c r="E184" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F184" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G184" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H184" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I184" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5901,24 +5197,20 @@
       <c r="B185" s="28"/>
       <c r="C185" s="28"/>
       <c r="D185" s="28"/>
-      <c r="E185" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F185" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G185" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H185" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I185" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5926,24 +5218,20 @@
       <c r="B186" s="28"/>
       <c r="C186" s="28"/>
       <c r="D186" s="28"/>
-      <c r="E186" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F186" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G186" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H186" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I186" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5951,24 +5239,20 @@
       <c r="B187" s="28"/>
       <c r="C187" s="28"/>
       <c r="D187" s="28"/>
-      <c r="E187" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F187" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G187" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H187" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I187" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -5976,24 +5260,20 @@
       <c r="B188" s="28"/>
       <c r="C188" s="28"/>
       <c r="D188" s="28"/>
-      <c r="E188" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F188" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G188" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H188" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I188" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -6001,24 +5281,20 @@
       <c r="B189" s="28"/>
       <c r="C189" s="28"/>
       <c r="D189" s="28"/>
-      <c r="E189" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F189" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G189" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H189" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I189" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -6026,24 +5302,20 @@
       <c r="B190" s="28"/>
       <c r="C190" s="28"/>
       <c r="D190" s="28"/>
-      <c r="E190" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F190" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G190" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H190" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I190" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -6051,24 +5323,20 @@
       <c r="B191" s="28"/>
       <c r="C191" s="28"/>
       <c r="D191" s="28"/>
-      <c r="E191" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F191" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G191" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H191" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I191" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -6076,24 +5344,20 @@
       <c r="B192" s="28"/>
       <c r="C192" s="28"/>
       <c r="D192" s="28"/>
-      <c r="E192" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F192" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G192" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H192" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I192" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -6101,24 +5365,20 @@
       <c r="B193" s="28"/>
       <c r="C193" s="28"/>
       <c r="D193" s="28"/>
-      <c r="E193" t="str">
-        <f t="shared" si="10"/>
-        <v>Em trânsito</v>
-      </c>
       <c r="F193" s="29" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="G193" s="29" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H193" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I193" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -6126,24 +5386,20 @@
       <c r="B194" s="28"/>
       <c r="C194" s="28"/>
       <c r="D194" s="28"/>
-      <c r="E194" t="str">
-        <f t="shared" ref="E194:E257" si="15">IF(D194="","Em trânsito","Recebido")</f>
-        <v>Em trânsito</v>
-      </c>
       <c r="F194" s="29" t="str">
-        <f t="shared" ref="F194:F257" ca="1" si="16">IF(B194="","",IF(E194="Recebido",D194-B194,TODAY()-B194))</f>
+        <f t="shared" ref="F194:F257" ca="1" si="13">IF(B194="","",IF(E194="Recebido",D194-B194,TODAY()-B194))</f>
         <v/>
       </c>
       <c r="G194" s="29" t="str">
-        <f t="shared" ref="G194:G257" ca="1" si="17">IF(C194="","",IF(E194="Recebido",D194-C194,TODAY()-C194))</f>
+        <f t="shared" ref="G194:G257" ca="1" si="14">IF(C194="","",IF(E194="Recebido",D194-C194,TODAY()-C194))</f>
         <v/>
       </c>
       <c r="H194" s="29" t="str">
-        <f t="shared" ref="H194:H257" si="18">IF(OR(B194="",C194=""),"",C194-B194)</f>
+        <f t="shared" ref="H194:H257" si="15">IF(OR(B194="",C194=""),"",C194-B194)</f>
         <v/>
       </c>
       <c r="I194" s="29" t="str">
-        <f t="shared" ref="I194:I257" si="19">IF(OR(C194="",D194=""),"",D194-C194)</f>
+        <f t="shared" ref="I194:I257" si="16">IF(OR(C194="",D194=""),"",D194-C194)</f>
         <v/>
       </c>
     </row>
@@ -6151,24 +5407,20 @@
       <c r="B195" s="28"/>
       <c r="C195" s="28"/>
       <c r="D195" s="28"/>
-      <c r="E195" t="str">
+      <c r="F195" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G195" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H195" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F195" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G195" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H195" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I195" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6176,24 +5428,20 @@
       <c r="B196" s="28"/>
       <c r="C196" s="28"/>
       <c r="D196" s="28"/>
-      <c r="E196" t="str">
+      <c r="F196" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G196" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H196" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F196" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G196" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H196" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I196" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6201,24 +5449,20 @@
       <c r="B197" s="28"/>
       <c r="C197" s="28"/>
       <c r="D197" s="28"/>
-      <c r="E197" t="str">
+      <c r="F197" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G197" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H197" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F197" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G197" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H197" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I197" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6226,24 +5470,20 @@
       <c r="B198" s="28"/>
       <c r="C198" s="28"/>
       <c r="D198" s="28"/>
-      <c r="E198" t="str">
+      <c r="F198" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G198" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H198" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F198" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G198" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H198" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I198" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6251,24 +5491,20 @@
       <c r="B199" s="28"/>
       <c r="C199" s="28"/>
       <c r="D199" s="28"/>
-      <c r="E199" t="str">
+      <c r="F199" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G199" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H199" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F199" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G199" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H199" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I199" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6276,24 +5512,20 @@
       <c r="B200" s="28"/>
       <c r="C200" s="28"/>
       <c r="D200" s="28"/>
-      <c r="E200" t="str">
+      <c r="F200" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G200" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H200" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F200" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G200" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H200" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I200" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6301,24 +5533,20 @@
       <c r="B201" s="28"/>
       <c r="C201" s="28"/>
       <c r="D201" s="28"/>
-      <c r="E201" t="str">
+      <c r="F201" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G201" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H201" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F201" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G201" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H201" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I201" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6326,24 +5554,20 @@
       <c r="B202" s="28"/>
       <c r="C202" s="28"/>
       <c r="D202" s="28"/>
-      <c r="E202" t="str">
+      <c r="F202" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G202" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H202" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F202" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G202" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H202" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I202" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6351,24 +5575,20 @@
       <c r="B203" s="28"/>
       <c r="C203" s="28"/>
       <c r="D203" s="28"/>
-      <c r="E203" t="str">
+      <c r="F203" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G203" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H203" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F203" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G203" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H203" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I203" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6376,24 +5596,20 @@
       <c r="B204" s="28"/>
       <c r="C204" s="28"/>
       <c r="D204" s="28"/>
-      <c r="E204" t="str">
+      <c r="F204" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G204" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H204" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F204" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G204" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H204" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I204" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6401,24 +5617,20 @@
       <c r="B205" s="28"/>
       <c r="C205" s="28"/>
       <c r="D205" s="28"/>
-      <c r="E205" t="str">
+      <c r="F205" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G205" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H205" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F205" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G205" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H205" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I205" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6426,24 +5638,20 @@
       <c r="B206" s="28"/>
       <c r="C206" s="28"/>
       <c r="D206" s="28"/>
-      <c r="E206" t="str">
+      <c r="F206" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G206" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H206" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F206" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G206" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H206" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I206" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6451,24 +5659,20 @@
       <c r="B207" s="28"/>
       <c r="C207" s="28"/>
       <c r="D207" s="28"/>
-      <c r="E207" t="str">
+      <c r="F207" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G207" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H207" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F207" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G207" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H207" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I207" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6476,24 +5680,20 @@
       <c r="B208" s="28"/>
       <c r="C208" s="28"/>
       <c r="D208" s="28"/>
-      <c r="E208" t="str">
+      <c r="F208" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G208" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H208" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F208" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G208" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H208" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I208" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6501,24 +5701,20 @@
       <c r="B209" s="28"/>
       <c r="C209" s="28"/>
       <c r="D209" s="28"/>
-      <c r="E209" t="str">
+      <c r="F209" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G209" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H209" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F209" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G209" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H209" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I209" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6526,24 +5722,20 @@
       <c r="B210" s="28"/>
       <c r="C210" s="28"/>
       <c r="D210" s="28"/>
-      <c r="E210" t="str">
+      <c r="F210" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G210" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H210" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F210" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G210" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H210" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I210" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6551,24 +5743,20 @@
       <c r="B211" s="28"/>
       <c r="C211" s="28"/>
       <c r="D211" s="28"/>
-      <c r="E211" t="str">
+      <c r="F211" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G211" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H211" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F211" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G211" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H211" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I211" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6576,24 +5764,20 @@
       <c r="B212" s="28"/>
       <c r="C212" s="28"/>
       <c r="D212" s="28"/>
-      <c r="E212" t="str">
+      <c r="F212" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G212" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H212" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F212" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G212" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H212" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I212" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6601,24 +5785,20 @@
       <c r="B213" s="28"/>
       <c r="C213" s="28"/>
       <c r="D213" s="28"/>
-      <c r="E213" t="str">
+      <c r="F213" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G213" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H213" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F213" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G213" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H213" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I213" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6626,24 +5806,20 @@
       <c r="B214" s="28"/>
       <c r="C214" s="28"/>
       <c r="D214" s="28"/>
-      <c r="E214" t="str">
+      <c r="F214" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G214" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H214" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F214" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G214" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H214" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I214" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6651,24 +5827,20 @@
       <c r="B215" s="28"/>
       <c r="C215" s="28"/>
       <c r="D215" s="28"/>
-      <c r="E215" t="str">
+      <c r="F215" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G215" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H215" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F215" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G215" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H215" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I215" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6676,24 +5848,20 @@
       <c r="B216" s="28"/>
       <c r="C216" s="28"/>
       <c r="D216" s="28"/>
-      <c r="E216" t="str">
+      <c r="F216" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G216" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H216" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F216" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G216" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H216" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I216" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6701,24 +5869,20 @@
       <c r="B217" s="28"/>
       <c r="C217" s="28"/>
       <c r="D217" s="28"/>
-      <c r="E217" t="str">
+      <c r="F217" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G217" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H217" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F217" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G217" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H217" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I217" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6726,24 +5890,20 @@
       <c r="B218" s="28"/>
       <c r="C218" s="28"/>
       <c r="D218" s="28"/>
-      <c r="E218" t="str">
+      <c r="F218" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G218" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H218" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F218" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G218" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H218" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I218" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6751,24 +5911,20 @@
       <c r="B219" s="28"/>
       <c r="C219" s="28"/>
       <c r="D219" s="28"/>
-      <c r="E219" t="str">
+      <c r="F219" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G219" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H219" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F219" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G219" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H219" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I219" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6776,24 +5932,20 @@
       <c r="B220" s="28"/>
       <c r="C220" s="28"/>
       <c r="D220" s="28"/>
-      <c r="E220" t="str">
+      <c r="F220" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G220" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H220" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F220" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G220" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H220" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I220" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6801,24 +5953,20 @@
       <c r="B221" s="28"/>
       <c r="C221" s="28"/>
       <c r="D221" s="28"/>
-      <c r="E221" t="str">
+      <c r="F221" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G221" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H221" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F221" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G221" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H221" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I221" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6826,24 +5974,20 @@
       <c r="B222" s="28"/>
       <c r="C222" s="28"/>
       <c r="D222" s="28"/>
-      <c r="E222" t="str">
+      <c r="F222" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G222" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H222" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F222" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G222" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H222" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I222" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6851,24 +5995,20 @@
       <c r="B223" s="28"/>
       <c r="C223" s="28"/>
       <c r="D223" s="28"/>
-      <c r="E223" t="str">
+      <c r="F223" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G223" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H223" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F223" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G223" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H223" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I223" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6876,24 +6016,20 @@
       <c r="B224" s="28"/>
       <c r="C224" s="28"/>
       <c r="D224" s="28"/>
-      <c r="E224" t="str">
+      <c r="F224" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G224" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H224" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F224" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G224" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H224" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I224" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6901,24 +6037,20 @@
       <c r="B225" s="28"/>
       <c r="C225" s="28"/>
       <c r="D225" s="28"/>
-      <c r="E225" t="str">
+      <c r="F225" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G225" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H225" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F225" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G225" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H225" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I225" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6926,24 +6058,20 @@
       <c r="B226" s="28"/>
       <c r="C226" s="28"/>
       <c r="D226" s="28"/>
-      <c r="E226" t="str">
+      <c r="F226" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G226" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H226" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F226" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G226" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H226" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I226" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6951,24 +6079,20 @@
       <c r="B227" s="28"/>
       <c r="C227" s="28"/>
       <c r="D227" s="28"/>
-      <c r="E227" t="str">
+      <c r="F227" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G227" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H227" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F227" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G227" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H227" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I227" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6976,24 +6100,20 @@
       <c r="B228" s="28"/>
       <c r="C228" s="28"/>
       <c r="D228" s="28"/>
-      <c r="E228" t="str">
+      <c r="F228" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G228" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H228" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F228" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G228" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H228" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I228" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7001,24 +6121,20 @@
       <c r="B229" s="28"/>
       <c r="C229" s="28"/>
       <c r="D229" s="28"/>
-      <c r="E229" t="str">
+      <c r="F229" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G229" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H229" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F229" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G229" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H229" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I229" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7026,24 +6142,20 @@
       <c r="B230" s="28"/>
       <c r="C230" s="28"/>
       <c r="D230" s="28"/>
-      <c r="E230" t="str">
+      <c r="F230" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G230" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H230" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F230" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G230" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H230" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I230" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7051,24 +6163,20 @@
       <c r="B231" s="28"/>
       <c r="C231" s="28"/>
       <c r="D231" s="28"/>
-      <c r="E231" t="str">
+      <c r="F231" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G231" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H231" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F231" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G231" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H231" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I231" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7076,24 +6184,20 @@
       <c r="B232" s="28"/>
       <c r="C232" s="28"/>
       <c r="D232" s="28"/>
-      <c r="E232" t="str">
+      <c r="F232" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G232" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H232" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F232" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G232" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H232" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I232" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7101,24 +6205,20 @@
       <c r="B233" s="28"/>
       <c r="C233" s="28"/>
       <c r="D233" s="28"/>
-      <c r="E233" t="str">
+      <c r="F233" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G233" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H233" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F233" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G233" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H233" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I233" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7126,24 +6226,20 @@
       <c r="B234" s="28"/>
       <c r="C234" s="28"/>
       <c r="D234" s="28"/>
-      <c r="E234" t="str">
+      <c r="F234" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G234" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H234" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F234" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G234" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H234" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I234" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7151,24 +6247,20 @@
       <c r="B235" s="28"/>
       <c r="C235" s="28"/>
       <c r="D235" s="28"/>
-      <c r="E235" t="str">
+      <c r="F235" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G235" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H235" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F235" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G235" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H235" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I235" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7176,24 +6268,20 @@
       <c r="B236" s="28"/>
       <c r="C236" s="28"/>
       <c r="D236" s="28"/>
-      <c r="E236" t="str">
+      <c r="F236" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G236" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H236" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F236" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G236" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H236" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I236" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7201,24 +6289,20 @@
       <c r="B237" s="28"/>
       <c r="C237" s="28"/>
       <c r="D237" s="28"/>
-      <c r="E237" t="str">
+      <c r="F237" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G237" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H237" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F237" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G237" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H237" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I237" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7226,24 +6310,20 @@
       <c r="B238" s="28"/>
       <c r="C238" s="28"/>
       <c r="D238" s="28"/>
-      <c r="E238" t="str">
+      <c r="F238" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G238" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H238" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F238" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G238" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H238" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I238" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7251,24 +6331,20 @@
       <c r="B239" s="28"/>
       <c r="C239" s="28"/>
       <c r="D239" s="28"/>
-      <c r="E239" t="str">
+      <c r="F239" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G239" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H239" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F239" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G239" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H239" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I239" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7276,24 +6352,20 @@
       <c r="B240" s="28"/>
       <c r="C240" s="28"/>
       <c r="D240" s="28"/>
-      <c r="E240" t="str">
+      <c r="F240" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G240" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H240" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F240" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G240" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H240" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I240" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7301,24 +6373,20 @@
       <c r="B241" s="28"/>
       <c r="C241" s="28"/>
       <c r="D241" s="28"/>
-      <c r="E241" t="str">
+      <c r="F241" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G241" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H241" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F241" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G241" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H241" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I241" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7326,24 +6394,20 @@
       <c r="B242" s="28"/>
       <c r="C242" s="28"/>
       <c r="D242" s="28"/>
-      <c r="E242" t="str">
+      <c r="F242" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G242" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H242" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F242" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G242" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H242" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I242" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7351,24 +6415,20 @@
       <c r="B243" s="28"/>
       <c r="C243" s="28"/>
       <c r="D243" s="28"/>
-      <c r="E243" t="str">
+      <c r="F243" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G243" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H243" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F243" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G243" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H243" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I243" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7376,24 +6436,20 @@
       <c r="B244" s="28"/>
       <c r="C244" s="28"/>
       <c r="D244" s="28"/>
-      <c r="E244" t="str">
+      <c r="F244" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G244" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H244" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F244" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G244" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H244" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I244" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7401,24 +6457,20 @@
       <c r="B245" s="28"/>
       <c r="C245" s="28"/>
       <c r="D245" s="28"/>
-      <c r="E245" t="str">
+      <c r="F245" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G245" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H245" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F245" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G245" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H245" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I245" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7426,24 +6478,20 @@
       <c r="B246" s="28"/>
       <c r="C246" s="28"/>
       <c r="D246" s="28"/>
-      <c r="E246" t="str">
+      <c r="F246" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G246" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H246" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F246" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G246" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H246" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I246" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7451,24 +6499,20 @@
       <c r="B247" s="28"/>
       <c r="C247" s="28"/>
       <c r="D247" s="28"/>
-      <c r="E247" t="str">
+      <c r="F247" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G247" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H247" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F247" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G247" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H247" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I247" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7476,24 +6520,20 @@
       <c r="B248" s="28"/>
       <c r="C248" s="28"/>
       <c r="D248" s="28"/>
-      <c r="E248" t="str">
+      <c r="F248" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G248" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H248" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F248" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G248" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H248" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I248" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7501,24 +6541,20 @@
       <c r="B249" s="28"/>
       <c r="C249" s="28"/>
       <c r="D249" s="28"/>
-      <c r="E249" t="str">
+      <c r="F249" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G249" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H249" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F249" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G249" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H249" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I249" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7526,24 +6562,20 @@
       <c r="B250" s="28"/>
       <c r="C250" s="28"/>
       <c r="D250" s="28"/>
-      <c r="E250" t="str">
+      <c r="F250" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G250" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H250" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F250" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G250" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H250" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I250" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7551,24 +6583,20 @@
       <c r="B251" s="28"/>
       <c r="C251" s="28"/>
       <c r="D251" s="28"/>
-      <c r="E251" t="str">
+      <c r="F251" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G251" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H251" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F251" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G251" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H251" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I251" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7576,24 +6604,20 @@
       <c r="B252" s="28"/>
       <c r="C252" s="28"/>
       <c r="D252" s="28"/>
-      <c r="E252" t="str">
+      <c r="F252" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G252" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H252" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F252" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G252" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H252" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I252" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7601,24 +6625,20 @@
       <c r="B253" s="28"/>
       <c r="C253" s="28"/>
       <c r="D253" s="28"/>
-      <c r="E253" t="str">
+      <c r="F253" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G253" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H253" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F253" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G253" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H253" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I253" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7626,24 +6646,20 @@
       <c r="B254" s="28"/>
       <c r="C254" s="28"/>
       <c r="D254" s="28"/>
-      <c r="E254" t="str">
+      <c r="F254" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G254" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H254" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F254" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G254" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H254" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I254" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7651,24 +6667,20 @@
       <c r="B255" s="28"/>
       <c r="C255" s="28"/>
       <c r="D255" s="28"/>
-      <c r="E255" t="str">
+      <c r="F255" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G255" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H255" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F255" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G255" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H255" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I255" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7676,24 +6688,20 @@
       <c r="B256" s="28"/>
       <c r="C256" s="28"/>
       <c r="D256" s="28"/>
-      <c r="E256" t="str">
+      <c r="F256" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G256" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H256" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F256" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G256" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H256" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I256" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7701,24 +6709,20 @@
       <c r="B257" s="28"/>
       <c r="C257" s="28"/>
       <c r="D257" s="28"/>
-      <c r="E257" t="str">
+      <c r="F257" s="29" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="G257" s="29" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="H257" s="29" t="str">
         <f t="shared" si="15"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F257" s="29" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="G257" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="H257" s="29" t="str">
-        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I257" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -7726,24 +6730,20 @@
       <c r="B258" s="28"/>
       <c r="C258" s="28"/>
       <c r="D258" s="28"/>
-      <c r="E258" t="str">
-        <f t="shared" ref="E258:E321" si="20">IF(D258="","Em trânsito","Recebido")</f>
-        <v>Em trânsito</v>
-      </c>
       <c r="F258" s="29" t="str">
-        <f t="shared" ref="F258:F321" ca="1" si="21">IF(B258="","",IF(E258="Recebido",D258-B258,TODAY()-B258))</f>
+        <f t="shared" ref="F258:F321" ca="1" si="17">IF(B258="","",IF(E258="Recebido",D258-B258,TODAY()-B258))</f>
         <v/>
       </c>
       <c r="G258" s="29" t="str">
-        <f t="shared" ref="G258:G300" ca="1" si="22">IF(C258="","",IF(E258="Recebido",D258-C258,TODAY()-C258))</f>
+        <f t="shared" ref="G258:G300" ca="1" si="18">IF(C258="","",IF(E258="Recebido",D258-C258,TODAY()-C258))</f>
         <v/>
       </c>
       <c r="H258" s="29" t="str">
-        <f t="shared" ref="H258:H300" si="23">IF(OR(B258="",C258=""),"",C258-B258)</f>
+        <f t="shared" ref="H258:H300" si="19">IF(OR(B258="",C258=""),"",C258-B258)</f>
         <v/>
       </c>
       <c r="I258" s="29" t="str">
-        <f t="shared" ref="I258:I300" si="24">IF(OR(C258="",D258=""),"",D258-C258)</f>
+        <f t="shared" ref="I258:I300" si="20">IF(OR(C258="",D258=""),"",D258-C258)</f>
         <v/>
       </c>
     </row>
@@ -7751,24 +6751,20 @@
       <c r="B259" s="28"/>
       <c r="C259" s="28"/>
       <c r="D259" s="28"/>
-      <c r="E259" t="str">
+      <c r="F259" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G259" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H259" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I259" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F259" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G259" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H259" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I259" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7776,24 +6772,20 @@
       <c r="B260" s="28"/>
       <c r="C260" s="28"/>
       <c r="D260" s="28"/>
-      <c r="E260" t="str">
+      <c r="F260" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G260" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H260" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I260" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F260" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G260" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H260" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I260" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7801,24 +6793,20 @@
       <c r="B261" s="28"/>
       <c r="C261" s="28"/>
       <c r="D261" s="28"/>
-      <c r="E261" t="str">
+      <c r="F261" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G261" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H261" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I261" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F261" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G261" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H261" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I261" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7826,24 +6814,20 @@
       <c r="B262" s="28"/>
       <c r="C262" s="28"/>
       <c r="D262" s="28"/>
-      <c r="E262" t="str">
+      <c r="F262" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G262" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H262" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I262" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F262" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G262" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H262" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I262" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7851,24 +6835,20 @@
       <c r="B263" s="28"/>
       <c r="C263" s="28"/>
       <c r="D263" s="28"/>
-      <c r="E263" t="str">
+      <c r="F263" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G263" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H263" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I263" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F263" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G263" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H263" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I263" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7876,24 +6856,20 @@
       <c r="B264" s="28"/>
       <c r="C264" s="28"/>
       <c r="D264" s="28"/>
-      <c r="E264" t="str">
+      <c r="F264" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G264" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H264" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I264" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F264" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G264" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H264" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I264" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7901,24 +6877,20 @@
       <c r="B265" s="28"/>
       <c r="C265" s="28"/>
       <c r="D265" s="28"/>
-      <c r="E265" t="str">
+      <c r="F265" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G265" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H265" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I265" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F265" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G265" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H265" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I265" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7926,24 +6898,20 @@
       <c r="B266" s="28"/>
       <c r="C266" s="28"/>
       <c r="D266" s="28"/>
-      <c r="E266" t="str">
+      <c r="F266" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G266" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H266" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I266" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F266" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G266" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H266" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I266" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7951,24 +6919,20 @@
       <c r="B267" s="28"/>
       <c r="C267" s="28"/>
       <c r="D267" s="28"/>
-      <c r="E267" t="str">
+      <c r="F267" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G267" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H267" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I267" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F267" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G267" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H267" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I267" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -7976,24 +6940,20 @@
       <c r="B268" s="28"/>
       <c r="C268" s="28"/>
       <c r="D268" s="28"/>
-      <c r="E268" t="str">
+      <c r="F268" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G268" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H268" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I268" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F268" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G268" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H268" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I268" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8001,24 +6961,20 @@
       <c r="B269" s="28"/>
       <c r="C269" s="28"/>
       <c r="D269" s="28"/>
-      <c r="E269" t="str">
+      <c r="F269" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G269" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H269" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I269" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F269" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G269" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H269" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I269" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8026,24 +6982,20 @@
       <c r="B270" s="28"/>
       <c r="C270" s="28"/>
       <c r="D270" s="28"/>
-      <c r="E270" t="str">
+      <c r="F270" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G270" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H270" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I270" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F270" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G270" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H270" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I270" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8051,24 +7003,20 @@
       <c r="B271" s="28"/>
       <c r="C271" s="28"/>
       <c r="D271" s="28"/>
-      <c r="E271" t="str">
+      <c r="F271" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G271" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H271" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I271" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F271" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G271" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H271" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I271" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8076,24 +7024,20 @@
       <c r="B272" s="28"/>
       <c r="C272" s="28"/>
       <c r="D272" s="28"/>
-      <c r="E272" t="str">
+      <c r="F272" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G272" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H272" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I272" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F272" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G272" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H272" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I272" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8101,24 +7045,20 @@
       <c r="B273" s="28"/>
       <c r="C273" s="28"/>
       <c r="D273" s="28"/>
-      <c r="E273" t="str">
+      <c r="F273" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G273" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H273" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I273" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F273" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G273" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H273" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I273" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8126,24 +7066,20 @@
       <c r="B274" s="28"/>
       <c r="C274" s="28"/>
       <c r="D274" s="28"/>
-      <c r="E274" t="str">
+      <c r="F274" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G274" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H274" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I274" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F274" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G274" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H274" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I274" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8151,24 +7087,20 @@
       <c r="B275" s="28"/>
       <c r="C275" s="28"/>
       <c r="D275" s="28"/>
-      <c r="E275" t="str">
+      <c r="F275" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G275" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H275" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I275" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F275" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G275" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H275" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I275" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8176,24 +7108,20 @@
       <c r="B276" s="28"/>
       <c r="C276" s="28"/>
       <c r="D276" s="28"/>
-      <c r="E276" t="str">
+      <c r="F276" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G276" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H276" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I276" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F276" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G276" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H276" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I276" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8201,24 +7129,20 @@
       <c r="B277" s="28"/>
       <c r="C277" s="28"/>
       <c r="D277" s="28"/>
-      <c r="E277" t="str">
+      <c r="F277" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G277" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H277" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I277" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F277" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G277" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H277" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I277" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8226,24 +7150,20 @@
       <c r="B278" s="28"/>
       <c r="C278" s="28"/>
       <c r="D278" s="28"/>
-      <c r="E278" t="str">
+      <c r="F278" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G278" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H278" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I278" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F278" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G278" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H278" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I278" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8251,24 +7171,20 @@
       <c r="B279" s="28"/>
       <c r="C279" s="28"/>
       <c r="D279" s="28"/>
-      <c r="E279" t="str">
+      <c r="F279" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G279" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H279" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I279" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F279" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G279" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H279" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I279" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8276,24 +7192,20 @@
       <c r="B280" s="28"/>
       <c r="C280" s="28"/>
       <c r="D280" s="28"/>
-      <c r="E280" t="str">
+      <c r="F280" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G280" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H280" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I280" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F280" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G280" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H280" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I280" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8301,24 +7213,20 @@
       <c r="B281" s="28"/>
       <c r="C281" s="28"/>
       <c r="D281" s="28"/>
-      <c r="E281" t="str">
+      <c r="F281" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G281" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H281" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I281" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F281" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G281" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H281" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I281" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8326,24 +7234,20 @@
       <c r="B282" s="28"/>
       <c r="C282" s="28"/>
       <c r="D282" s="28"/>
-      <c r="E282" t="str">
+      <c r="F282" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G282" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H282" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I282" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F282" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G282" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H282" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I282" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8351,24 +7255,20 @@
       <c r="B283" s="28"/>
       <c r="C283" s="28"/>
       <c r="D283" s="28"/>
-      <c r="E283" t="str">
+      <c r="F283" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G283" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H283" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I283" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F283" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G283" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H283" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I283" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8376,24 +7276,20 @@
       <c r="B284" s="28"/>
       <c r="C284" s="28"/>
       <c r="D284" s="28"/>
-      <c r="E284" t="str">
+      <c r="F284" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G284" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H284" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I284" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F284" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G284" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H284" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I284" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8401,24 +7297,20 @@
       <c r="B285" s="28"/>
       <c r="C285" s="28"/>
       <c r="D285" s="28"/>
-      <c r="E285" t="str">
+      <c r="F285" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G285" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H285" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I285" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F285" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G285" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H285" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I285" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8426,24 +7318,20 @@
       <c r="B286" s="28"/>
       <c r="C286" s="28"/>
       <c r="D286" s="28"/>
-      <c r="E286" t="str">
+      <c r="F286" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G286" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H286" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I286" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F286" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G286" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H286" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I286" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8451,24 +7339,20 @@
       <c r="B287" s="28"/>
       <c r="C287" s="28"/>
       <c r="D287" s="28"/>
-      <c r="E287" t="str">
+      <c r="F287" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G287" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H287" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I287" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F287" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G287" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H287" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I287" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8476,24 +7360,20 @@
       <c r="B288" s="28"/>
       <c r="C288" s="28"/>
       <c r="D288" s="28"/>
-      <c r="E288" t="str">
+      <c r="F288" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G288" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H288" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I288" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F288" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G288" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H288" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I288" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8501,24 +7381,20 @@
       <c r="B289" s="28"/>
       <c r="C289" s="28"/>
       <c r="D289" s="28"/>
-      <c r="E289" t="str">
+      <c r="F289" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G289" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H289" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I289" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F289" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G289" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H289" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I289" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8526,24 +7402,20 @@
       <c r="B290" s="28"/>
       <c r="C290" s="28"/>
       <c r="D290" s="28"/>
-      <c r="E290" t="str">
+      <c r="F290" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G290" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H290" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I290" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F290" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G290" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H290" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I290" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8551,24 +7423,20 @@
       <c r="B291" s="28"/>
       <c r="C291" s="28"/>
       <c r="D291" s="28"/>
-      <c r="E291" t="str">
+      <c r="F291" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G291" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H291" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I291" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F291" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G291" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H291" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I291" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8576,24 +7444,20 @@
       <c r="B292" s="28"/>
       <c r="C292" s="28"/>
       <c r="D292" s="28"/>
-      <c r="E292" t="str">
+      <c r="F292" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G292" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H292" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I292" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F292" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G292" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H292" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I292" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8601,24 +7465,20 @@
       <c r="B293" s="28"/>
       <c r="C293" s="28"/>
       <c r="D293" s="28"/>
-      <c r="E293" t="str">
+      <c r="F293" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G293" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H293" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I293" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F293" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G293" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H293" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I293" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8626,24 +7486,20 @@
       <c r="B294" s="28"/>
       <c r="C294" s="28"/>
       <c r="D294" s="28"/>
-      <c r="E294" t="str">
+      <c r="F294" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G294" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H294" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I294" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F294" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G294" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H294" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I294" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8651,24 +7507,20 @@
       <c r="B295" s="28"/>
       <c r="C295" s="28"/>
       <c r="D295" s="28"/>
-      <c r="E295" t="str">
+      <c r="F295" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G295" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H295" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I295" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F295" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G295" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H295" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I295" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8676,24 +7528,20 @@
       <c r="B296" s="28"/>
       <c r="C296" s="28"/>
       <c r="D296" s="28"/>
-      <c r="E296" t="str">
+      <c r="F296" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G296" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H296" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I296" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F296" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G296" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H296" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I296" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8701,24 +7549,20 @@
       <c r="B297" s="28"/>
       <c r="C297" s="28"/>
       <c r="D297" s="28"/>
-      <c r="E297" t="str">
+      <c r="F297" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G297" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H297" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I297" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F297" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G297" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H297" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I297" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8726,24 +7570,20 @@
       <c r="B298" s="28"/>
       <c r="C298" s="28"/>
       <c r="D298" s="28"/>
-      <c r="E298" t="str">
+      <c r="F298" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G298" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H298" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I298" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F298" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G298" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H298" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I298" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8751,24 +7591,20 @@
       <c r="B299" s="28"/>
       <c r="C299" s="28"/>
       <c r="D299" s="28"/>
-      <c r="E299" t="str">
+      <c r="F299" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G299" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H299" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I299" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F299" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G299" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H299" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I299" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -8776,24 +7612,20 @@
       <c r="B300" s="28"/>
       <c r="C300" s="28"/>
       <c r="D300" s="28"/>
-      <c r="E300" t="str">
+      <c r="F300" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="G300" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="H300" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="I300" s="29" t="str">
         <f t="shared" si="20"/>
-        <v>Em trânsito</v>
-      </c>
-      <c r="F300" s="29" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
-      <c r="G300" s="29" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
-      <c r="H300" s="29" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I300" s="29" t="str">
-        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>

--- a/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
+++ b/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\dashboard_pacotes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CA0E44-56A7-445A-BB8A-61FEE0E23381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="12315" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ORIGINAL" sheetId="1" r:id="rId1"/>
     <sheet name="PACOTES" sheetId="2" r:id="rId2"/>
     <sheet name="DICIONARIO" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="55">
   <si>
     <t>PEDIDOS DE CAMISAS 2026</t>
   </si>
@@ -146,11 +145,53 @@
   <si>
     <t>Data de recebimento - Data do envio</t>
   </si>
+  <si>
+    <t>35.1</t>
+  </si>
+  <si>
+    <t>35.2</t>
+  </si>
+  <si>
+    <t>36.1</t>
+  </si>
+  <si>
+    <t>36.2</t>
+  </si>
+  <si>
+    <t>38.1</t>
+  </si>
+  <si>
+    <t>38.2</t>
+  </si>
+  <si>
+    <t>Código de Rastreio</t>
+  </si>
+  <si>
+    <t>LZ373185768CN</t>
+  </si>
+  <si>
+    <t>LZ373185825CN</t>
+  </si>
+  <si>
+    <t>LZ373185326CN</t>
+  </si>
+  <si>
+    <t>LZ373185887CN</t>
+  </si>
+  <si>
+    <t>LZ373185961CN</t>
+  </si>
+  <si>
+    <t>LZ369979599CN</t>
+  </si>
+  <si>
+    <t>LZ369979625CN</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -454,28 +495,88 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -489,18 +590,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaPacotes" displayName="TabelaPacotes" ref="A1:I8">
-  <autoFilter ref="A1:I8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Pacote"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Data do pedido"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Data do envio"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Data de recebimento"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Status"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Dias desde pedido"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Dias desde envio"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dias pedido→envio"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Duração importação (envio→receb.)"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaPacotes" displayName="TabelaPacotes" ref="A1:J11" headerRowDxfId="3" dataDxfId="1" totalsRowDxfId="2">
+  <autoFilter ref="A1:J11"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Pacote" dataDxfId="12"/>
+    <tableColumn id="10" name="Código de Rastreio" dataDxfId="0"/>
+    <tableColumn id="2" name="Data do pedido" dataDxfId="11"/>
+    <tableColumn id="3" name="Data do envio" dataDxfId="10"/>
+    <tableColumn id="4" name="Data de recebimento" dataDxfId="9"/>
+    <tableColumn id="5" name="Status" dataDxfId="8"/>
+    <tableColumn id="6" name="Dias desde pedido" dataDxfId="7"/>
+    <tableColumn id="7" name="Dias desde envio" dataDxfId="6"/>
+    <tableColumn id="8" name="Dias pedido→envio" dataDxfId="5"/>
+    <tableColumn id="9" name="Duração importação (envio→receb.)" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -681,7 +783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1225,6406 +1327,6531 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I300"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J303"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="1" max="1" width="10" style="12" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="12" customWidth="1"/>
+    <col min="5" max="5" width="18" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12" style="12" customWidth="1"/>
+    <col min="7" max="7" width="16" style="12" customWidth="1"/>
+    <col min="8" max="9" width="15" style="12" customWidth="1"/>
+    <col min="10" max="10" width="24" style="12" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D1" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="J1" s="22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="23">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
         <v>33</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="25"/>
+      <c r="C2" s="26">
         <v>46036</v>
       </c>
-      <c r="C2" s="24">
+      <c r="D2" s="26">
         <v>46038</v>
       </c>
-      <c r="D2" s="24">
+      <c r="E2" s="26">
         <v>46058</v>
       </c>
-      <c r="E2" s="23" t="str">
-        <f t="shared" ref="E2:E65" si="0">IF(D2="","Em trânsito","Recebido")</f>
+      <c r="F2" s="25" t="str">
+        <f t="shared" ref="F2:F11" si="0">IF(E2="","Em trânsito","Recebido")</f>
         <v>Recebido</v>
       </c>
-      <c r="F2" s="27">
-        <f t="shared" ref="F2:F65" ca="1" si="1">IF(B2="","",IF(E2="Recebido",D2-B2,TODAY()-B2))</f>
+      <c r="G2" s="27">
+        <f t="shared" ref="G2:G68" ca="1" si="1">IF(C2="","",IF(F2="Recebido",E2-C2,TODAY()-C2))</f>
         <v>22</v>
       </c>
-      <c r="G2" s="27">
-        <f t="shared" ref="G2:G65" ca="1" si="2">IF(C2="","",IF(E2="Recebido",D2-C2,TODAY()-C2))</f>
+      <c r="H2" s="27">
+        <f t="shared" ref="H2:H68" ca="1" si="2">IF(D2="","",IF(F2="Recebido",E2-D2,TODAY()-D2))</f>
         <v>20</v>
       </c>
-      <c r="H2" s="27">
-        <f t="shared" ref="H2:H65" si="3">IF(OR(B2="",C2=""),"",C2-B2)</f>
+      <c r="I2" s="27">
+        <f t="shared" ref="I2:I68" si="3">IF(OR(C2="",D2=""),"",D2-C2)</f>
         <v>2</v>
       </c>
-      <c r="I2" s="27">
-        <f t="shared" ref="I2:I65" si="4">IF(OR(C2="",D2=""),"",D2-C2)</f>
+      <c r="J2" s="27">
+        <f t="shared" ref="J2:J68" si="4">IF(OR(D2="",E2=""),"",E2-D2)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="23">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
         <v>34</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="25"/>
+      <c r="C3" s="26">
         <v>46030</v>
       </c>
-      <c r="C3" s="24">
+      <c r="D3" s="26">
         <v>46038</v>
       </c>
-      <c r="D3" s="24">
+      <c r="E3" s="26">
         <v>46065</v>
       </c>
-      <c r="E3" s="23" t="str">
+      <c r="F3" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Recebido</v>
       </c>
-      <c r="F3" s="27">
+      <c r="G3" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
-      <c r="G3" s="27">
+      <c r="H3" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>27</v>
       </c>
-      <c r="H3" s="27">
+      <c r="I3" s="27">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="I3" s="27">
+      <c r="J3" s="27">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="23">
-        <v>35</v>
-      </c>
-      <c r="B4" s="24">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="26">
         <v>46049</v>
       </c>
-      <c r="C4" s="24">
+      <c r="D4" s="26">
         <v>46051</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="23" t="str">
+      <c r="E4" s="26"/>
+      <c r="F4" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="F4" s="27">
+      <c r="G4" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="G4" s="27">
+      <c r="H4" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>26</v>
       </c>
-      <c r="H4" s="27">
+      <c r="I4" s="27">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="I4" s="27" t="str">
+      <c r="J4" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="23">
-        <v>36</v>
-      </c>
-      <c r="B5" s="24">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="26">
         <v>46049</v>
       </c>
-      <c r="C5" s="24">
-        <v>46052</v>
-      </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="23" t="str">
+      <c r="D5" s="26">
+        <v>46051</v>
+      </c>
+      <c r="E5" s="26"/>
+      <c r="F5" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="F5" s="27">
+      <c r="G5" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="G5" s="27">
+      <c r="H5" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="I5" s="27">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="J5" s="27" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="26">
+        <v>46049</v>
+      </c>
+      <c r="D6" s="26">
+        <v>46052</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>Em trânsito</v>
+      </c>
+      <c r="G6" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="H6" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>25</v>
       </c>
-      <c r="H5" s="27">
+      <c r="I6" s="27">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I5" s="27" t="str">
+      <c r="J6" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="23">
-        <v>37</v>
-      </c>
-      <c r="B6" s="24">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="26">
         <v>46049</v>
       </c>
-      <c r="C6" s="24">
+      <c r="D7" s="26">
         <v>46052</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="23" t="str">
+      <c r="E7" s="26"/>
+      <c r="F7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="F6" s="27">
+      <c r="G7" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="G6" s="27">
+      <c r="H7" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>25</v>
       </c>
-      <c r="H6" s="27">
+      <c r="I7" s="27">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I6" s="27" t="str">
+      <c r="J7" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
-        <v>38</v>
-      </c>
-      <c r="B7" s="24">
-        <v>46051</v>
-      </c>
-      <c r="C7" s="24">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>37</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="26">
+        <v>46049</v>
+      </c>
+      <c r="D8" s="26">
         <v>46052</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="23" t="str">
+      <c r="E8" s="26"/>
+      <c r="F8" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="F7" s="27">
+      <c r="G8" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="H8" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="I8" s="27">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J8" s="27" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="26">
+        <v>46051</v>
+      </c>
+      <c r="D9" s="26">
+        <v>46052</v>
+      </c>
+      <c r="E9" s="26"/>
+      <c r="F9" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>Em trânsito</v>
+      </c>
+      <c r="G9" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>26</v>
       </c>
-      <c r="G7" s="27">
+      <c r="H9" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>25</v>
       </c>
-      <c r="H7" s="27">
+      <c r="I9" s="27">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="I7" s="27" t="str">
+      <c r="J9" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="23">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="26">
+        <v>46051</v>
+      </c>
+      <c r="D10" s="26">
+        <v>46052</v>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>Em trânsito</v>
+      </c>
+      <c r="G10" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="H10" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="I10" s="27">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J10" s="27" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
         <v>39</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B11" s="25"/>
+      <c r="C11" s="26">
         <v>46056</v>
       </c>
-      <c r="C8" s="24">
+      <c r="D11" s="26">
         <v>46062</v>
       </c>
-      <c r="D8" s="24">
+      <c r="E11" s="26">
         <v>46073</v>
       </c>
-      <c r="E8" s="23" t="str">
+      <c r="F11" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Recebido</v>
       </c>
-      <c r="F8" s="27">
+      <c r="G11" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>17</v>
       </c>
-      <c r="G8" s="27">
+      <c r="H11" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>11</v>
       </c>
-      <c r="H8" s="27">
+      <c r="I11" s="27">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="I8" s="27">
+      <c r="J11" s="27">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="F9" s="29" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="G9" s="29" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="H9" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I9" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="F10" s="29" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="G10" s="29" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="H10" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I10" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="F11" s="29" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="G11" s="29" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="H11" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I11" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="28"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
-      <c r="F12" s="29" t="str">
+      <c r="E12" s="28"/>
+      <c r="G12" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G12" s="29" t="str">
+      <c r="H12" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H12" s="29" t="str">
+      <c r="I12" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I12" s="29" t="str">
+      <c r="J12" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="28"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
-      <c r="F13" s="29" t="str">
+      <c r="E13" s="28"/>
+      <c r="G13" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G13" s="29" t="str">
+      <c r="H13" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H13" s="29" t="str">
+      <c r="I13" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I13" s="29" t="str">
+      <c r="J13" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="28"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
-      <c r="F14" s="29" t="str">
+      <c r="E14" s="28"/>
+      <c r="G14" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G14" s="29" t="str">
+      <c r="H14" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H14" s="29" t="str">
+      <c r="I14" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I14" s="29" t="str">
+      <c r="J14" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="28"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
-      <c r="F15" s="29" t="str">
+      <c r="E15" s="28"/>
+      <c r="G15" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G15" s="29" t="str">
+      <c r="H15" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H15" s="29" t="str">
+      <c r="I15" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I15" s="29" t="str">
+      <c r="J15" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="28"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
-      <c r="F16" s="29" t="str">
+      <c r="E16" s="28"/>
+      <c r="G16" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G16" s="29" t="str">
+      <c r="H16" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H16" s="29" t="str">
+      <c r="I16" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I16" s="29" t="str">
+      <c r="J16" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="28"/>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
-      <c r="F17" s="29" t="str">
+      <c r="E17" s="28"/>
+      <c r="G17" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G17" s="29" t="str">
+      <c r="H17" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H17" s="29" t="str">
+      <c r="I17" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I17" s="29" t="str">
+      <c r="J17" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="28"/>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
-      <c r="F18" s="29" t="str">
+      <c r="E18" s="28"/>
+      <c r="G18" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G18" s="29" t="str">
+      <c r="H18" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H18" s="29" t="str">
+      <c r="I18" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I18" s="29" t="str">
+      <c r="J18" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="28"/>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
-      <c r="F19" s="29" t="str">
+      <c r="E19" s="28"/>
+      <c r="G19" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G19" s="29" t="str">
+      <c r="H19" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H19" s="29" t="str">
+      <c r="I19" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I19" s="29" t="str">
+      <c r="J19" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="28"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="28"/>
       <c r="D20" s="28"/>
-      <c r="F20" s="29" t="str">
+      <c r="E20" s="28"/>
+      <c r="G20" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G20" s="29" t="str">
+      <c r="H20" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H20" s="29" t="str">
+      <c r="I20" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I20" s="29" t="str">
+      <c r="J20" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="28"/>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
-      <c r="F21" s="29" t="str">
+      <c r="E21" s="28"/>
+      <c r="G21" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G21" s="29" t="str">
+      <c r="H21" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H21" s="29" t="str">
+      <c r="I21" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I21" s="29" t="str">
+      <c r="J21" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="28"/>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="28"/>
       <c r="D22" s="28"/>
-      <c r="F22" s="29" t="str">
+      <c r="E22" s="28"/>
+      <c r="G22" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G22" s="29" t="str">
+      <c r="H22" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H22" s="29" t="str">
+      <c r="I22" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I22" s="29" t="str">
+      <c r="J22" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="28"/>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
-      <c r="F23" s="29" t="str">
+      <c r="E23" s="28"/>
+      <c r="G23" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G23" s="29" t="str">
+      <c r="H23" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H23" s="29" t="str">
+      <c r="I23" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I23" s="29" t="str">
+      <c r="J23" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="28"/>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
-      <c r="F24" s="29" t="str">
+      <c r="E24" s="28"/>
+      <c r="G24" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G24" s="29" t="str">
+      <c r="H24" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H24" s="29" t="str">
+      <c r="I24" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I24" s="29" t="str">
+      <c r="J24" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="28"/>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
-      <c r="F25" s="29" t="str">
+      <c r="E25" s="28"/>
+      <c r="G25" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G25" s="29" t="str">
+      <c r="H25" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H25" s="29" t="str">
+      <c r="I25" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I25" s="29" t="str">
+      <c r="J25" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="28"/>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C26" s="28"/>
       <c r="D26" s="28"/>
-      <c r="F26" s="29" t="str">
+      <c r="E26" s="28"/>
+      <c r="G26" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G26" s="29" t="str">
+      <c r="H26" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H26" s="29" t="str">
+      <c r="I26" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I26" s="29" t="str">
+      <c r="J26" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="28"/>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
-      <c r="F27" s="29" t="str">
+      <c r="E27" s="28"/>
+      <c r="G27" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G27" s="29" t="str">
+      <c r="H27" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H27" s="29" t="str">
+      <c r="I27" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I27" s="29" t="str">
+      <c r="J27" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="28"/>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C28" s="28"/>
       <c r="D28" s="28"/>
-      <c r="F28" s="29" t="str">
+      <c r="E28" s="28"/>
+      <c r="G28" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G28" s="29" t="str">
+      <c r="H28" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H28" s="29" t="str">
+      <c r="I28" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I28" s="29" t="str">
+      <c r="J28" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="28"/>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
-      <c r="F29" s="29" t="str">
+      <c r="E29" s="28"/>
+      <c r="G29" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G29" s="29" t="str">
+      <c r="H29" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H29" s="29" t="str">
+      <c r="I29" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I29" s="29" t="str">
+      <c r="J29" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="28"/>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
-      <c r="F30" s="29" t="str">
+      <c r="E30" s="28"/>
+      <c r="G30" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G30" s="29" t="str">
+      <c r="H30" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H30" s="29" t="str">
+      <c r="I30" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I30" s="29" t="str">
+      <c r="J30" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="28"/>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
-      <c r="F31" s="29" t="str">
+      <c r="E31" s="28"/>
+      <c r="G31" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G31" s="29" t="str">
+      <c r="H31" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H31" s="29" t="str">
+      <c r="I31" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I31" s="29" t="str">
+      <c r="J31" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="28"/>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C32" s="28"/>
       <c r="D32" s="28"/>
-      <c r="F32" s="29" t="str">
+      <c r="E32" s="28"/>
+      <c r="G32" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G32" s="29" t="str">
+      <c r="H32" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H32" s="29" t="str">
+      <c r="I32" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I32" s="29" t="str">
+      <c r="J32" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="28"/>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
-      <c r="F33" s="29" t="str">
+      <c r="E33" s="28"/>
+      <c r="G33" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G33" s="29" t="str">
+      <c r="H33" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H33" s="29" t="str">
+      <c r="I33" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I33" s="29" t="str">
+      <c r="J33" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="28"/>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
-      <c r="F34" s="29" t="str">
+      <c r="E34" s="28"/>
+      <c r="G34" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G34" s="29" t="str">
+      <c r="H34" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H34" s="29" t="str">
+      <c r="I34" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I34" s="29" t="str">
+      <c r="J34" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="28"/>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
-      <c r="F35" s="29" t="str">
+      <c r="E35" s="28"/>
+      <c r="G35" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G35" s="29" t="str">
+      <c r="H35" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H35" s="29" t="str">
+      <c r="I35" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I35" s="29" t="str">
+      <c r="J35" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="28"/>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
-      <c r="F36" s="29" t="str">
+      <c r="E36" s="28"/>
+      <c r="G36" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G36" s="29" t="str">
+      <c r="H36" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H36" s="29" t="str">
+      <c r="I36" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I36" s="29" t="str">
+      <c r="J36" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="28"/>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
-      <c r="F37" s="29" t="str">
+      <c r="E37" s="28"/>
+      <c r="G37" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G37" s="29" t="str">
+      <c r="H37" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H37" s="29" t="str">
+      <c r="I37" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I37" s="29" t="str">
+      <c r="J37" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="28"/>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
-      <c r="F38" s="29" t="str">
+      <c r="E38" s="28"/>
+      <c r="G38" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="29" t="str">
+      <c r="H38" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H38" s="29" t="str">
+      <c r="I38" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I38" s="29" t="str">
+      <c r="J38" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="28"/>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
-      <c r="F39" s="29" t="str">
+      <c r="E39" s="28"/>
+      <c r="G39" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="29" t="str">
+      <c r="H39" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H39" s="29" t="str">
+      <c r="I39" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I39" s="29" t="str">
+      <c r="J39" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="28"/>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
-      <c r="F40" s="29" t="str">
+      <c r="E40" s="28"/>
+      <c r="G40" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="29" t="str">
+      <c r="H40" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H40" s="29" t="str">
+      <c r="I40" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I40" s="29" t="str">
+      <c r="J40" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="28"/>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C41" s="28"/>
       <c r="D41" s="28"/>
-      <c r="F41" s="29" t="str">
+      <c r="E41" s="28"/>
+      <c r="G41" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="29" t="str">
+      <c r="H41" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H41" s="29" t="str">
+      <c r="I41" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I41" s="29" t="str">
+      <c r="J41" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="28"/>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C42" s="28"/>
       <c r="D42" s="28"/>
-      <c r="F42" s="29" t="str">
+      <c r="E42" s="28"/>
+      <c r="G42" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="29" t="str">
+      <c r="H42" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H42" s="29" t="str">
+      <c r="I42" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I42" s="29" t="str">
+      <c r="J42" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B43" s="28"/>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C43" s="28"/>
       <c r="D43" s="28"/>
-      <c r="F43" s="29" t="str">
+      <c r="E43" s="28"/>
+      <c r="G43" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="29" t="str">
+      <c r="H43" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H43" s="29" t="str">
+      <c r="I43" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I43" s="29" t="str">
+      <c r="J43" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="28"/>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C44" s="28"/>
       <c r="D44" s="28"/>
-      <c r="F44" s="29" t="str">
+      <c r="E44" s="28"/>
+      <c r="G44" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="29" t="str">
+      <c r="H44" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H44" s="29" t="str">
+      <c r="I44" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I44" s="29" t="str">
+      <c r="J44" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="28"/>
+    <row r="45" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C45" s="28"/>
       <c r="D45" s="28"/>
-      <c r="F45" s="29" t="str">
+      <c r="E45" s="28"/>
+      <c r="G45" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G45" s="29" t="str">
+      <c r="H45" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H45" s="29" t="str">
+      <c r="I45" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I45" s="29" t="str">
+      <c r="J45" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B46" s="28"/>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C46" s="28"/>
       <c r="D46" s="28"/>
-      <c r="F46" s="29" t="str">
+      <c r="E46" s="28"/>
+      <c r="G46" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G46" s="29" t="str">
+      <c r="H46" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H46" s="29" t="str">
+      <c r="I46" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I46" s="29" t="str">
+      <c r="J46" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="28"/>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C47" s="28"/>
       <c r="D47" s="28"/>
-      <c r="F47" s="29" t="str">
+      <c r="E47" s="28"/>
+      <c r="G47" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G47" s="29" t="str">
+      <c r="H47" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H47" s="29" t="str">
+      <c r="I47" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I47" s="29" t="str">
+      <c r="J47" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="28"/>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C48" s="28"/>
       <c r="D48" s="28"/>
-      <c r="F48" s="29" t="str">
+      <c r="E48" s="28"/>
+      <c r="G48" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G48" s="29" t="str">
+      <c r="H48" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H48" s="29" t="str">
+      <c r="I48" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I48" s="29" t="str">
+      <c r="J48" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B49" s="28"/>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
-      <c r="F49" s="29" t="str">
+      <c r="E49" s="28"/>
+      <c r="G49" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G49" s="29" t="str">
+      <c r="H49" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H49" s="29" t="str">
+      <c r="I49" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I49" s="29" t="str">
+      <c r="J49" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="28"/>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C50" s="28"/>
       <c r="D50" s="28"/>
-      <c r="F50" s="29" t="str">
+      <c r="E50" s="28"/>
+      <c r="G50" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G50" s="29" t="str">
+      <c r="H50" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H50" s="29" t="str">
+      <c r="I50" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I50" s="29" t="str">
+      <c r="J50" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="28"/>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C51" s="28"/>
       <c r="D51" s="28"/>
-      <c r="F51" s="29" t="str">
+      <c r="E51" s="28"/>
+      <c r="G51" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G51" s="29" t="str">
+      <c r="H51" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H51" s="29" t="str">
+      <c r="I51" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I51" s="29" t="str">
+      <c r="J51" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="28"/>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C52" s="28"/>
       <c r="D52" s="28"/>
-      <c r="F52" s="29" t="str">
+      <c r="E52" s="28"/>
+      <c r="G52" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G52" s="29" t="str">
+      <c r="H52" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H52" s="29" t="str">
+      <c r="I52" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I52" s="29" t="str">
+      <c r="J52" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="28"/>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C53" s="28"/>
       <c r="D53" s="28"/>
-      <c r="F53" s="29" t="str">
+      <c r="E53" s="28"/>
+      <c r="G53" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G53" s="29" t="str">
+      <c r="H53" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H53" s="29" t="str">
+      <c r="I53" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I53" s="29" t="str">
+      <c r="J53" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B54" s="28"/>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C54" s="28"/>
       <c r="D54" s="28"/>
-      <c r="F54" s="29" t="str">
+      <c r="E54" s="28"/>
+      <c r="G54" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G54" s="29" t="str">
+      <c r="H54" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H54" s="29" t="str">
+      <c r="I54" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I54" s="29" t="str">
+      <c r="J54" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B55" s="28"/>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C55" s="28"/>
       <c r="D55" s="28"/>
-      <c r="F55" s="29" t="str">
+      <c r="E55" s="28"/>
+      <c r="G55" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G55" s="29" t="str">
+      <c r="H55" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H55" s="29" t="str">
+      <c r="I55" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I55" s="29" t="str">
+      <c r="J55" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B56" s="28"/>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C56" s="28"/>
       <c r="D56" s="28"/>
-      <c r="F56" s="29" t="str">
+      <c r="E56" s="28"/>
+      <c r="G56" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G56" s="29" t="str">
+      <c r="H56" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H56" s="29" t="str">
+      <c r="I56" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I56" s="29" t="str">
+      <c r="J56" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B57" s="28"/>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C57" s="28"/>
       <c r="D57" s="28"/>
-      <c r="F57" s="29" t="str">
+      <c r="E57" s="28"/>
+      <c r="G57" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G57" s="29" t="str">
+      <c r="H57" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H57" s="29" t="str">
+      <c r="I57" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I57" s="29" t="str">
+      <c r="J57" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B58" s="28"/>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C58" s="28"/>
       <c r="D58" s="28"/>
-      <c r="F58" s="29" t="str">
+      <c r="E58" s="28"/>
+      <c r="G58" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G58" s="29" t="str">
+      <c r="H58" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H58" s="29" t="str">
+      <c r="I58" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I58" s="29" t="str">
+      <c r="J58" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B59" s="28"/>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C59" s="28"/>
       <c r="D59" s="28"/>
-      <c r="F59" s="29" t="str">
+      <c r="E59" s="28"/>
+      <c r="G59" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G59" s="29" t="str">
+      <c r="H59" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H59" s="29" t="str">
+      <c r="I59" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I59" s="29" t="str">
+      <c r="J59" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B60" s="28"/>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C60" s="28"/>
       <c r="D60" s="28"/>
-      <c r="F60" s="29" t="str">
+      <c r="E60" s="28"/>
+      <c r="G60" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G60" s="29" t="str">
+      <c r="H60" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H60" s="29" t="str">
+      <c r="I60" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I60" s="29" t="str">
+      <c r="J60" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B61" s="28"/>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C61" s="28"/>
       <c r="D61" s="28"/>
-      <c r="F61" s="29" t="str">
+      <c r="E61" s="28"/>
+      <c r="G61" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G61" s="29" t="str">
+      <c r="H61" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H61" s="29" t="str">
+      <c r="I61" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I61" s="29" t="str">
+      <c r="J61" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B62" s="28"/>
+    <row r="62" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C62" s="28"/>
       <c r="D62" s="28"/>
-      <c r="F62" s="29" t="str">
+      <c r="E62" s="28"/>
+      <c r="G62" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G62" s="29" t="str">
+      <c r="H62" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H62" s="29" t="str">
+      <c r="I62" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I62" s="29" t="str">
+      <c r="J62" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B63" s="28"/>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C63" s="28"/>
       <c r="D63" s="28"/>
-      <c r="F63" s="29" t="str">
+      <c r="E63" s="28"/>
+      <c r="G63" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G63" s="29" t="str">
+      <c r="H63" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H63" s="29" t="str">
+      <c r="I63" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I63" s="29" t="str">
+      <c r="J63" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B64" s="28"/>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C64" s="28"/>
       <c r="D64" s="28"/>
-      <c r="F64" s="29" t="str">
+      <c r="E64" s="28"/>
+      <c r="G64" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G64" s="29" t="str">
+      <c r="H64" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H64" s="29" t="str">
+      <c r="I64" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I64" s="29" t="str">
+      <c r="J64" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B65" s="28"/>
+    <row r="65" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C65" s="28"/>
       <c r="D65" s="28"/>
-      <c r="F65" s="29" t="str">
+      <c r="E65" s="28"/>
+      <c r="G65" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="G65" s="29" t="str">
+      <c r="H65" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="H65" s="29" t="str">
+      <c r="I65" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I65" s="29" t="str">
+      <c r="J65" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B66" s="28"/>
+    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C66" s="28"/>
       <c r="D66" s="28"/>
-      <c r="F66" s="29" t="str">
-        <f t="shared" ref="F66:F129" ca="1" si="5">IF(B66="","",IF(E66="Recebido",D66-B66,TODAY()-B66))</f>
-        <v/>
-      </c>
+      <c r="E66" s="28"/>
       <c r="G66" s="29" t="str">
-        <f t="shared" ref="G66:G129" ca="1" si="6">IF(C66="","",IF(E66="Recebido",D66-C66,TODAY()-C66))</f>
+        <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="H66" s="29" t="str">
-        <f t="shared" ref="H66:H129" si="7">IF(OR(B66="",C66=""),"",C66-B66)</f>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="I66" s="29" t="str">
-        <f t="shared" ref="I66:I129" si="8">IF(OR(C66="",D66=""),"",D66-C66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B67" s="28"/>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="J66" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C67" s="28"/>
       <c r="D67" s="28"/>
-      <c r="F67" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
+      <c r="E67" s="28"/>
       <c r="G67" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="H67" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="I67" s="29" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B68" s="28"/>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="J67" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C68" s="28"/>
       <c r="D68" s="28"/>
-      <c r="F68" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
+      <c r="E68" s="28"/>
       <c r="G68" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="H68" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="I68" s="29" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B69" s="28"/>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="J68" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C69" s="28"/>
       <c r="D69" s="28"/>
-      <c r="F69" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
+      <c r="E69" s="28"/>
       <c r="G69" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ref="G69:G132" ca="1" si="5">IF(C69="","",IF(F69="Recebido",E69-C69,TODAY()-C69))</f>
         <v/>
       </c>
       <c r="H69" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="H69:H132" ca="1" si="6">IF(D69="","",IF(F69="Recebido",E69-D69,TODAY()-D69))</f>
         <v/>
       </c>
       <c r="I69" s="29" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B70" s="28"/>
+        <f t="shared" ref="I69:I132" si="7">IF(OR(C69="",D69=""),"",D69-C69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="29" t="str">
+        <f t="shared" ref="J69:J132" si="8">IF(OR(D69="",E69=""),"",E69-D69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C70" s="28"/>
       <c r="D70" s="28"/>
-      <c r="F70" s="29" t="str">
+      <c r="E70" s="28"/>
+      <c r="G70" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G70" s="29" t="str">
+      <c r="H70" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H70" s="29" t="str">
+      <c r="I70" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I70" s="29" t="str">
+      <c r="J70" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B71" s="28"/>
+    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C71" s="28"/>
       <c r="D71" s="28"/>
-      <c r="F71" s="29" t="str">
+      <c r="E71" s="28"/>
+      <c r="G71" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G71" s="29" t="str">
+      <c r="H71" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H71" s="29" t="str">
+      <c r="I71" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I71" s="29" t="str">
+      <c r="J71" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B72" s="28"/>
+    <row r="72" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C72" s="28"/>
       <c r="D72" s="28"/>
-      <c r="F72" s="29" t="str">
+      <c r="E72" s="28"/>
+      <c r="G72" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G72" s="29" t="str">
+      <c r="H72" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H72" s="29" t="str">
+      <c r="I72" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I72" s="29" t="str">
+      <c r="J72" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B73" s="28"/>
+    <row r="73" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C73" s="28"/>
       <c r="D73" s="28"/>
-      <c r="F73" s="29" t="str">
+      <c r="E73" s="28"/>
+      <c r="G73" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G73" s="29" t="str">
+      <c r="H73" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H73" s="29" t="str">
+      <c r="I73" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I73" s="29" t="str">
+      <c r="J73" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B74" s="28"/>
+    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C74" s="28"/>
       <c r="D74" s="28"/>
-      <c r="F74" s="29" t="str">
+      <c r="E74" s="28"/>
+      <c r="G74" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G74" s="29" t="str">
+      <c r="H74" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H74" s="29" t="str">
+      <c r="I74" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I74" s="29" t="str">
+      <c r="J74" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B75" s="28"/>
+    <row r="75" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C75" s="28"/>
       <c r="D75" s="28"/>
-      <c r="F75" s="29" t="str">
+      <c r="E75" s="28"/>
+      <c r="G75" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G75" s="29" t="str">
+      <c r="H75" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H75" s="29" t="str">
+      <c r="I75" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I75" s="29" t="str">
+      <c r="J75" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B76" s="28"/>
+    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C76" s="28"/>
       <c r="D76" s="28"/>
-      <c r="F76" s="29" t="str">
+      <c r="E76" s="28"/>
+      <c r="G76" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G76" s="29" t="str">
+      <c r="H76" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H76" s="29" t="str">
+      <c r="I76" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I76" s="29" t="str">
+      <c r="J76" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B77" s="28"/>
+    <row r="77" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C77" s="28"/>
       <c r="D77" s="28"/>
-      <c r="F77" s="29" t="str">
+      <c r="E77" s="28"/>
+      <c r="G77" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G77" s="29" t="str">
+      <c r="H77" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H77" s="29" t="str">
+      <c r="I77" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I77" s="29" t="str">
+      <c r="J77" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B78" s="28"/>
+    <row r="78" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C78" s="28"/>
       <c r="D78" s="28"/>
-      <c r="F78" s="29" t="str">
+      <c r="E78" s="28"/>
+      <c r="G78" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G78" s="29" t="str">
+      <c r="H78" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H78" s="29" t="str">
+      <c r="I78" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I78" s="29" t="str">
+      <c r="J78" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B79" s="28"/>
+    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C79" s="28"/>
       <c r="D79" s="28"/>
-      <c r="F79" s="29" t="str">
+      <c r="E79" s="28"/>
+      <c r="G79" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G79" s="29" t="str">
+      <c r="H79" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H79" s="29" t="str">
+      <c r="I79" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I79" s="29" t="str">
+      <c r="J79" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B80" s="28"/>
+    <row r="80" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C80" s="28"/>
       <c r="D80" s="28"/>
-      <c r="F80" s="29" t="str">
+      <c r="E80" s="28"/>
+      <c r="G80" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G80" s="29" t="str">
+      <c r="H80" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H80" s="29" t="str">
+      <c r="I80" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I80" s="29" t="str">
+      <c r="J80" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B81" s="28"/>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C81" s="28"/>
       <c r="D81" s="28"/>
-      <c r="F81" s="29" t="str">
+      <c r="E81" s="28"/>
+      <c r="G81" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G81" s="29" t="str">
+      <c r="H81" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H81" s="29" t="str">
+      <c r="I81" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I81" s="29" t="str">
+      <c r="J81" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B82" s="28"/>
+    <row r="82" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C82" s="28"/>
       <c r="D82" s="28"/>
-      <c r="F82" s="29" t="str">
+      <c r="E82" s="28"/>
+      <c r="G82" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G82" s="29" t="str">
+      <c r="H82" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H82" s="29" t="str">
+      <c r="I82" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I82" s="29" t="str">
+      <c r="J82" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B83" s="28"/>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C83" s="28"/>
       <c r="D83" s="28"/>
-      <c r="F83" s="29" t="str">
+      <c r="E83" s="28"/>
+      <c r="G83" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G83" s="29" t="str">
+      <c r="H83" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H83" s="29" t="str">
+      <c r="I83" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I83" s="29" t="str">
+      <c r="J83" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B84" s="28"/>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C84" s="28"/>
       <c r="D84" s="28"/>
-      <c r="F84" s="29" t="str">
+      <c r="E84" s="28"/>
+      <c r="G84" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G84" s="29" t="str">
+      <c r="H84" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H84" s="29" t="str">
+      <c r="I84" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I84" s="29" t="str">
+      <c r="J84" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B85" s="28"/>
+    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C85" s="28"/>
       <c r="D85" s="28"/>
-      <c r="F85" s="29" t="str">
+      <c r="E85" s="28"/>
+      <c r="G85" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G85" s="29" t="str">
+      <c r="H85" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H85" s="29" t="str">
+      <c r="I85" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I85" s="29" t="str">
+      <c r="J85" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B86" s="28"/>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C86" s="28"/>
       <c r="D86" s="28"/>
-      <c r="F86" s="29" t="str">
+      <c r="E86" s="28"/>
+      <c r="G86" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G86" s="29" t="str">
+      <c r="H86" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H86" s="29" t="str">
+      <c r="I86" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I86" s="29" t="str">
+      <c r="J86" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B87" s="28"/>
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C87" s="28"/>
       <c r="D87" s="28"/>
-      <c r="F87" s="29" t="str">
+      <c r="E87" s="28"/>
+      <c r="G87" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G87" s="29" t="str">
+      <c r="H87" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H87" s="29" t="str">
+      <c r="I87" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I87" s="29" t="str">
+      <c r="J87" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B88" s="28"/>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C88" s="28"/>
       <c r="D88" s="28"/>
-      <c r="F88" s="29" t="str">
+      <c r="E88" s="28"/>
+      <c r="G88" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G88" s="29" t="str">
+      <c r="H88" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H88" s="29" t="str">
+      <c r="I88" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I88" s="29" t="str">
+      <c r="J88" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B89" s="28"/>
+    <row r="89" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C89" s="28"/>
       <c r="D89" s="28"/>
-      <c r="F89" s="29" t="str">
+      <c r="E89" s="28"/>
+      <c r="G89" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G89" s="29" t="str">
+      <c r="H89" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H89" s="29" t="str">
+      <c r="I89" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I89" s="29" t="str">
+      <c r="J89" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B90" s="28"/>
+    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C90" s="28"/>
       <c r="D90" s="28"/>
-      <c r="F90" s="29" t="str">
+      <c r="E90" s="28"/>
+      <c r="G90" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G90" s="29" t="str">
+      <c r="H90" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H90" s="29" t="str">
+      <c r="I90" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I90" s="29" t="str">
+      <c r="J90" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B91" s="28"/>
+    <row r="91" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C91" s="28"/>
       <c r="D91" s="28"/>
-      <c r="F91" s="29" t="str">
+      <c r="E91" s="28"/>
+      <c r="G91" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G91" s="29" t="str">
+      <c r="H91" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H91" s="29" t="str">
+      <c r="I91" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I91" s="29" t="str">
+      <c r="J91" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B92" s="28"/>
+    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C92" s="28"/>
       <c r="D92" s="28"/>
-      <c r="F92" s="29" t="str">
+      <c r="E92" s="28"/>
+      <c r="G92" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G92" s="29" t="str">
+      <c r="H92" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H92" s="29" t="str">
+      <c r="I92" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I92" s="29" t="str">
+      <c r="J92" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B93" s="28"/>
+    <row r="93" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C93" s="28"/>
       <c r="D93" s="28"/>
-      <c r="F93" s="29" t="str">
+      <c r="E93" s="28"/>
+      <c r="G93" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G93" s="29" t="str">
+      <c r="H93" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H93" s="29" t="str">
+      <c r="I93" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I93" s="29" t="str">
+      <c r="J93" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B94" s="28"/>
+    <row r="94" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C94" s="28"/>
       <c r="D94" s="28"/>
-      <c r="F94" s="29" t="str">
+      <c r="E94" s="28"/>
+      <c r="G94" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G94" s="29" t="str">
+      <c r="H94" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H94" s="29" t="str">
+      <c r="I94" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I94" s="29" t="str">
+      <c r="J94" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B95" s="28"/>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C95" s="28"/>
       <c r="D95" s="28"/>
-      <c r="F95" s="29" t="str">
+      <c r="E95" s="28"/>
+      <c r="G95" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G95" s="29" t="str">
+      <c r="H95" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H95" s="29" t="str">
+      <c r="I95" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I95" s="29" t="str">
+      <c r="J95" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B96" s="28"/>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C96" s="28"/>
       <c r="D96" s="28"/>
-      <c r="F96" s="29" t="str">
+      <c r="E96" s="28"/>
+      <c r="G96" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G96" s="29" t="str">
+      <c r="H96" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H96" s="29" t="str">
+      <c r="I96" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I96" s="29" t="str">
+      <c r="J96" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" s="28"/>
+    <row r="97" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C97" s="28"/>
       <c r="D97" s="28"/>
-      <c r="F97" s="29" t="str">
+      <c r="E97" s="28"/>
+      <c r="G97" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G97" s="29" t="str">
+      <c r="H97" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H97" s="29" t="str">
+      <c r="I97" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I97" s="29" t="str">
+      <c r="J97" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" s="28"/>
+    <row r="98" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C98" s="28"/>
       <c r="D98" s="28"/>
-      <c r="F98" s="29" t="str">
+      <c r="E98" s="28"/>
+      <c r="G98" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G98" s="29" t="str">
+      <c r="H98" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H98" s="29" t="str">
+      <c r="I98" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I98" s="29" t="str">
+      <c r="J98" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B99" s="28"/>
+    <row r="99" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C99" s="28"/>
       <c r="D99" s="28"/>
-      <c r="F99" s="29" t="str">
+      <c r="E99" s="28"/>
+      <c r="G99" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G99" s="29" t="str">
+      <c r="H99" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H99" s="29" t="str">
+      <c r="I99" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I99" s="29" t="str">
+      <c r="J99" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B100" s="28"/>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C100" s="28"/>
       <c r="D100" s="28"/>
-      <c r="F100" s="29" t="str">
+      <c r="E100" s="28"/>
+      <c r="G100" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G100" s="29" t="str">
+      <c r="H100" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H100" s="29" t="str">
+      <c r="I100" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I100" s="29" t="str">
+      <c r="J100" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B101" s="28"/>
+    <row r="101" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C101" s="28"/>
       <c r="D101" s="28"/>
-      <c r="F101" s="29" t="str">
+      <c r="E101" s="28"/>
+      <c r="G101" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G101" s="29" t="str">
+      <c r="H101" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H101" s="29" t="str">
+      <c r="I101" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I101" s="29" t="str">
+      <c r="J101" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B102" s="28"/>
+    <row r="102" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C102" s="28"/>
       <c r="D102" s="28"/>
-      <c r="F102" s="29" t="str">
+      <c r="E102" s="28"/>
+      <c r="G102" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G102" s="29" t="str">
+      <c r="H102" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H102" s="29" t="str">
+      <c r="I102" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I102" s="29" t="str">
+      <c r="J102" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B103" s="28"/>
+    <row r="103" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C103" s="28"/>
       <c r="D103" s="28"/>
-      <c r="F103" s="29" t="str">
+      <c r="E103" s="28"/>
+      <c r="G103" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G103" s="29" t="str">
+      <c r="H103" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H103" s="29" t="str">
+      <c r="I103" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I103" s="29" t="str">
+      <c r="J103" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B104" s="28"/>
+    <row r="104" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C104" s="28"/>
       <c r="D104" s="28"/>
-      <c r="F104" s="29" t="str">
+      <c r="E104" s="28"/>
+      <c r="G104" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G104" s="29" t="str">
+      <c r="H104" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H104" s="29" t="str">
+      <c r="I104" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I104" s="29" t="str">
+      <c r="J104" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B105" s="28"/>
+    <row r="105" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C105" s="28"/>
       <c r="D105" s="28"/>
-      <c r="F105" s="29" t="str">
+      <c r="E105" s="28"/>
+      <c r="G105" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G105" s="29" t="str">
+      <c r="H105" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H105" s="29" t="str">
+      <c r="I105" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I105" s="29" t="str">
+      <c r="J105" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B106" s="28"/>
+    <row r="106" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C106" s="28"/>
       <c r="D106" s="28"/>
-      <c r="F106" s="29" t="str">
+      <c r="E106" s="28"/>
+      <c r="G106" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G106" s="29" t="str">
+      <c r="H106" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H106" s="29" t="str">
+      <c r="I106" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I106" s="29" t="str">
+      <c r="J106" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B107" s="28"/>
+    <row r="107" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C107" s="28"/>
       <c r="D107" s="28"/>
-      <c r="F107" s="29" t="str">
+      <c r="E107" s="28"/>
+      <c r="G107" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G107" s="29" t="str">
+      <c r="H107" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H107" s="29" t="str">
+      <c r="I107" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I107" s="29" t="str">
+      <c r="J107" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B108" s="28"/>
+    <row r="108" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C108" s="28"/>
       <c r="D108" s="28"/>
-      <c r="F108" s="29" t="str">
+      <c r="E108" s="28"/>
+      <c r="G108" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G108" s="29" t="str">
+      <c r="H108" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H108" s="29" t="str">
+      <c r="I108" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I108" s="29" t="str">
+      <c r="J108" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B109" s="28"/>
+    <row r="109" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C109" s="28"/>
       <c r="D109" s="28"/>
-      <c r="F109" s="29" t="str">
+      <c r="E109" s="28"/>
+      <c r="G109" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G109" s="29" t="str">
+      <c r="H109" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H109" s="29" t="str">
+      <c r="I109" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I109" s="29" t="str">
+      <c r="J109" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B110" s="28"/>
+    <row r="110" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C110" s="28"/>
       <c r="D110" s="28"/>
-      <c r="F110" s="29" t="str">
+      <c r="E110" s="28"/>
+      <c r="G110" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G110" s="29" t="str">
+      <c r="H110" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H110" s="29" t="str">
+      <c r="I110" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I110" s="29" t="str">
+      <c r="J110" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B111" s="28"/>
+    <row r="111" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C111" s="28"/>
       <c r="D111" s="28"/>
-      <c r="F111" s="29" t="str">
+      <c r="E111" s="28"/>
+      <c r="G111" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G111" s="29" t="str">
+      <c r="H111" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H111" s="29" t="str">
+      <c r="I111" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I111" s="29" t="str">
+      <c r="J111" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B112" s="28"/>
+    <row r="112" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C112" s="28"/>
       <c r="D112" s="28"/>
-      <c r="F112" s="29" t="str">
+      <c r="E112" s="28"/>
+      <c r="G112" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G112" s="29" t="str">
+      <c r="H112" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H112" s="29" t="str">
+      <c r="I112" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I112" s="29" t="str">
+      <c r="J112" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B113" s="28"/>
+    <row r="113" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C113" s="28"/>
       <c r="D113" s="28"/>
-      <c r="F113" s="29" t="str">
+      <c r="E113" s="28"/>
+      <c r="G113" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G113" s="29" t="str">
+      <c r="H113" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H113" s="29" t="str">
+      <c r="I113" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I113" s="29" t="str">
+      <c r="J113" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B114" s="28"/>
+    <row r="114" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C114" s="28"/>
       <c r="D114" s="28"/>
-      <c r="F114" s="29" t="str">
+      <c r="E114" s="28"/>
+      <c r="G114" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G114" s="29" t="str">
+      <c r="H114" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H114" s="29" t="str">
+      <c r="I114" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I114" s="29" t="str">
+      <c r="J114" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B115" s="28"/>
+    <row r="115" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C115" s="28"/>
       <c r="D115" s="28"/>
-      <c r="F115" s="29" t="str">
+      <c r="E115" s="28"/>
+      <c r="G115" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G115" s="29" t="str">
+      <c r="H115" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H115" s="29" t="str">
+      <c r="I115" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I115" s="29" t="str">
+      <c r="J115" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B116" s="28"/>
+    <row r="116" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C116" s="28"/>
       <c r="D116" s="28"/>
-      <c r="F116" s="29" t="str">
+      <c r="E116" s="28"/>
+      <c r="G116" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G116" s="29" t="str">
+      <c r="H116" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H116" s="29" t="str">
+      <c r="I116" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I116" s="29" t="str">
+      <c r="J116" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B117" s="28"/>
+    <row r="117" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C117" s="28"/>
       <c r="D117" s="28"/>
-      <c r="F117" s="29" t="str">
+      <c r="E117" s="28"/>
+      <c r="G117" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G117" s="29" t="str">
+      <c r="H117" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H117" s="29" t="str">
+      <c r="I117" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I117" s="29" t="str">
+      <c r="J117" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B118" s="28"/>
+    <row r="118" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C118" s="28"/>
       <c r="D118" s="28"/>
-      <c r="F118" s="29" t="str">
+      <c r="E118" s="28"/>
+      <c r="G118" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G118" s="29" t="str">
+      <c r="H118" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H118" s="29" t="str">
+      <c r="I118" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I118" s="29" t="str">
+      <c r="J118" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B119" s="28"/>
+    <row r="119" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C119" s="28"/>
       <c r="D119" s="28"/>
-      <c r="F119" s="29" t="str">
+      <c r="E119" s="28"/>
+      <c r="G119" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G119" s="29" t="str">
+      <c r="H119" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H119" s="29" t="str">
+      <c r="I119" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I119" s="29" t="str">
+      <c r="J119" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B120" s="28"/>
+    <row r="120" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C120" s="28"/>
       <c r="D120" s="28"/>
-      <c r="F120" s="29" t="str">
+      <c r="E120" s="28"/>
+      <c r="G120" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G120" s="29" t="str">
+      <c r="H120" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H120" s="29" t="str">
+      <c r="I120" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I120" s="29" t="str">
+      <c r="J120" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B121" s="28"/>
+    <row r="121" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C121" s="28"/>
       <c r="D121" s="28"/>
-      <c r="F121" s="29" t="str">
+      <c r="E121" s="28"/>
+      <c r="G121" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G121" s="29" t="str">
+      <c r="H121" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H121" s="29" t="str">
+      <c r="I121" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I121" s="29" t="str">
+      <c r="J121" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B122" s="28"/>
+    <row r="122" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C122" s="28"/>
       <c r="D122" s="28"/>
-      <c r="F122" s="29" t="str">
+      <c r="E122" s="28"/>
+      <c r="G122" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G122" s="29" t="str">
+      <c r="H122" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H122" s="29" t="str">
+      <c r="I122" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I122" s="29" t="str">
+      <c r="J122" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B123" s="28"/>
+    <row r="123" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C123" s="28"/>
       <c r="D123" s="28"/>
-      <c r="F123" s="29" t="str">
+      <c r="E123" s="28"/>
+      <c r="G123" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G123" s="29" t="str">
+      <c r="H123" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H123" s="29" t="str">
+      <c r="I123" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I123" s="29" t="str">
+      <c r="J123" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B124" s="28"/>
+    <row r="124" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C124" s="28"/>
       <c r="D124" s="28"/>
-      <c r="F124" s="29" t="str">
+      <c r="E124" s="28"/>
+      <c r="G124" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G124" s="29" t="str">
+      <c r="H124" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H124" s="29" t="str">
+      <c r="I124" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I124" s="29" t="str">
+      <c r="J124" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B125" s="28"/>
+    <row r="125" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C125" s="28"/>
       <c r="D125" s="28"/>
-      <c r="F125" s="29" t="str">
+      <c r="E125" s="28"/>
+      <c r="G125" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G125" s="29" t="str">
+      <c r="H125" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H125" s="29" t="str">
+      <c r="I125" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I125" s="29" t="str">
+      <c r="J125" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B126" s="28"/>
+    <row r="126" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C126" s="28"/>
       <c r="D126" s="28"/>
-      <c r="F126" s="29" t="str">
+      <c r="E126" s="28"/>
+      <c r="G126" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G126" s="29" t="str">
+      <c r="H126" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H126" s="29" t="str">
+      <c r="I126" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I126" s="29" t="str">
+      <c r="J126" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B127" s="28"/>
+    <row r="127" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C127" s="28"/>
       <c r="D127" s="28"/>
-      <c r="F127" s="29" t="str">
+      <c r="E127" s="28"/>
+      <c r="G127" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G127" s="29" t="str">
+      <c r="H127" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H127" s="29" t="str">
+      <c r="I127" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I127" s="29" t="str">
+      <c r="J127" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B128" s="28"/>
+    <row r="128" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C128" s="28"/>
       <c r="D128" s="28"/>
-      <c r="F128" s="29" t="str">
+      <c r="E128" s="28"/>
+      <c r="G128" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G128" s="29" t="str">
+      <c r="H128" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H128" s="29" t="str">
+      <c r="I128" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I128" s="29" t="str">
+      <c r="J128" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B129" s="28"/>
+    <row r="129" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C129" s="28"/>
       <c r="D129" s="28"/>
-      <c r="F129" s="29" t="str">
+      <c r="E129" s="28"/>
+      <c r="G129" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="G129" s="29" t="str">
+      <c r="H129" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="H129" s="29" t="str">
+      <c r="I129" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I129" s="29" t="str">
+      <c r="J129" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B130" s="28"/>
+    <row r="130" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C130" s="28"/>
       <c r="D130" s="28"/>
-      <c r="F130" s="29" t="str">
-        <f t="shared" ref="F130:F193" ca="1" si="9">IF(B130="","",IF(E130="Recebido",D130-B130,TODAY()-B130))</f>
-        <v/>
-      </c>
+      <c r="E130" s="28"/>
       <c r="G130" s="29" t="str">
-        <f t="shared" ref="G130:G193" ca="1" si="10">IF(C130="","",IF(E130="Recebido",D130-C130,TODAY()-C130))</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="H130" s="29" t="str">
-        <f t="shared" ref="H130:H193" si="11">IF(OR(B130="",C130=""),"",C130-B130)</f>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="I130" s="29" t="str">
-        <f t="shared" ref="I130:I193" si="12">IF(OR(C130="",D130=""),"",D130-C130)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B131" s="28"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="J130" s="29" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C131" s="28"/>
       <c r="D131" s="28"/>
-      <c r="F131" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
+      <c r="E131" s="28"/>
       <c r="G131" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="H131" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="I131" s="29" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B132" s="28"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="J131" s="29" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C132" s="28"/>
       <c r="D132" s="28"/>
-      <c r="F132" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
+      <c r="E132" s="28"/>
       <c r="G132" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="H132" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="I132" s="29" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B133" s="28"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="J132" s="29" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C133" s="28"/>
       <c r="D133" s="28"/>
-      <c r="F133" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
+      <c r="E133" s="28"/>
       <c r="G133" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ref="G133:G196" ca="1" si="9">IF(C133="","",IF(F133="Recebido",E133-C133,TODAY()-C133))</f>
         <v/>
       </c>
       <c r="H133" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="H133:H196" ca="1" si="10">IF(D133="","",IF(F133="Recebido",E133-D133,TODAY()-D133))</f>
         <v/>
       </c>
       <c r="I133" s="29" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B134" s="28"/>
+        <f t="shared" ref="I133:I196" si="11">IF(OR(C133="",D133=""),"",D133-C133)</f>
+        <v/>
+      </c>
+      <c r="J133" s="29" t="str">
+        <f t="shared" ref="J133:J196" si="12">IF(OR(D133="",E133=""),"",E133-D133)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C134" s="28"/>
       <c r="D134" s="28"/>
-      <c r="F134" s="29" t="str">
+      <c r="E134" s="28"/>
+      <c r="G134" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G134" s="29" t="str">
+      <c r="H134" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H134" s="29" t="str">
+      <c r="I134" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I134" s="29" t="str">
+      <c r="J134" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B135" s="28"/>
+    <row r="135" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C135" s="28"/>
       <c r="D135" s="28"/>
-      <c r="F135" s="29" t="str">
+      <c r="E135" s="28"/>
+      <c r="G135" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G135" s="29" t="str">
+      <c r="H135" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H135" s="29" t="str">
+      <c r="I135" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I135" s="29" t="str">
+      <c r="J135" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B136" s="28"/>
+    <row r="136" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C136" s="28"/>
       <c r="D136" s="28"/>
-      <c r="F136" s="29" t="str">
+      <c r="E136" s="28"/>
+      <c r="G136" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G136" s="29" t="str">
+      <c r="H136" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H136" s="29" t="str">
+      <c r="I136" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I136" s="29" t="str">
+      <c r="J136" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B137" s="28"/>
+    <row r="137" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C137" s="28"/>
       <c r="D137" s="28"/>
-      <c r="F137" s="29" t="str">
+      <c r="E137" s="28"/>
+      <c r="G137" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G137" s="29" t="str">
+      <c r="H137" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H137" s="29" t="str">
+      <c r="I137" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I137" s="29" t="str">
+      <c r="J137" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B138" s="28"/>
+    <row r="138" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C138" s="28"/>
       <c r="D138" s="28"/>
-      <c r="F138" s="29" t="str">
+      <c r="E138" s="28"/>
+      <c r="G138" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G138" s="29" t="str">
+      <c r="H138" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H138" s="29" t="str">
+      <c r="I138" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I138" s="29" t="str">
+      <c r="J138" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B139" s="28"/>
+    <row r="139" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C139" s="28"/>
       <c r="D139" s="28"/>
-      <c r="F139" s="29" t="str">
+      <c r="E139" s="28"/>
+      <c r="G139" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G139" s="29" t="str">
+      <c r="H139" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H139" s="29" t="str">
+      <c r="I139" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I139" s="29" t="str">
+      <c r="J139" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B140" s="28"/>
+    <row r="140" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C140" s="28"/>
       <c r="D140" s="28"/>
-      <c r="F140" s="29" t="str">
+      <c r="E140" s="28"/>
+      <c r="G140" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G140" s="29" t="str">
+      <c r="H140" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H140" s="29" t="str">
+      <c r="I140" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I140" s="29" t="str">
+      <c r="J140" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B141" s="28"/>
+    <row r="141" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C141" s="28"/>
       <c r="D141" s="28"/>
-      <c r="F141" s="29" t="str">
+      <c r="E141" s="28"/>
+      <c r="G141" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G141" s="29" t="str">
+      <c r="H141" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H141" s="29" t="str">
+      <c r="I141" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I141" s="29" t="str">
+      <c r="J141" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B142" s="28"/>
+    <row r="142" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C142" s="28"/>
       <c r="D142" s="28"/>
-      <c r="F142" s="29" t="str">
+      <c r="E142" s="28"/>
+      <c r="G142" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G142" s="29" t="str">
+      <c r="H142" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H142" s="29" t="str">
+      <c r="I142" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I142" s="29" t="str">
+      <c r="J142" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B143" s="28"/>
+    <row r="143" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C143" s="28"/>
       <c r="D143" s="28"/>
-      <c r="F143" s="29" t="str">
+      <c r="E143" s="28"/>
+      <c r="G143" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G143" s="29" t="str">
+      <c r="H143" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H143" s="29" t="str">
+      <c r="I143" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I143" s="29" t="str">
+      <c r="J143" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B144" s="28"/>
+    <row r="144" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C144" s="28"/>
       <c r="D144" s="28"/>
-      <c r="F144" s="29" t="str">
+      <c r="E144" s="28"/>
+      <c r="G144" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G144" s="29" t="str">
+      <c r="H144" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H144" s="29" t="str">
+      <c r="I144" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I144" s="29" t="str">
+      <c r="J144" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B145" s="28"/>
+    <row r="145" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C145" s="28"/>
       <c r="D145" s="28"/>
-      <c r="F145" s="29" t="str">
+      <c r="E145" s="28"/>
+      <c r="G145" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G145" s="29" t="str">
+      <c r="H145" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H145" s="29" t="str">
+      <c r="I145" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I145" s="29" t="str">
+      <c r="J145" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B146" s="28"/>
+    <row r="146" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C146" s="28"/>
       <c r="D146" s="28"/>
-      <c r="F146" s="29" t="str">
+      <c r="E146" s="28"/>
+      <c r="G146" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G146" s="29" t="str">
+      <c r="H146" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H146" s="29" t="str">
+      <c r="I146" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I146" s="29" t="str">
+      <c r="J146" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B147" s="28"/>
+    <row r="147" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C147" s="28"/>
       <c r="D147" s="28"/>
-      <c r="F147" s="29" t="str">
+      <c r="E147" s="28"/>
+      <c r="G147" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G147" s="29" t="str">
+      <c r="H147" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H147" s="29" t="str">
+      <c r="I147" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I147" s="29" t="str">
+      <c r="J147" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B148" s="28"/>
+    <row r="148" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C148" s="28"/>
       <c r="D148" s="28"/>
-      <c r="F148" s="29" t="str">
+      <c r="E148" s="28"/>
+      <c r="G148" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G148" s="29" t="str">
+      <c r="H148" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H148" s="29" t="str">
+      <c r="I148" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I148" s="29" t="str">
+      <c r="J148" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B149" s="28"/>
+    <row r="149" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C149" s="28"/>
       <c r="D149" s="28"/>
-      <c r="F149" s="29" t="str">
+      <c r="E149" s="28"/>
+      <c r="G149" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G149" s="29" t="str">
+      <c r="H149" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H149" s="29" t="str">
+      <c r="I149" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I149" s="29" t="str">
+      <c r="J149" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B150" s="28"/>
+    <row r="150" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C150" s="28"/>
       <c r="D150" s="28"/>
-      <c r="F150" s="29" t="str">
+      <c r="E150" s="28"/>
+      <c r="G150" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G150" s="29" t="str">
+      <c r="H150" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H150" s="29" t="str">
+      <c r="I150" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I150" s="29" t="str">
+      <c r="J150" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B151" s="28"/>
+    <row r="151" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C151" s="28"/>
       <c r="D151" s="28"/>
-      <c r="F151" s="29" t="str">
+      <c r="E151" s="28"/>
+      <c r="G151" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G151" s="29" t="str">
+      <c r="H151" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H151" s="29" t="str">
+      <c r="I151" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I151" s="29" t="str">
+      <c r="J151" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B152" s="28"/>
+    <row r="152" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C152" s="28"/>
       <c r="D152" s="28"/>
-      <c r="F152" s="29" t="str">
+      <c r="E152" s="28"/>
+      <c r="G152" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G152" s="29" t="str">
+      <c r="H152" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H152" s="29" t="str">
+      <c r="I152" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I152" s="29" t="str">
+      <c r="J152" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B153" s="28"/>
+    <row r="153" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C153" s="28"/>
       <c r="D153" s="28"/>
-      <c r="F153" s="29" t="str">
+      <c r="E153" s="28"/>
+      <c r="G153" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G153" s="29" t="str">
+      <c r="H153" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H153" s="29" t="str">
+      <c r="I153" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I153" s="29" t="str">
+      <c r="J153" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B154" s="28"/>
+    <row r="154" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C154" s="28"/>
       <c r="D154" s="28"/>
-      <c r="F154" s="29" t="str">
+      <c r="E154" s="28"/>
+      <c r="G154" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G154" s="29" t="str">
+      <c r="H154" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H154" s="29" t="str">
+      <c r="I154" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I154" s="29" t="str">
+      <c r="J154" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B155" s="28"/>
+    <row r="155" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C155" s="28"/>
       <c r="D155" s="28"/>
-      <c r="F155" s="29" t="str">
+      <c r="E155" s="28"/>
+      <c r="G155" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G155" s="29" t="str">
+      <c r="H155" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H155" s="29" t="str">
+      <c r="I155" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I155" s="29" t="str">
+      <c r="J155" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B156" s="28"/>
+    <row r="156" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C156" s="28"/>
       <c r="D156" s="28"/>
-      <c r="F156" s="29" t="str">
+      <c r="E156" s="28"/>
+      <c r="G156" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G156" s="29" t="str">
+      <c r="H156" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H156" s="29" t="str">
+      <c r="I156" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I156" s="29" t="str">
+      <c r="J156" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B157" s="28"/>
+    <row r="157" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C157" s="28"/>
       <c r="D157" s="28"/>
-      <c r="F157" s="29" t="str">
+      <c r="E157" s="28"/>
+      <c r="G157" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G157" s="29" t="str">
+      <c r="H157" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H157" s="29" t="str">
+      <c r="I157" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I157" s="29" t="str">
+      <c r="J157" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B158" s="28"/>
+    <row r="158" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C158" s="28"/>
       <c r="D158" s="28"/>
-      <c r="F158" s="29" t="str">
+      <c r="E158" s="28"/>
+      <c r="G158" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G158" s="29" t="str">
+      <c r="H158" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H158" s="29" t="str">
+      <c r="I158" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I158" s="29" t="str">
+      <c r="J158" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B159" s="28"/>
+    <row r="159" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C159" s="28"/>
       <c r="D159" s="28"/>
-      <c r="F159" s="29" t="str">
+      <c r="E159" s="28"/>
+      <c r="G159" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G159" s="29" t="str">
+      <c r="H159" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H159" s="29" t="str">
+      <c r="I159" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I159" s="29" t="str">
+      <c r="J159" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B160" s="28"/>
+    <row r="160" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C160" s="28"/>
       <c r="D160" s="28"/>
-      <c r="F160" s="29" t="str">
+      <c r="E160" s="28"/>
+      <c r="G160" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G160" s="29" t="str">
+      <c r="H160" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H160" s="29" t="str">
+      <c r="I160" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I160" s="29" t="str">
+      <c r="J160" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B161" s="28"/>
+    <row r="161" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C161" s="28"/>
       <c r="D161" s="28"/>
-      <c r="F161" s="29" t="str">
+      <c r="E161" s="28"/>
+      <c r="G161" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G161" s="29" t="str">
+      <c r="H161" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H161" s="29" t="str">
+      <c r="I161" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I161" s="29" t="str">
+      <c r="J161" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B162" s="28"/>
+    <row r="162" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C162" s="28"/>
       <c r="D162" s="28"/>
-      <c r="F162" s="29" t="str">
+      <c r="E162" s="28"/>
+      <c r="G162" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G162" s="29" t="str">
+      <c r="H162" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H162" s="29" t="str">
+      <c r="I162" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I162" s="29" t="str">
+      <c r="J162" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B163" s="28"/>
+    <row r="163" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C163" s="28"/>
       <c r="D163" s="28"/>
-      <c r="F163" s="29" t="str">
+      <c r="E163" s="28"/>
+      <c r="G163" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G163" s="29" t="str">
+      <c r="H163" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H163" s="29" t="str">
+      <c r="I163" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I163" s="29" t="str">
+      <c r="J163" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B164" s="28"/>
+    <row r="164" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C164" s="28"/>
       <c r="D164" s="28"/>
-      <c r="F164" s="29" t="str">
+      <c r="E164" s="28"/>
+      <c r="G164" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G164" s="29" t="str">
+      <c r="H164" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H164" s="29" t="str">
+      <c r="I164" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I164" s="29" t="str">
+      <c r="J164" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B165" s="28"/>
+    <row r="165" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C165" s="28"/>
       <c r="D165" s="28"/>
-      <c r="F165" s="29" t="str">
+      <c r="E165" s="28"/>
+      <c r="G165" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G165" s="29" t="str">
+      <c r="H165" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H165" s="29" t="str">
+      <c r="I165" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I165" s="29" t="str">
+      <c r="J165" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B166" s="28"/>
+    <row r="166" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C166" s="28"/>
       <c r="D166" s="28"/>
-      <c r="F166" s="29" t="str">
+      <c r="E166" s="28"/>
+      <c r="G166" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G166" s="29" t="str">
+      <c r="H166" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H166" s="29" t="str">
+      <c r="I166" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I166" s="29" t="str">
+      <c r="J166" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B167" s="28"/>
+    <row r="167" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C167" s="28"/>
       <c r="D167" s="28"/>
-      <c r="F167" s="29" t="str">
+      <c r="E167" s="28"/>
+      <c r="G167" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G167" s="29" t="str">
+      <c r="H167" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H167" s="29" t="str">
+      <c r="I167" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I167" s="29" t="str">
+      <c r="J167" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B168" s="28"/>
+    <row r="168" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C168" s="28"/>
       <c r="D168" s="28"/>
-      <c r="F168" s="29" t="str">
+      <c r="E168" s="28"/>
+      <c r="G168" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G168" s="29" t="str">
+      <c r="H168" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H168" s="29" t="str">
+      <c r="I168" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I168" s="29" t="str">
+      <c r="J168" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B169" s="28"/>
+    <row r="169" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C169" s="28"/>
       <c r="D169" s="28"/>
-      <c r="F169" s="29" t="str">
+      <c r="E169" s="28"/>
+      <c r="G169" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G169" s="29" t="str">
+      <c r="H169" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H169" s="29" t="str">
+      <c r="I169" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I169" s="29" t="str">
+      <c r="J169" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B170" s="28"/>
+    <row r="170" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C170" s="28"/>
       <c r="D170" s="28"/>
-      <c r="F170" s="29" t="str">
+      <c r="E170" s="28"/>
+      <c r="G170" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G170" s="29" t="str">
+      <c r="H170" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H170" s="29" t="str">
+      <c r="I170" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I170" s="29" t="str">
+      <c r="J170" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B171" s="28"/>
+    <row r="171" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C171" s="28"/>
       <c r="D171" s="28"/>
-      <c r="F171" s="29" t="str">
+      <c r="E171" s="28"/>
+      <c r="G171" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G171" s="29" t="str">
+      <c r="H171" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H171" s="29" t="str">
+      <c r="I171" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I171" s="29" t="str">
+      <c r="J171" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B172" s="28"/>
+    <row r="172" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C172" s="28"/>
       <c r="D172" s="28"/>
-      <c r="F172" s="29" t="str">
+      <c r="E172" s="28"/>
+      <c r="G172" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G172" s="29" t="str">
+      <c r="H172" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H172" s="29" t="str">
+      <c r="I172" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I172" s="29" t="str">
+      <c r="J172" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B173" s="28"/>
+    <row r="173" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C173" s="28"/>
       <c r="D173" s="28"/>
-      <c r="F173" s="29" t="str">
+      <c r="E173" s="28"/>
+      <c r="G173" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G173" s="29" t="str">
+      <c r="H173" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H173" s="29" t="str">
+      <c r="I173" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I173" s="29" t="str">
+      <c r="J173" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B174" s="28"/>
+    <row r="174" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C174" s="28"/>
       <c r="D174" s="28"/>
-      <c r="F174" s="29" t="str">
+      <c r="E174" s="28"/>
+      <c r="G174" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G174" s="29" t="str">
+      <c r="H174" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H174" s="29" t="str">
+      <c r="I174" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I174" s="29" t="str">
+      <c r="J174" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B175" s="28"/>
+    <row r="175" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C175" s="28"/>
       <c r="D175" s="28"/>
-      <c r="F175" s="29" t="str">
+      <c r="E175" s="28"/>
+      <c r="G175" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G175" s="29" t="str">
+      <c r="H175" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H175" s="29" t="str">
+      <c r="I175" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I175" s="29" t="str">
+      <c r="J175" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B176" s="28"/>
+    <row r="176" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C176" s="28"/>
       <c r="D176" s="28"/>
-      <c r="F176" s="29" t="str">
+      <c r="E176" s="28"/>
+      <c r="G176" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G176" s="29" t="str">
+      <c r="H176" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H176" s="29" t="str">
+      <c r="I176" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I176" s="29" t="str">
+      <c r="J176" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B177" s="28"/>
+    <row r="177" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C177" s="28"/>
       <c r="D177" s="28"/>
-      <c r="F177" s="29" t="str">
+      <c r="E177" s="28"/>
+      <c r="G177" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G177" s="29" t="str">
+      <c r="H177" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H177" s="29" t="str">
+      <c r="I177" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I177" s="29" t="str">
+      <c r="J177" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B178" s="28"/>
+    <row r="178" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C178" s="28"/>
       <c r="D178" s="28"/>
-      <c r="F178" s="29" t="str">
+      <c r="E178" s="28"/>
+      <c r="G178" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G178" s="29" t="str">
+      <c r="H178" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H178" s="29" t="str">
+      <c r="I178" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I178" s="29" t="str">
+      <c r="J178" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B179" s="28"/>
+    <row r="179" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C179" s="28"/>
       <c r="D179" s="28"/>
-      <c r="F179" s="29" t="str">
+      <c r="E179" s="28"/>
+      <c r="G179" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G179" s="29" t="str">
+      <c r="H179" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H179" s="29" t="str">
+      <c r="I179" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I179" s="29" t="str">
+      <c r="J179" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B180" s="28"/>
+    <row r="180" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C180" s="28"/>
       <c r="D180" s="28"/>
-      <c r="F180" s="29" t="str">
+      <c r="E180" s="28"/>
+      <c r="G180" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G180" s="29" t="str">
+      <c r="H180" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H180" s="29" t="str">
+      <c r="I180" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I180" s="29" t="str">
+      <c r="J180" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B181" s="28"/>
+    <row r="181" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C181" s="28"/>
       <c r="D181" s="28"/>
-      <c r="F181" s="29" t="str">
+      <c r="E181" s="28"/>
+      <c r="G181" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G181" s="29" t="str">
+      <c r="H181" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H181" s="29" t="str">
+      <c r="I181" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I181" s="29" t="str">
+      <c r="J181" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B182" s="28"/>
+    <row r="182" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C182" s="28"/>
       <c r="D182" s="28"/>
-      <c r="F182" s="29" t="str">
+      <c r="E182" s="28"/>
+      <c r="G182" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G182" s="29" t="str">
+      <c r="H182" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H182" s="29" t="str">
+      <c r="I182" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I182" s="29" t="str">
+      <c r="J182" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B183" s="28"/>
+    <row r="183" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C183" s="28"/>
       <c r="D183" s="28"/>
-      <c r="F183" s="29" t="str">
+      <c r="E183" s="28"/>
+      <c r="G183" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G183" s="29" t="str">
+      <c r="H183" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H183" s="29" t="str">
+      <c r="I183" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I183" s="29" t="str">
+      <c r="J183" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B184" s="28"/>
+    <row r="184" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C184" s="28"/>
       <c r="D184" s="28"/>
-      <c r="F184" s="29" t="str">
+      <c r="E184" s="28"/>
+      <c r="G184" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G184" s="29" t="str">
+      <c r="H184" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H184" s="29" t="str">
+      <c r="I184" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I184" s="29" t="str">
+      <c r="J184" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B185" s="28"/>
+    <row r="185" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C185" s="28"/>
       <c r="D185" s="28"/>
-      <c r="F185" s="29" t="str">
+      <c r="E185" s="28"/>
+      <c r="G185" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G185" s="29" t="str">
+      <c r="H185" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H185" s="29" t="str">
+      <c r="I185" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I185" s="29" t="str">
+      <c r="J185" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B186" s="28"/>
+    <row r="186" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C186" s="28"/>
       <c r="D186" s="28"/>
-      <c r="F186" s="29" t="str">
+      <c r="E186" s="28"/>
+      <c r="G186" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G186" s="29" t="str">
+      <c r="H186" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H186" s="29" t="str">
+      <c r="I186" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I186" s="29" t="str">
+      <c r="J186" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B187" s="28"/>
+    <row r="187" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C187" s="28"/>
       <c r="D187" s="28"/>
-      <c r="F187" s="29" t="str">
+      <c r="E187" s="28"/>
+      <c r="G187" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G187" s="29" t="str">
+      <c r="H187" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H187" s="29" t="str">
+      <c r="I187" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I187" s="29" t="str">
+      <c r="J187" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B188" s="28"/>
+    <row r="188" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C188" s="28"/>
       <c r="D188" s="28"/>
-      <c r="F188" s="29" t="str">
+      <c r="E188" s="28"/>
+      <c r="G188" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G188" s="29" t="str">
+      <c r="H188" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H188" s="29" t="str">
+      <c r="I188" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I188" s="29" t="str">
+      <c r="J188" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B189" s="28"/>
+    <row r="189" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C189" s="28"/>
       <c r="D189" s="28"/>
-      <c r="F189" s="29" t="str">
+      <c r="E189" s="28"/>
+      <c r="G189" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G189" s="29" t="str">
+      <c r="H189" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H189" s="29" t="str">
+      <c r="I189" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I189" s="29" t="str">
+      <c r="J189" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B190" s="28"/>
+    <row r="190" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C190" s="28"/>
       <c r="D190" s="28"/>
-      <c r="F190" s="29" t="str">
+      <c r="E190" s="28"/>
+      <c r="G190" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G190" s="29" t="str">
+      <c r="H190" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H190" s="29" t="str">
+      <c r="I190" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I190" s="29" t="str">
+      <c r="J190" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B191" s="28"/>
+    <row r="191" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C191" s="28"/>
       <c r="D191" s="28"/>
-      <c r="F191" s="29" t="str">
+      <c r="E191" s="28"/>
+      <c r="G191" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G191" s="29" t="str">
+      <c r="H191" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H191" s="29" t="str">
+      <c r="I191" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I191" s="29" t="str">
+      <c r="J191" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B192" s="28"/>
+    <row r="192" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C192" s="28"/>
       <c r="D192" s="28"/>
-      <c r="F192" s="29" t="str">
+      <c r="E192" s="28"/>
+      <c r="G192" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G192" s="29" t="str">
+      <c r="H192" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H192" s="29" t="str">
+      <c r="I192" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I192" s="29" t="str">
+      <c r="J192" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B193" s="28"/>
+    <row r="193" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C193" s="28"/>
       <c r="D193" s="28"/>
-      <c r="F193" s="29" t="str">
+      <c r="E193" s="28"/>
+      <c r="G193" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="G193" s="29" t="str">
+      <c r="H193" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="H193" s="29" t="str">
+      <c r="I193" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I193" s="29" t="str">
+      <c r="J193" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B194" s="28"/>
+    <row r="194" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C194" s="28"/>
       <c r="D194" s="28"/>
-      <c r="F194" s="29" t="str">
-        <f t="shared" ref="F194:F257" ca="1" si="13">IF(B194="","",IF(E194="Recebido",D194-B194,TODAY()-B194))</f>
-        <v/>
-      </c>
+      <c r="E194" s="28"/>
       <c r="G194" s="29" t="str">
-        <f t="shared" ref="G194:G257" ca="1" si="14">IF(C194="","",IF(E194="Recebido",D194-C194,TODAY()-C194))</f>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="H194" s="29" t="str">
-        <f t="shared" ref="H194:H257" si="15">IF(OR(B194="",C194=""),"",C194-B194)</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="I194" s="29" t="str">
-        <f t="shared" ref="I194:I257" si="16">IF(OR(C194="",D194=""),"",D194-C194)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B195" s="28"/>
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J194" s="29" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C195" s="28"/>
       <c r="D195" s="28"/>
-      <c r="F195" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
+      <c r="E195" s="28"/>
       <c r="G195" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="H195" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="I195" s="29" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B196" s="28"/>
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J195" s="29" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C196" s="28"/>
       <c r="D196" s="28"/>
-      <c r="F196" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
+      <c r="E196" s="28"/>
       <c r="G196" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="H196" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="I196" s="29" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B197" s="28"/>
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J196" s="29" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C197" s="28"/>
       <c r="D197" s="28"/>
-      <c r="F197" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
+      <c r="E197" s="28"/>
       <c r="G197" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ref="G197:G260" ca="1" si="13">IF(C197="","",IF(F197="Recebido",E197-C197,TODAY()-C197))</f>
         <v/>
       </c>
       <c r="H197" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="H197:H260" ca="1" si="14">IF(D197="","",IF(F197="Recebido",E197-D197,TODAY()-D197))</f>
         <v/>
       </c>
       <c r="I197" s="29" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B198" s="28"/>
+        <f t="shared" ref="I197:I260" si="15">IF(OR(C197="",D197=""),"",D197-C197)</f>
+        <v/>
+      </c>
+      <c r="J197" s="29" t="str">
+        <f t="shared" ref="J197:J260" si="16">IF(OR(D197="",E197=""),"",E197-D197)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C198" s="28"/>
       <c r="D198" s="28"/>
-      <c r="F198" s="29" t="str">
+      <c r="E198" s="28"/>
+      <c r="G198" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G198" s="29" t="str">
+      <c r="H198" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H198" s="29" t="str">
+      <c r="I198" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I198" s="29" t="str">
+      <c r="J198" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B199" s="28"/>
+    <row r="199" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C199" s="28"/>
       <c r="D199" s="28"/>
-      <c r="F199" s="29" t="str">
+      <c r="E199" s="28"/>
+      <c r="G199" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G199" s="29" t="str">
+      <c r="H199" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H199" s="29" t="str">
+      <c r="I199" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I199" s="29" t="str">
+      <c r="J199" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B200" s="28"/>
+    <row r="200" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C200" s="28"/>
       <c r="D200" s="28"/>
-      <c r="F200" s="29" t="str">
+      <c r="E200" s="28"/>
+      <c r="G200" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G200" s="29" t="str">
+      <c r="H200" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H200" s="29" t="str">
+      <c r="I200" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I200" s="29" t="str">
+      <c r="J200" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B201" s="28"/>
+    <row r="201" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C201" s="28"/>
       <c r="D201" s="28"/>
-      <c r="F201" s="29" t="str">
+      <c r="E201" s="28"/>
+      <c r="G201" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G201" s="29" t="str">
+      <c r="H201" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H201" s="29" t="str">
+      <c r="I201" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I201" s="29" t="str">
+      <c r="J201" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B202" s="28"/>
+    <row r="202" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C202" s="28"/>
       <c r="D202" s="28"/>
-      <c r="F202" s="29" t="str">
+      <c r="E202" s="28"/>
+      <c r="G202" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G202" s="29" t="str">
+      <c r="H202" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H202" s="29" t="str">
+      <c r="I202" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I202" s="29" t="str">
+      <c r="J202" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B203" s="28"/>
+    <row r="203" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C203" s="28"/>
       <c r="D203" s="28"/>
-      <c r="F203" s="29" t="str">
+      <c r="E203" s="28"/>
+      <c r="G203" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G203" s="29" t="str">
+      <c r="H203" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H203" s="29" t="str">
+      <c r="I203" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I203" s="29" t="str">
+      <c r="J203" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B204" s="28"/>
+    <row r="204" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C204" s="28"/>
       <c r="D204" s="28"/>
-      <c r="F204" s="29" t="str">
+      <c r="E204" s="28"/>
+      <c r="G204" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G204" s="29" t="str">
+      <c r="H204" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H204" s="29" t="str">
+      <c r="I204" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I204" s="29" t="str">
+      <c r="J204" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="205" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B205" s="28"/>
+    <row r="205" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C205" s="28"/>
       <c r="D205" s="28"/>
-      <c r="F205" s="29" t="str">
+      <c r="E205" s="28"/>
+      <c r="G205" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G205" s="29" t="str">
+      <c r="H205" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H205" s="29" t="str">
+      <c r="I205" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I205" s="29" t="str">
+      <c r="J205" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="206" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B206" s="28"/>
+    <row r="206" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C206" s="28"/>
       <c r="D206" s="28"/>
-      <c r="F206" s="29" t="str">
+      <c r="E206" s="28"/>
+      <c r="G206" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G206" s="29" t="str">
+      <c r="H206" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H206" s="29" t="str">
+      <c r="I206" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I206" s="29" t="str">
+      <c r="J206" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B207" s="28"/>
+    <row r="207" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C207" s="28"/>
       <c r="D207" s="28"/>
-      <c r="F207" s="29" t="str">
+      <c r="E207" s="28"/>
+      <c r="G207" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G207" s="29" t="str">
+      <c r="H207" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H207" s="29" t="str">
+      <c r="I207" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I207" s="29" t="str">
+      <c r="J207" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B208" s="28"/>
+    <row r="208" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C208" s="28"/>
       <c r="D208" s="28"/>
-      <c r="F208" s="29" t="str">
+      <c r="E208" s="28"/>
+      <c r="G208" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G208" s="29" t="str">
+      <c r="H208" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H208" s="29" t="str">
+      <c r="I208" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I208" s="29" t="str">
+      <c r="J208" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="209" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B209" s="28"/>
+    <row r="209" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C209" s="28"/>
       <c r="D209" s="28"/>
-      <c r="F209" s="29" t="str">
+      <c r="E209" s="28"/>
+      <c r="G209" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G209" s="29" t="str">
+      <c r="H209" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H209" s="29" t="str">
+      <c r="I209" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I209" s="29" t="str">
+      <c r="J209" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="210" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B210" s="28"/>
+    <row r="210" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C210" s="28"/>
       <c r="D210" s="28"/>
-      <c r="F210" s="29" t="str">
+      <c r="E210" s="28"/>
+      <c r="G210" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G210" s="29" t="str">
+      <c r="H210" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H210" s="29" t="str">
+      <c r="I210" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I210" s="29" t="str">
+      <c r="J210" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="211" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B211" s="28"/>
+    <row r="211" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C211" s="28"/>
       <c r="D211" s="28"/>
-      <c r="F211" s="29" t="str">
+      <c r="E211" s="28"/>
+      <c r="G211" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G211" s="29" t="str">
+      <c r="H211" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H211" s="29" t="str">
+      <c r="I211" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I211" s="29" t="str">
+      <c r="J211" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="212" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B212" s="28"/>
+    <row r="212" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C212" s="28"/>
       <c r="D212" s="28"/>
-      <c r="F212" s="29" t="str">
+      <c r="E212" s="28"/>
+      <c r="G212" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G212" s="29" t="str">
+      <c r="H212" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H212" s="29" t="str">
+      <c r="I212" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I212" s="29" t="str">
+      <c r="J212" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="213" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B213" s="28"/>
+    <row r="213" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C213" s="28"/>
       <c r="D213" s="28"/>
-      <c r="F213" s="29" t="str">
+      <c r="E213" s="28"/>
+      <c r="G213" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G213" s="29" t="str">
+      <c r="H213" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H213" s="29" t="str">
+      <c r="I213" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I213" s="29" t="str">
+      <c r="J213" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="214" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B214" s="28"/>
+    <row r="214" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C214" s="28"/>
       <c r="D214" s="28"/>
-      <c r="F214" s="29" t="str">
+      <c r="E214" s="28"/>
+      <c r="G214" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G214" s="29" t="str">
+      <c r="H214" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H214" s="29" t="str">
+      <c r="I214" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I214" s="29" t="str">
+      <c r="J214" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="215" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B215" s="28"/>
+    <row r="215" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C215" s="28"/>
       <c r="D215" s="28"/>
-      <c r="F215" s="29" t="str">
+      <c r="E215" s="28"/>
+      <c r="G215" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G215" s="29" t="str">
+      <c r="H215" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H215" s="29" t="str">
+      <c r="I215" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I215" s="29" t="str">
+      <c r="J215" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="216" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B216" s="28"/>
+    <row r="216" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C216" s="28"/>
       <c r="D216" s="28"/>
-      <c r="F216" s="29" t="str">
+      <c r="E216" s="28"/>
+      <c r="G216" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G216" s="29" t="str">
+      <c r="H216" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H216" s="29" t="str">
+      <c r="I216" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I216" s="29" t="str">
+      <c r="J216" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="217" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B217" s="28"/>
+    <row r="217" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C217" s="28"/>
       <c r="D217" s="28"/>
-      <c r="F217" s="29" t="str">
+      <c r="E217" s="28"/>
+      <c r="G217" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G217" s="29" t="str">
+      <c r="H217" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H217" s="29" t="str">
+      <c r="I217" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I217" s="29" t="str">
+      <c r="J217" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="218" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B218" s="28"/>
+    <row r="218" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C218" s="28"/>
       <c r="D218" s="28"/>
-      <c r="F218" s="29" t="str">
+      <c r="E218" s="28"/>
+      <c r="G218" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G218" s="29" t="str">
+      <c r="H218" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H218" s="29" t="str">
+      <c r="I218" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I218" s="29" t="str">
+      <c r="J218" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="219" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B219" s="28"/>
+    <row r="219" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C219" s="28"/>
       <c r="D219" s="28"/>
-      <c r="F219" s="29" t="str">
+      <c r="E219" s="28"/>
+      <c r="G219" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G219" s="29" t="str">
+      <c r="H219" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H219" s="29" t="str">
+      <c r="I219" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I219" s="29" t="str">
+      <c r="J219" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="220" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B220" s="28"/>
+    <row r="220" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C220" s="28"/>
       <c r="D220" s="28"/>
-      <c r="F220" s="29" t="str">
+      <c r="E220" s="28"/>
+      <c r="G220" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G220" s="29" t="str">
+      <c r="H220" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H220" s="29" t="str">
+      <c r="I220" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I220" s="29" t="str">
+      <c r="J220" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="221" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B221" s="28"/>
+    <row r="221" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C221" s="28"/>
       <c r="D221" s="28"/>
-      <c r="F221" s="29" t="str">
+      <c r="E221" s="28"/>
+      <c r="G221" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G221" s="29" t="str">
+      <c r="H221" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H221" s="29" t="str">
+      <c r="I221" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I221" s="29" t="str">
+      <c r="J221" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="222" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B222" s="28"/>
+    <row r="222" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C222" s="28"/>
       <c r="D222" s="28"/>
-      <c r="F222" s="29" t="str">
+      <c r="E222" s="28"/>
+      <c r="G222" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G222" s="29" t="str">
+      <c r="H222" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H222" s="29" t="str">
+      <c r="I222" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I222" s="29" t="str">
+      <c r="J222" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="223" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B223" s="28"/>
+    <row r="223" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C223" s="28"/>
       <c r="D223" s="28"/>
-      <c r="F223" s="29" t="str">
+      <c r="E223" s="28"/>
+      <c r="G223" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G223" s="29" t="str">
+      <c r="H223" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H223" s="29" t="str">
+      <c r="I223" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I223" s="29" t="str">
+      <c r="J223" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="224" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B224" s="28"/>
+    <row r="224" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C224" s="28"/>
       <c r="D224" s="28"/>
-      <c r="F224" s="29" t="str">
+      <c r="E224" s="28"/>
+      <c r="G224" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G224" s="29" t="str">
+      <c r="H224" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H224" s="29" t="str">
+      <c r="I224" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I224" s="29" t="str">
+      <c r="J224" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="225" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B225" s="28"/>
+    <row r="225" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C225" s="28"/>
       <c r="D225" s="28"/>
-      <c r="F225" s="29" t="str">
+      <c r="E225" s="28"/>
+      <c r="G225" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G225" s="29" t="str">
+      <c r="H225" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H225" s="29" t="str">
+      <c r="I225" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I225" s="29" t="str">
+      <c r="J225" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="226" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B226" s="28"/>
+    <row r="226" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C226" s="28"/>
       <c r="D226" s="28"/>
-      <c r="F226" s="29" t="str">
+      <c r="E226" s="28"/>
+      <c r="G226" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G226" s="29" t="str">
+      <c r="H226" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H226" s="29" t="str">
+      <c r="I226" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I226" s="29" t="str">
+      <c r="J226" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="227" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B227" s="28"/>
+    <row r="227" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C227" s="28"/>
       <c r="D227" s="28"/>
-      <c r="F227" s="29" t="str">
+      <c r="E227" s="28"/>
+      <c r="G227" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G227" s="29" t="str">
+      <c r="H227" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H227" s="29" t="str">
+      <c r="I227" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I227" s="29" t="str">
+      <c r="J227" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="228" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B228" s="28"/>
+    <row r="228" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C228" s="28"/>
       <c r="D228" s="28"/>
-      <c r="F228" s="29" t="str">
+      <c r="E228" s="28"/>
+      <c r="G228" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G228" s="29" t="str">
+      <c r="H228" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H228" s="29" t="str">
+      <c r="I228" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I228" s="29" t="str">
+      <c r="J228" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="229" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B229" s="28"/>
+    <row r="229" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C229" s="28"/>
       <c r="D229" s="28"/>
-      <c r="F229" s="29" t="str">
+      <c r="E229" s="28"/>
+      <c r="G229" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G229" s="29" t="str">
+      <c r="H229" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H229" s="29" t="str">
+      <c r="I229" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I229" s="29" t="str">
+      <c r="J229" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="230" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B230" s="28"/>
+    <row r="230" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C230" s="28"/>
       <c r="D230" s="28"/>
-      <c r="F230" s="29" t="str">
+      <c r="E230" s="28"/>
+      <c r="G230" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G230" s="29" t="str">
+      <c r="H230" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H230" s="29" t="str">
+      <c r="I230" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I230" s="29" t="str">
+      <c r="J230" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="231" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B231" s="28"/>
+    <row r="231" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C231" s="28"/>
       <c r="D231" s="28"/>
-      <c r="F231" s="29" t="str">
+      <c r="E231" s="28"/>
+      <c r="G231" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G231" s="29" t="str">
+      <c r="H231" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H231" s="29" t="str">
+      <c r="I231" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I231" s="29" t="str">
+      <c r="J231" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="232" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B232" s="28"/>
+    <row r="232" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C232" s="28"/>
       <c r="D232" s="28"/>
-      <c r="F232" s="29" t="str">
+      <c r="E232" s="28"/>
+      <c r="G232" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G232" s="29" t="str">
+      <c r="H232" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H232" s="29" t="str">
+      <c r="I232" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I232" s="29" t="str">
+      <c r="J232" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="233" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B233" s="28"/>
+    <row r="233" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C233" s="28"/>
       <c r="D233" s="28"/>
-      <c r="F233" s="29" t="str">
+      <c r="E233" s="28"/>
+      <c r="G233" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G233" s="29" t="str">
+      <c r="H233" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H233" s="29" t="str">
+      <c r="I233" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I233" s="29" t="str">
+      <c r="J233" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="234" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B234" s="28"/>
+    <row r="234" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C234" s="28"/>
       <c r="D234" s="28"/>
-      <c r="F234" s="29" t="str">
+      <c r="E234" s="28"/>
+      <c r="G234" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G234" s="29" t="str">
+      <c r="H234" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H234" s="29" t="str">
+      <c r="I234" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I234" s="29" t="str">
+      <c r="J234" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="235" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B235" s="28"/>
+    <row r="235" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C235" s="28"/>
       <c r="D235" s="28"/>
-      <c r="F235" s="29" t="str">
+      <c r="E235" s="28"/>
+      <c r="G235" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G235" s="29" t="str">
+      <c r="H235" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H235" s="29" t="str">
+      <c r="I235" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I235" s="29" t="str">
+      <c r="J235" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="236" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B236" s="28"/>
+    <row r="236" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C236" s="28"/>
       <c r="D236" s="28"/>
-      <c r="F236" s="29" t="str">
+      <c r="E236" s="28"/>
+      <c r="G236" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G236" s="29" t="str">
+      <c r="H236" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H236" s="29" t="str">
+      <c r="I236" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I236" s="29" t="str">
+      <c r="J236" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="237" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B237" s="28"/>
+    <row r="237" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C237" s="28"/>
       <c r="D237" s="28"/>
-      <c r="F237" s="29" t="str">
+      <c r="E237" s="28"/>
+      <c r="G237" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G237" s="29" t="str">
+      <c r="H237" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H237" s="29" t="str">
+      <c r="I237" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I237" s="29" t="str">
+      <c r="J237" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="238" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B238" s="28"/>
+    <row r="238" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C238" s="28"/>
       <c r="D238" s="28"/>
-      <c r="F238" s="29" t="str">
+      <c r="E238" s="28"/>
+      <c r="G238" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G238" s="29" t="str">
+      <c r="H238" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H238" s="29" t="str">
+      <c r="I238" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I238" s="29" t="str">
+      <c r="J238" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="239" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B239" s="28"/>
+    <row r="239" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C239" s="28"/>
       <c r="D239" s="28"/>
-      <c r="F239" s="29" t="str">
+      <c r="E239" s="28"/>
+      <c r="G239" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G239" s="29" t="str">
+      <c r="H239" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H239" s="29" t="str">
+      <c r="I239" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I239" s="29" t="str">
+      <c r="J239" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="240" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B240" s="28"/>
+    <row r="240" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C240" s="28"/>
       <c r="D240" s="28"/>
-      <c r="F240" s="29" t="str">
+      <c r="E240" s="28"/>
+      <c r="G240" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G240" s="29" t="str">
+      <c r="H240" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H240" s="29" t="str">
+      <c r="I240" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I240" s="29" t="str">
+      <c r="J240" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="241" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B241" s="28"/>
+    <row r="241" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C241" s="28"/>
       <c r="D241" s="28"/>
-      <c r="F241" s="29" t="str">
+      <c r="E241" s="28"/>
+      <c r="G241" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G241" s="29" t="str">
+      <c r="H241" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H241" s="29" t="str">
+      <c r="I241" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I241" s="29" t="str">
+      <c r="J241" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="242" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B242" s="28"/>
+    <row r="242" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C242" s="28"/>
       <c r="D242" s="28"/>
-      <c r="F242" s="29" t="str">
+      <c r="E242" s="28"/>
+      <c r="G242" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G242" s="29" t="str">
+      <c r="H242" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H242" s="29" t="str">
+      <c r="I242" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I242" s="29" t="str">
+      <c r="J242" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="243" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B243" s="28"/>
+    <row r="243" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C243" s="28"/>
       <c r="D243" s="28"/>
-      <c r="F243" s="29" t="str">
+      <c r="E243" s="28"/>
+      <c r="G243" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G243" s="29" t="str">
+      <c r="H243" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H243" s="29" t="str">
+      <c r="I243" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I243" s="29" t="str">
+      <c r="J243" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="244" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B244" s="28"/>
+    <row r="244" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C244" s="28"/>
       <c r="D244" s="28"/>
-      <c r="F244" s="29" t="str">
+      <c r="E244" s="28"/>
+      <c r="G244" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G244" s="29" t="str">
+      <c r="H244" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H244" s="29" t="str">
+      <c r="I244" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I244" s="29" t="str">
+      <c r="J244" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="245" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B245" s="28"/>
+    <row r="245" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C245" s="28"/>
       <c r="D245" s="28"/>
-      <c r="F245" s="29" t="str">
+      <c r="E245" s="28"/>
+      <c r="G245" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G245" s="29" t="str">
+      <c r="H245" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H245" s="29" t="str">
+      <c r="I245" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I245" s="29" t="str">
+      <c r="J245" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="246" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B246" s="28"/>
+    <row r="246" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C246" s="28"/>
       <c r="D246" s="28"/>
-      <c r="F246" s="29" t="str">
+      <c r="E246" s="28"/>
+      <c r="G246" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G246" s="29" t="str">
+      <c r="H246" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H246" s="29" t="str">
+      <c r="I246" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I246" s="29" t="str">
+      <c r="J246" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="247" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B247" s="28"/>
+    <row r="247" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C247" s="28"/>
       <c r="D247" s="28"/>
-      <c r="F247" s="29" t="str">
+      <c r="E247" s="28"/>
+      <c r="G247" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G247" s="29" t="str">
+      <c r="H247" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H247" s="29" t="str">
+      <c r="I247" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I247" s="29" t="str">
+      <c r="J247" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="248" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B248" s="28"/>
+    <row r="248" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C248" s="28"/>
       <c r="D248" s="28"/>
-      <c r="F248" s="29" t="str">
+      <c r="E248" s="28"/>
+      <c r="G248" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G248" s="29" t="str">
+      <c r="H248" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H248" s="29" t="str">
+      <c r="I248" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I248" s="29" t="str">
+      <c r="J248" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="249" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B249" s="28"/>
+    <row r="249" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C249" s="28"/>
       <c r="D249" s="28"/>
-      <c r="F249" s="29" t="str">
+      <c r="E249" s="28"/>
+      <c r="G249" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G249" s="29" t="str">
+      <c r="H249" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H249" s="29" t="str">
+      <c r="I249" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I249" s="29" t="str">
+      <c r="J249" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="250" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B250" s="28"/>
+    <row r="250" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C250" s="28"/>
       <c r="D250" s="28"/>
-      <c r="F250" s="29" t="str">
+      <c r="E250" s="28"/>
+      <c r="G250" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G250" s="29" t="str">
+      <c r="H250" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H250" s="29" t="str">
+      <c r="I250" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I250" s="29" t="str">
+      <c r="J250" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="251" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B251" s="28"/>
+    <row r="251" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C251" s="28"/>
       <c r="D251" s="28"/>
-      <c r="F251" s="29" t="str">
+      <c r="E251" s="28"/>
+      <c r="G251" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G251" s="29" t="str">
+      <c r="H251" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H251" s="29" t="str">
+      <c r="I251" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I251" s="29" t="str">
+      <c r="J251" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="252" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B252" s="28"/>
+    <row r="252" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C252" s="28"/>
       <c r="D252" s="28"/>
-      <c r="F252" s="29" t="str">
+      <c r="E252" s="28"/>
+      <c r="G252" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G252" s="29" t="str">
+      <c r="H252" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H252" s="29" t="str">
+      <c r="I252" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I252" s="29" t="str">
+      <c r="J252" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="253" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B253" s="28"/>
+    <row r="253" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C253" s="28"/>
       <c r="D253" s="28"/>
-      <c r="F253" s="29" t="str">
+      <c r="E253" s="28"/>
+      <c r="G253" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G253" s="29" t="str">
+      <c r="H253" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H253" s="29" t="str">
+      <c r="I253" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I253" s="29" t="str">
+      <c r="J253" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="254" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B254" s="28"/>
+    <row r="254" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C254" s="28"/>
       <c r="D254" s="28"/>
-      <c r="F254" s="29" t="str">
+      <c r="E254" s="28"/>
+      <c r="G254" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G254" s="29" t="str">
+      <c r="H254" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H254" s="29" t="str">
+      <c r="I254" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I254" s="29" t="str">
+      <c r="J254" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="255" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B255" s="28"/>
+    <row r="255" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C255" s="28"/>
       <c r="D255" s="28"/>
-      <c r="F255" s="29" t="str">
+      <c r="E255" s="28"/>
+      <c r="G255" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G255" s="29" t="str">
+      <c r="H255" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H255" s="29" t="str">
+      <c r="I255" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I255" s="29" t="str">
+      <c r="J255" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="256" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B256" s="28"/>
+    <row r="256" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C256" s="28"/>
       <c r="D256" s="28"/>
-      <c r="F256" s="29" t="str">
+      <c r="E256" s="28"/>
+      <c r="G256" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G256" s="29" t="str">
+      <c r="H256" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H256" s="29" t="str">
+      <c r="I256" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I256" s="29" t="str">
+      <c r="J256" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="257" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B257" s="28"/>
+    <row r="257" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C257" s="28"/>
       <c r="D257" s="28"/>
-      <c r="F257" s="29" t="str">
+      <c r="E257" s="28"/>
+      <c r="G257" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="G257" s="29" t="str">
+      <c r="H257" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="H257" s="29" t="str">
+      <c r="I257" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I257" s="29" t="str">
+      <c r="J257" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="258" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B258" s="28"/>
+    <row r="258" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C258" s="28"/>
       <c r="D258" s="28"/>
-      <c r="F258" s="29" t="str">
-        <f t="shared" ref="F258:F321" ca="1" si="17">IF(B258="","",IF(E258="Recebido",D258-B258,TODAY()-B258))</f>
-        <v/>
-      </c>
+      <c r="E258" s="28"/>
       <c r="G258" s="29" t="str">
-        <f t="shared" ref="G258:G300" ca="1" si="18">IF(C258="","",IF(E258="Recebido",D258-C258,TODAY()-C258))</f>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="H258" s="29" t="str">
-        <f t="shared" ref="H258:H300" si="19">IF(OR(B258="",C258=""),"",C258-B258)</f>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="I258" s="29" t="str">
-        <f t="shared" ref="I258:I300" si="20">IF(OR(C258="",D258=""),"",D258-C258)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B259" s="28"/>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="J258" s="29" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C259" s="28"/>
       <c r="D259" s="28"/>
-      <c r="F259" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
+      <c r="E259" s="28"/>
       <c r="G259" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="H259" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="I259" s="29" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B260" s="28"/>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="J259" s="29" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C260" s="28"/>
       <c r="D260" s="28"/>
-      <c r="F260" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
+      <c r="E260" s="28"/>
       <c r="G260" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="H260" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="I260" s="29" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B261" s="28"/>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="J260" s="29" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C261" s="28"/>
       <c r="D261" s="28"/>
-      <c r="F261" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
+      <c r="E261" s="28"/>
       <c r="G261" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ref="G261:G303" ca="1" si="17">IF(C261="","",IF(F261="Recebido",E261-C261,TODAY()-C261))</f>
         <v/>
       </c>
       <c r="H261" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="H261:H303" ca="1" si="18">IF(D261="","",IF(F261="Recebido",E261-D261,TODAY()-D261))</f>
         <v/>
       </c>
       <c r="I261" s="29" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B262" s="28"/>
+        <f t="shared" ref="I261:I303" si="19">IF(OR(C261="",D261=""),"",D261-C261)</f>
+        <v/>
+      </c>
+      <c r="J261" s="29" t="str">
+        <f t="shared" ref="J261:J303" si="20">IF(OR(D261="",E261=""),"",E261-D261)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C262" s="28"/>
       <c r="D262" s="28"/>
-      <c r="F262" s="29" t="str">
+      <c r="E262" s="28"/>
+      <c r="G262" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G262" s="29" t="str">
+      <c r="H262" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H262" s="29" t="str">
+      <c r="I262" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I262" s="29" t="str">
+      <c r="J262" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="263" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B263" s="28"/>
+    <row r="263" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C263" s="28"/>
       <c r="D263" s="28"/>
-      <c r="F263" s="29" t="str">
+      <c r="E263" s="28"/>
+      <c r="G263" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G263" s="29" t="str">
+      <c r="H263" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H263" s="29" t="str">
+      <c r="I263" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I263" s="29" t="str">
+      <c r="J263" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="264" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B264" s="28"/>
+    <row r="264" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C264" s="28"/>
       <c r="D264" s="28"/>
-      <c r="F264" s="29" t="str">
+      <c r="E264" s="28"/>
+      <c r="G264" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G264" s="29" t="str">
+      <c r="H264" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H264" s="29" t="str">
+      <c r="I264" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I264" s="29" t="str">
+      <c r="J264" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="265" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B265" s="28"/>
+    <row r="265" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C265" s="28"/>
       <c r="D265" s="28"/>
-      <c r="F265" s="29" t="str">
+      <c r="E265" s="28"/>
+      <c r="G265" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G265" s="29" t="str">
+      <c r="H265" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H265" s="29" t="str">
+      <c r="I265" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I265" s="29" t="str">
+      <c r="J265" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="266" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B266" s="28"/>
+    <row r="266" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C266" s="28"/>
       <c r="D266" s="28"/>
-      <c r="F266" s="29" t="str">
+      <c r="E266" s="28"/>
+      <c r="G266" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G266" s="29" t="str">
+      <c r="H266" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H266" s="29" t="str">
+      <c r="I266" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I266" s="29" t="str">
+      <c r="J266" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="267" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B267" s="28"/>
+    <row r="267" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C267" s="28"/>
       <c r="D267" s="28"/>
-      <c r="F267" s="29" t="str">
+      <c r="E267" s="28"/>
+      <c r="G267" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G267" s="29" t="str">
+      <c r="H267" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H267" s="29" t="str">
+      <c r="I267" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I267" s="29" t="str">
+      <c r="J267" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="268" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B268" s="28"/>
+    <row r="268" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C268" s="28"/>
       <c r="D268" s="28"/>
-      <c r="F268" s="29" t="str">
+      <c r="E268" s="28"/>
+      <c r="G268" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G268" s="29" t="str">
+      <c r="H268" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H268" s="29" t="str">
+      <c r="I268" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I268" s="29" t="str">
+      <c r="J268" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="269" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B269" s="28"/>
+    <row r="269" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C269" s="28"/>
       <c r="D269" s="28"/>
-      <c r="F269" s="29" t="str">
+      <c r="E269" s="28"/>
+      <c r="G269" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G269" s="29" t="str">
+      <c r="H269" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H269" s="29" t="str">
+      <c r="I269" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I269" s="29" t="str">
+      <c r="J269" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="270" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B270" s="28"/>
+    <row r="270" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C270" s="28"/>
       <c r="D270" s="28"/>
-      <c r="F270" s="29" t="str">
+      <c r="E270" s="28"/>
+      <c r="G270" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G270" s="29" t="str">
+      <c r="H270" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H270" s="29" t="str">
+      <c r="I270" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I270" s="29" t="str">
+      <c r="J270" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="271" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B271" s="28"/>
+    <row r="271" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C271" s="28"/>
       <c r="D271" s="28"/>
-      <c r="F271" s="29" t="str">
+      <c r="E271" s="28"/>
+      <c r="G271" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G271" s="29" t="str">
+      <c r="H271" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H271" s="29" t="str">
+      <c r="I271" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I271" s="29" t="str">
+      <c r="J271" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="272" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B272" s="28"/>
+    <row r="272" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C272" s="28"/>
       <c r="D272" s="28"/>
-      <c r="F272" s="29" t="str">
+      <c r="E272" s="28"/>
+      <c r="G272" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G272" s="29" t="str">
+      <c r="H272" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H272" s="29" t="str">
+      <c r="I272" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I272" s="29" t="str">
+      <c r="J272" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="273" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B273" s="28"/>
+    <row r="273" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C273" s="28"/>
       <c r="D273" s="28"/>
-      <c r="F273" s="29" t="str">
+      <c r="E273" s="28"/>
+      <c r="G273" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G273" s="29" t="str">
+      <c r="H273" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H273" s="29" t="str">
+      <c r="I273" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I273" s="29" t="str">
+      <c r="J273" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="274" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B274" s="28"/>
+    <row r="274" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C274" s="28"/>
       <c r="D274" s="28"/>
-      <c r="F274" s="29" t="str">
+      <c r="E274" s="28"/>
+      <c r="G274" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G274" s="29" t="str">
+      <c r="H274" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H274" s="29" t="str">
+      <c r="I274" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I274" s="29" t="str">
+      <c r="J274" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="275" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B275" s="28"/>
+    <row r="275" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C275" s="28"/>
       <c r="D275" s="28"/>
-      <c r="F275" s="29" t="str">
+      <c r="E275" s="28"/>
+      <c r="G275" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G275" s="29" t="str">
+      <c r="H275" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H275" s="29" t="str">
+      <c r="I275" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I275" s="29" t="str">
+      <c r="J275" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="276" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B276" s="28"/>
+    <row r="276" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C276" s="28"/>
       <c r="D276" s="28"/>
-      <c r="F276" s="29" t="str">
+      <c r="E276" s="28"/>
+      <c r="G276" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G276" s="29" t="str">
+      <c r="H276" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H276" s="29" t="str">
+      <c r="I276" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I276" s="29" t="str">
+      <c r="J276" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="277" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B277" s="28"/>
+    <row r="277" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C277" s="28"/>
       <c r="D277" s="28"/>
-      <c r="F277" s="29" t="str">
+      <c r="E277" s="28"/>
+      <c r="G277" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G277" s="29" t="str">
+      <c r="H277" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H277" s="29" t="str">
+      <c r="I277" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I277" s="29" t="str">
+      <c r="J277" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="278" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B278" s="28"/>
+    <row r="278" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C278" s="28"/>
       <c r="D278" s="28"/>
-      <c r="F278" s="29" t="str">
+      <c r="E278" s="28"/>
+      <c r="G278" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G278" s="29" t="str">
+      <c r="H278" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H278" s="29" t="str">
+      <c r="I278" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I278" s="29" t="str">
+      <c r="J278" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="279" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B279" s="28"/>
+    <row r="279" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C279" s="28"/>
       <c r="D279" s="28"/>
-      <c r="F279" s="29" t="str">
+      <c r="E279" s="28"/>
+      <c r="G279" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G279" s="29" t="str">
+      <c r="H279" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H279" s="29" t="str">
+      <c r="I279" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I279" s="29" t="str">
+      <c r="J279" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="280" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B280" s="28"/>
+    <row r="280" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C280" s="28"/>
       <c r="D280" s="28"/>
-      <c r="F280" s="29" t="str">
+      <c r="E280" s="28"/>
+      <c r="G280" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G280" s="29" t="str">
+      <c r="H280" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H280" s="29" t="str">
+      <c r="I280" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I280" s="29" t="str">
+      <c r="J280" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="281" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B281" s="28"/>
+    <row r="281" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C281" s="28"/>
       <c r="D281" s="28"/>
-      <c r="F281" s="29" t="str">
+      <c r="E281" s="28"/>
+      <c r="G281" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G281" s="29" t="str">
+      <c r="H281" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H281" s="29" t="str">
+      <c r="I281" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I281" s="29" t="str">
+      <c r="J281" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="282" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B282" s="28"/>
+    <row r="282" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C282" s="28"/>
       <c r="D282" s="28"/>
-      <c r="F282" s="29" t="str">
+      <c r="E282" s="28"/>
+      <c r="G282" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G282" s="29" t="str">
+      <c r="H282" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H282" s="29" t="str">
+      <c r="I282" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I282" s="29" t="str">
+      <c r="J282" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="283" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B283" s="28"/>
+    <row r="283" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C283" s="28"/>
       <c r="D283" s="28"/>
-      <c r="F283" s="29" t="str">
+      <c r="E283" s="28"/>
+      <c r="G283" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G283" s="29" t="str">
+      <c r="H283" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H283" s="29" t="str">
+      <c r="I283" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I283" s="29" t="str">
+      <c r="J283" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="284" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B284" s="28"/>
+    <row r="284" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C284" s="28"/>
       <c r="D284" s="28"/>
-      <c r="F284" s="29" t="str">
+      <c r="E284" s="28"/>
+      <c r="G284" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G284" s="29" t="str">
+      <c r="H284" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H284" s="29" t="str">
+      <c r="I284" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I284" s="29" t="str">
+      <c r="J284" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="285" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B285" s="28"/>
+    <row r="285" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C285" s="28"/>
       <c r="D285" s="28"/>
-      <c r="F285" s="29" t="str">
+      <c r="E285" s="28"/>
+      <c r="G285" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G285" s="29" t="str">
+      <c r="H285" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H285" s="29" t="str">
+      <c r="I285" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I285" s="29" t="str">
+      <c r="J285" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="286" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B286" s="28"/>
+    <row r="286" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C286" s="28"/>
       <c r="D286" s="28"/>
-      <c r="F286" s="29" t="str">
+      <c r="E286" s="28"/>
+      <c r="G286" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G286" s="29" t="str">
+      <c r="H286" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H286" s="29" t="str">
+      <c r="I286" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I286" s="29" t="str">
+      <c r="J286" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="287" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B287" s="28"/>
+    <row r="287" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C287" s="28"/>
       <c r="D287" s="28"/>
-      <c r="F287" s="29" t="str">
+      <c r="E287" s="28"/>
+      <c r="G287" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G287" s="29" t="str">
+      <c r="H287" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H287" s="29" t="str">
+      <c r="I287" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I287" s="29" t="str">
+      <c r="J287" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="288" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B288" s="28"/>
+    <row r="288" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C288" s="28"/>
       <c r="D288" s="28"/>
-      <c r="F288" s="29" t="str">
+      <c r="E288" s="28"/>
+      <c r="G288" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G288" s="29" t="str">
+      <c r="H288" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H288" s="29" t="str">
+      <c r="I288" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I288" s="29" t="str">
+      <c r="J288" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="289" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B289" s="28"/>
+    <row r="289" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C289" s="28"/>
       <c r="D289" s="28"/>
-      <c r="F289" s="29" t="str">
+      <c r="E289" s="28"/>
+      <c r="G289" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G289" s="29" t="str">
+      <c r="H289" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H289" s="29" t="str">
+      <c r="I289" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I289" s="29" t="str">
+      <c r="J289" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="290" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B290" s="28"/>
+    <row r="290" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C290" s="28"/>
       <c r="D290" s="28"/>
-      <c r="F290" s="29" t="str">
+      <c r="E290" s="28"/>
+      <c r="G290" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G290" s="29" t="str">
+      <c r="H290" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H290" s="29" t="str">
+      <c r="I290" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I290" s="29" t="str">
+      <c r="J290" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="291" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B291" s="28"/>
+    <row r="291" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C291" s="28"/>
       <c r="D291" s="28"/>
-      <c r="F291" s="29" t="str">
+      <c r="E291" s="28"/>
+      <c r="G291" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G291" s="29" t="str">
+      <c r="H291" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H291" s="29" t="str">
+      <c r="I291" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I291" s="29" t="str">
+      <c r="J291" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="292" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B292" s="28"/>
+    <row r="292" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C292" s="28"/>
       <c r="D292" s="28"/>
-      <c r="F292" s="29" t="str">
+      <c r="E292" s="28"/>
+      <c r="G292" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G292" s="29" t="str">
+      <c r="H292" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H292" s="29" t="str">
+      <c r="I292" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I292" s="29" t="str">
+      <c r="J292" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="293" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B293" s="28"/>
+    <row r="293" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C293" s="28"/>
       <c r="D293" s="28"/>
-      <c r="F293" s="29" t="str">
+      <c r="E293" s="28"/>
+      <c r="G293" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G293" s="29" t="str">
+      <c r="H293" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H293" s="29" t="str">
+      <c r="I293" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I293" s="29" t="str">
+      <c r="J293" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="294" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B294" s="28"/>
+    <row r="294" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C294" s="28"/>
       <c r="D294" s="28"/>
-      <c r="F294" s="29" t="str">
+      <c r="E294" s="28"/>
+      <c r="G294" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G294" s="29" t="str">
+      <c r="H294" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H294" s="29" t="str">
+      <c r="I294" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I294" s="29" t="str">
+      <c r="J294" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="295" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B295" s="28"/>
+    <row r="295" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C295" s="28"/>
       <c r="D295" s="28"/>
-      <c r="F295" s="29" t="str">
+      <c r="E295" s="28"/>
+      <c r="G295" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G295" s="29" t="str">
+      <c r="H295" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H295" s="29" t="str">
+      <c r="I295" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I295" s="29" t="str">
+      <c r="J295" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="296" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B296" s="28"/>
+    <row r="296" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C296" s="28"/>
       <c r="D296" s="28"/>
-      <c r="F296" s="29" t="str">
+      <c r="E296" s="28"/>
+      <c r="G296" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G296" s="29" t="str">
+      <c r="H296" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H296" s="29" t="str">
+      <c r="I296" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I296" s="29" t="str">
+      <c r="J296" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="297" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B297" s="28"/>
+    <row r="297" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C297" s="28"/>
       <c r="D297" s="28"/>
-      <c r="F297" s="29" t="str">
+      <c r="E297" s="28"/>
+      <c r="G297" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G297" s="29" t="str">
+      <c r="H297" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H297" s="29" t="str">
+      <c r="I297" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I297" s="29" t="str">
+      <c r="J297" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="298" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B298" s="28"/>
+    <row r="298" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C298" s="28"/>
       <c r="D298" s="28"/>
-      <c r="F298" s="29" t="str">
+      <c r="E298" s="28"/>
+      <c r="G298" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G298" s="29" t="str">
+      <c r="H298" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H298" s="29" t="str">
+      <c r="I298" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I298" s="29" t="str">
+      <c r="J298" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="299" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B299" s="28"/>
+    <row r="299" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C299" s="28"/>
       <c r="D299" s="28"/>
-      <c r="F299" s="29" t="str">
+      <c r="E299" s="28"/>
+      <c r="G299" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G299" s="29" t="str">
+      <c r="H299" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H299" s="29" t="str">
+      <c r="I299" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I299" s="29" t="str">
+      <c r="J299" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
-    <row r="300" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B300" s="28"/>
+    <row r="300" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C300" s="28"/>
       <c r="D300" s="28"/>
-      <c r="F300" s="29" t="str">
+      <c r="E300" s="28"/>
+      <c r="G300" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="G300" s="29" t="str">
+      <c r="H300" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="H300" s="29" t="str">
+      <c r="I300" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I300" s="29" t="str">
+      <c r="J300" s="29" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C301" s="28"/>
+      <c r="D301" s="28"/>
+      <c r="E301" s="28"/>
+      <c r="G301" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="H301" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="I301" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="J301" s="29" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C302" s="28"/>
+      <c r="D302" s="28"/>
+      <c r="E302" s="28"/>
+      <c r="G302" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="H302" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="I302" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="J302" s="29" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C303" s="28"/>
+      <c r="D303" s="28"/>
+      <c r="E303" s="28"/>
+      <c r="G303" s="29" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="H303" s="29" t="str">
+        <f t="shared" ca="1" si="18"/>
+        <v/>
+      </c>
+      <c r="I303" s="29" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="J303" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7638,7 +7865,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7648,112 +7875,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="23" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="24" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="24" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="24" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="24" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>37</v>
       </c>
     </row>

--- a/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
+++ b/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="94">
   <si>
     <t>PEDIDOS DE CAMISAS 2026</t>
   </si>
@@ -551,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,9 +619,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -638,33 +635,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="21">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -735,33 +735,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaPacotes" displayName="TabelaPacotes" ref="A1:J11" headerRowDxfId="10" dataDxfId="8" totalsRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaPacotes" displayName="TabelaPacotes" ref="A1:J11" headerRowDxfId="11" dataDxfId="9" totalsRowDxfId="10">
   <autoFilter ref="A1:J11"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="Pacote" dataDxfId="19"/>
-    <tableColumn id="10" name="Código de Rastreio" dataDxfId="7"/>
-    <tableColumn id="2" name="Data do pedido" dataDxfId="18"/>
-    <tableColumn id="3" name="Data do envio" dataDxfId="17"/>
-    <tableColumn id="4" name="Data de recebimento" dataDxfId="16"/>
-    <tableColumn id="5" name="Status" dataDxfId="15"/>
-    <tableColumn id="6" name="Dias desde pedido" dataDxfId="14"/>
-    <tableColumn id="7" name="Dias desde envio" dataDxfId="13"/>
-    <tableColumn id="8" name="Dias pedido→envio" dataDxfId="12"/>
-    <tableColumn id="9" name="Duração importação (envio→receb.)" dataDxfId="11"/>
+    <tableColumn id="1" name="Pacote" dataDxfId="20"/>
+    <tableColumn id="10" name="Código de Rastreio" dataDxfId="8"/>
+    <tableColumn id="2" name="Data do pedido" dataDxfId="19"/>
+    <tableColumn id="3" name="Data do envio" dataDxfId="18"/>
+    <tableColumn id="4" name="Data de recebimento" dataDxfId="17"/>
+    <tableColumn id="5" name="Status" dataDxfId="16"/>
+    <tableColumn id="6" name="Dias desde pedido" dataDxfId="15"/>
+    <tableColumn id="7" name="Dias desde envio" dataDxfId="14"/>
+    <tableColumn id="8" name="Dias pedido→envio" dataDxfId="13"/>
+    <tableColumn id="9" name="Duração importação (envio→receb.)" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela3" displayName="Tabela3" ref="C2:G37" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="C2:G37"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Pacote " dataDxfId="4"/>
-    <tableColumn id="2" name="Camisa" dataDxfId="2"/>
-    <tableColumn id="3" name="Tamanho" dataDxfId="3"/>
-    <tableColumn id="5" name="QUANT" dataDxfId="1"/>
-    <tableColumn id="4" name="Cliente" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela3" displayName="Tabela3" ref="C2:H37" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="C2:H37"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Pacote " dataDxfId="7"/>
+    <tableColumn id="6" name="Código de Rastreio" dataDxfId="6"/>
+    <tableColumn id="2" name="Camisa" dataDxfId="5"/>
+    <tableColumn id="3" name="Tamanho" dataDxfId="4"/>
+    <tableColumn id="5" name="QUANT" dataDxfId="3"/>
+    <tableColumn id="4" name="Cliente" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1535,4488 +1536,4488 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="25">
         <v>33</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="27">
+      <c r="B2" s="25"/>
+      <c r="C2" s="26">
         <v>46036</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="26">
         <v>46038</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="26">
         <v>46058</v>
       </c>
-      <c r="F2" s="26" t="str">
+      <c r="F2" s="25" t="str">
         <f t="shared" ref="F2:F11" si="0">IF(E2="","Em trânsito","Recebido")</f>
         <v>Recebido</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <f t="shared" ref="G2:G12" ca="1" si="1">IF(C2="","",IF(F2="Recebido",E2-C2,TODAY()-C2))</f>
         <v>22</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <f t="shared" ref="H2:H12" ca="1" si="2">IF(D2="","",IF(F2="Recebido",E2-D2,TODAY()-D2))</f>
         <v>20</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="27">
         <f t="shared" ref="I2:I12" si="3">IF(OR(C2="",D2=""),"",D2-C2)</f>
         <v>2</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="27">
         <f t="shared" ref="J2:J12" si="4">IF(OR(D2="",E2=""),"",E2-D2)</f>
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3" s="25">
         <v>34</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="27">
+      <c r="B3" s="25"/>
+      <c r="C3" s="26">
         <v>46030</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="26">
         <v>46038</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="26">
         <v>46065</v>
       </c>
-      <c r="F3" s="26" t="str">
+      <c r="F3" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Recebido</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>27</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="27">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="27">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>46049</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="26">
         <v>46051</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="26" t="str">
+      <c r="E4" s="26"/>
+      <c r="F4" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>26</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="27">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="J4" s="28" t="str">
+      <c r="J4" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>46049</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="26">
         <v>46051</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="26" t="str">
+      <c r="E5" s="26"/>
+      <c r="F5" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>26</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="27">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="J5" s="28" t="str">
+      <c r="J5" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>46049</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <v>46052</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="26" t="str">
+      <c r="E6" s="26"/>
+      <c r="F6" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>25</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="27">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="J6" s="28" t="str">
+      <c r="J6" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>46049</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="26">
         <v>46052</v>
       </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="26" t="str">
+      <c r="E7" s="26"/>
+      <c r="F7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>25</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="27">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="J7" s="28" t="str">
+      <c r="J7" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>37</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>46049</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <v>46052</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="26" t="str">
+      <c r="E8" s="26"/>
+      <c r="F8" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>25</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="J8" s="28" t="str">
+      <c r="J8" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>46051</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="26">
         <v>46052</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="26" t="str">
+      <c r="E9" s="26"/>
+      <c r="F9" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>26</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>25</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="27">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J9" s="28" t="str">
+      <c r="J9" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>46051</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <v>46052</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="26" t="str">
+      <c r="E10" s="26"/>
+      <c r="F10" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Em trânsito</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>26</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>25</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="27">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J10" s="28" t="str">
+      <c r="J10" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11" s="25">
         <v>39</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="27">
+      <c r="B11" s="25"/>
+      <c r="C11" s="26">
         <v>46056</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="26">
         <v>46062</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="26">
         <v>46073</v>
       </c>
-      <c r="F11" s="26" t="str">
+      <c r="F11" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Recebido</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="27">
         <f t="shared" ca="1" si="1"/>
         <v>17</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="27">
         <f t="shared" ca="1" si="2"/>
         <v>11</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="27">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="27">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="G12" s="30" t="str">
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="G12" s="29" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="H12" s="30" t="str">
+      <c r="H12" s="29" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="I12" s="30" t="str">
+      <c r="I12" s="29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J12" s="30" t="str">
+      <c r="J12" s="29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="G13" s="30" t="str">
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="G13" s="29" t="str">
         <f t="shared" ref="G13:G37" ca="1" si="5">IF(C13="","",IF(F13="Recebido",E13-C13,TODAY()-C13))</f>
         <v/>
       </c>
-      <c r="H13" s="30" t="str">
+      <c r="H13" s="29" t="str">
         <f t="shared" ref="H13:H37" ca="1" si="6">IF(D13="","",IF(F13="Recebido",E13-D13,TODAY()-D13))</f>
         <v/>
       </c>
-      <c r="I13" s="30" t="str">
+      <c r="I13" s="29" t="str">
         <f t="shared" ref="I13:I37" si="7">IF(OR(C13="",D13=""),"",D13-C13)</f>
         <v/>
       </c>
-      <c r="J13" s="30" t="str">
+      <c r="J13" s="29" t="str">
         <f t="shared" ref="J13:J37" si="8">IF(OR(D13="",E13=""),"",E13-D13)</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="G14" s="30" t="str">
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="G14" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H14" s="30" t="str">
+      <c r="H14" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I14" s="30" t="str">
+      <c r="I14" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J14" s="30" t="str">
+      <c r="J14" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="G15" s="30" t="str">
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="G15" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H15" s="30" t="str">
+      <c r="H15" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I15" s="30" t="str">
+      <c r="I15" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J15" s="30" t="str">
+      <c r="J15" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="G16" s="30" t="str">
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="G16" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H16" s="30" t="str">
+      <c r="H16" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I16" s="30" t="str">
+      <c r="I16" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J16" s="30" t="str">
+      <c r="J16" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="G17" s="30" t="str">
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="G17" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H17" s="30" t="str">
+      <c r="H17" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I17" s="30" t="str">
+      <c r="I17" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J17" s="30" t="str">
+      <c r="J17" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="G18" s="30" t="str">
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="G18" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H18" s="30" t="str">
+      <c r="H18" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I18" s="30" t="str">
+      <c r="I18" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J18" s="30" t="str">
+      <c r="J18" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="G19" s="30" t="str">
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="G19" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H19" s="30" t="str">
+      <c r="H19" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I19" s="30" t="str">
+      <c r="I19" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J19" s="30" t="str">
+      <c r="J19" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="G20" s="30" t="str">
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="G20" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H20" s="30" t="str">
+      <c r="H20" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I20" s="30" t="str">
+      <c r="I20" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J20" s="30" t="str">
+      <c r="J20" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="G21" s="30" t="str">
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="G21" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H21" s="30" t="str">
+      <c r="H21" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I21" s="30" t="str">
+      <c r="I21" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J21" s="30" t="str">
+      <c r="J21" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="G22" s="30" t="str">
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="G22" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H22" s="30" t="str">
+      <c r="H22" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I22" s="30" t="str">
+      <c r="I22" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J22" s="30" t="str">
+      <c r="J22" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="G23" s="30" t="str">
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="G23" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H23" s="30" t="str">
+      <c r="H23" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I23" s="30" t="str">
+      <c r="I23" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J23" s="30" t="str">
+      <c r="J23" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="G24" s="30" t="str">
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="G24" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H24" s="30" t="str">
+      <c r="H24" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I24" s="30" t="str">
+      <c r="I24" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J24" s="30" t="str">
+      <c r="J24" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="G25" s="30" t="str">
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="G25" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H25" s="30" t="str">
+      <c r="H25" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I25" s="30" t="str">
+      <c r="I25" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J25" s="30" t="str">
+      <c r="J25" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="G26" s="30" t="str">
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="G26" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H26" s="30" t="str">
+      <c r="H26" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I26" s="30" t="str">
+      <c r="I26" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J26" s="30" t="str">
+      <c r="J26" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="G27" s="30" t="str">
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="G27" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H27" s="30" t="str">
+      <c r="H27" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I27" s="30" t="str">
+      <c r="I27" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J27" s="30" t="str">
+      <c r="J27" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="G28" s="30" t="str">
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="G28" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H28" s="30" t="str">
+      <c r="H28" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I28" s="30" t="str">
+      <c r="I28" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J28" s="30" t="str">
+      <c r="J28" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="G29" s="30" t="str">
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="G29" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H29" s="30" t="str">
+      <c r="H29" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I29" s="30" t="str">
+      <c r="I29" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J29" s="30" t="str">
+      <c r="J29" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="G30" s="30" t="str">
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="G30" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H30" s="30" t="str">
+      <c r="H30" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I30" s="30" t="str">
+      <c r="I30" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J30" s="30" t="str">
+      <c r="J30" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="G31" s="30" t="str">
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="G31" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H31" s="30" t="str">
+      <c r="H31" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I31" s="30" t="str">
+      <c r="I31" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J31" s="30" t="str">
+      <c r="J31" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="G32" s="30" t="str">
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="G32" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H32" s="30" t="str">
+      <c r="H32" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I32" s="30" t="str">
+      <c r="I32" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J32" s="30" t="str">
+      <c r="J32" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="G33" s="30" t="str">
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="G33" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H33" s="30" t="str">
+      <c r="H33" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I33" s="30" t="str">
+      <c r="I33" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J33" s="30" t="str">
+      <c r="J33" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="G34" s="30" t="str">
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="G34" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H34" s="30" t="str">
+      <c r="H34" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I34" s="30" t="str">
+      <c r="I34" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J34" s="30" t="str">
+      <c r="J34" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="G35" s="30" t="str">
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="G35" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H35" s="30" t="str">
+      <c r="H35" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I35" s="30" t="str">
+      <c r="I35" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J35" s="30" t="str">
+      <c r="J35" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="G36" s="30" t="str">
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="G36" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H36" s="30" t="str">
+      <c r="H36" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I36" s="30" t="str">
+      <c r="I36" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J36" s="30" t="str">
+      <c r="J36" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="G37" s="30" t="str">
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="G37" s="29" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="H37" s="30" t="str">
+      <c r="H37" s="29" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="I37" s="30" t="str">
+      <c r="I37" s="29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J37" s="30" t="str">
+      <c r="J37" s="29" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="G38" s="30" t="str">
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="G38" s="29" t="str">
         <f t="shared" ref="G38:G101" ca="1" si="9">IF(C38="","",IF(F38="Recebido",E38-C38,TODAY()-C38))</f>
         <v/>
       </c>
-      <c r="H38" s="30" t="str">
+      <c r="H38" s="29" t="str">
         <f t="shared" ref="H38:H101" ca="1" si="10">IF(D38="","",IF(F38="Recebido",E38-D38,TODAY()-D38))</f>
         <v/>
       </c>
-      <c r="I38" s="30" t="str">
+      <c r="I38" s="29" t="str">
         <f t="shared" ref="I38:I101" si="11">IF(OR(C38="",D38=""),"",D38-C38)</f>
         <v/>
       </c>
-      <c r="J38" s="30" t="str">
+      <c r="J38" s="29" t="str">
         <f t="shared" ref="J38:J101" si="12">IF(OR(D38="",E38=""),"",E38-D38)</f>
         <v/>
       </c>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="G39" s="30" t="str">
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="G39" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H39" s="30" t="str">
+      <c r="H39" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I39" s="30" t="str">
+      <c r="I39" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J39" s="30" t="str">
+      <c r="J39" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="G40" s="30" t="str">
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="G40" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H40" s="30" t="str">
+      <c r="H40" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I40" s="30" t="str">
+      <c r="I40" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J40" s="30" t="str">
+      <c r="J40" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="G41" s="30" t="str">
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="G41" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H41" s="30" t="str">
+      <c r="H41" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I41" s="30" t="str">
+      <c r="I41" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J41" s="30" t="str">
+      <c r="J41" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="G42" s="30" t="str">
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="G42" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H42" s="30" t="str">
+      <c r="H42" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I42" s="30" t="str">
+      <c r="I42" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J42" s="30" t="str">
+      <c r="J42" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="G43" s="30" t="str">
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="G43" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H43" s="30" t="str">
+      <c r="H43" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I43" s="30" t="str">
+      <c r="I43" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J43" s="30" t="str">
+      <c r="J43" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="G44" s="30" t="str">
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="G44" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H44" s="30" t="str">
+      <c r="H44" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I44" s="30" t="str">
+      <c r="I44" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J44" s="30" t="str">
+      <c r="J44" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="G45" s="30" t="str">
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="G45" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H45" s="30" t="str">
+      <c r="H45" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I45" s="30" t="str">
+      <c r="I45" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J45" s="30" t="str">
+      <c r="J45" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="G46" s="30" t="str">
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="G46" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H46" s="30" t="str">
+      <c r="H46" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I46" s="30" t="str">
+      <c r="I46" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J46" s="30" t="str">
+      <c r="J46" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="G47" s="30" t="str">
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="G47" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H47" s="30" t="str">
+      <c r="H47" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I47" s="30" t="str">
+      <c r="I47" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J47" s="30" t="str">
+      <c r="J47" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="G48" s="30" t="str">
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="G48" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H48" s="30" t="str">
+      <c r="H48" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I48" s="30" t="str">
+      <c r="I48" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J48" s="30" t="str">
+      <c r="J48" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="G49" s="30" t="str">
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="G49" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H49" s="30" t="str">
+      <c r="H49" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I49" s="30" t="str">
+      <c r="I49" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J49" s="30" t="str">
+      <c r="J49" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="G50" s="30" t="str">
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="G50" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H50" s="30" t="str">
+      <c r="H50" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I50" s="30" t="str">
+      <c r="I50" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J50" s="30" t="str">
+      <c r="J50" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="G51" s="30" t="str">
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="G51" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H51" s="30" t="str">
+      <c r="H51" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I51" s="30" t="str">
+      <c r="I51" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J51" s="30" t="str">
+      <c r="J51" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="G52" s="30" t="str">
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="G52" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H52" s="30" t="str">
+      <c r="H52" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I52" s="30" t="str">
+      <c r="I52" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J52" s="30" t="str">
+      <c r="J52" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="G53" s="30" t="str">
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="G53" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H53" s="30" t="str">
+      <c r="H53" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I53" s="30" t="str">
+      <c r="I53" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J53" s="30" t="str">
+      <c r="J53" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="G54" s="30" t="str">
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="G54" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H54" s="30" t="str">
+      <c r="H54" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I54" s="30" t="str">
+      <c r="I54" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J54" s="30" t="str">
+      <c r="J54" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="G55" s="30" t="str">
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="G55" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H55" s="30" t="str">
+      <c r="H55" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I55" s="30" t="str">
+      <c r="I55" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J55" s="30" t="str">
+      <c r="J55" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="56" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="G56" s="30" t="str">
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="G56" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H56" s="30" t="str">
+      <c r="H56" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I56" s="30" t="str">
+      <c r="I56" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J56" s="30" t="str">
+      <c r="J56" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="57" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="G57" s="30" t="str">
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="G57" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H57" s="30" t="str">
+      <c r="H57" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I57" s="30" t="str">
+      <c r="I57" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J57" s="30" t="str">
+      <c r="J57" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="58" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="G58" s="30" t="str">
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="G58" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H58" s="30" t="str">
+      <c r="H58" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I58" s="30" t="str">
+      <c r="I58" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J58" s="30" t="str">
+      <c r="J58" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="59" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
-      <c r="G59" s="30" t="str">
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="G59" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H59" s="30" t="str">
+      <c r="H59" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I59" s="30" t="str">
+      <c r="I59" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J59" s="30" t="str">
+      <c r="J59" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="60" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="G60" s="30" t="str">
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="G60" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H60" s="30" t="str">
+      <c r="H60" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I60" s="30" t="str">
+      <c r="I60" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J60" s="30" t="str">
+      <c r="J60" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="61" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="G61" s="30" t="str">
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="G61" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H61" s="30" t="str">
+      <c r="H61" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I61" s="30" t="str">
+      <c r="I61" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J61" s="30" t="str">
+      <c r="J61" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="62" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
-      <c r="G62" s="30" t="str">
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="G62" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H62" s="30" t="str">
+      <c r="H62" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I62" s="30" t="str">
+      <c r="I62" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J62" s="30" t="str">
+      <c r="J62" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="63" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="G63" s="30" t="str">
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="G63" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H63" s="30" t="str">
+      <c r="H63" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I63" s="30" t="str">
+      <c r="I63" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J63" s="30" t="str">
+      <c r="J63" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="G64" s="30" t="str">
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="G64" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H64" s="30" t="str">
+      <c r="H64" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I64" s="30" t="str">
+      <c r="I64" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J64" s="30" t="str">
+      <c r="J64" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="G65" s="30" t="str">
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="G65" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H65" s="30" t="str">
+      <c r="H65" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I65" s="30" t="str">
+      <c r="I65" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J65" s="30" t="str">
+      <c r="J65" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="G66" s="30" t="str">
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="G66" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H66" s="30" t="str">
+      <c r="H66" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I66" s="30" t="str">
+      <c r="I66" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J66" s="30" t="str">
+      <c r="J66" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="G67" s="30" t="str">
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="G67" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H67" s="30" t="str">
+      <c r="H67" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I67" s="30" t="str">
+      <c r="I67" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J67" s="30" t="str">
+      <c r="J67" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="68" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="G68" s="30" t="str">
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="G68" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H68" s="30" t="str">
+      <c r="H68" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I68" s="30" t="str">
+      <c r="I68" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J68" s="30" t="str">
+      <c r="J68" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="69" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="G69" s="30" t="str">
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="G69" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H69" s="30" t="str">
+      <c r="H69" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I69" s="30" t="str">
+      <c r="I69" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J69" s="30" t="str">
+      <c r="J69" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="G70" s="30" t="str">
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="G70" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H70" s="30" t="str">
+      <c r="H70" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I70" s="30" t="str">
+      <c r="I70" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J70" s="30" t="str">
+      <c r="J70" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="71" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="G71" s="30" t="str">
+      <c r="C71" s="28"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
+      <c r="G71" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H71" s="30" t="str">
+      <c r="H71" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I71" s="30" t="str">
+      <c r="I71" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J71" s="30" t="str">
+      <c r="J71" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="72" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="G72" s="30" t="str">
+      <c r="C72" s="28"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="G72" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H72" s="30" t="str">
+      <c r="H72" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I72" s="30" t="str">
+      <c r="I72" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J72" s="30" t="str">
+      <c r="J72" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="73" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="G73" s="30" t="str">
+      <c r="C73" s="28"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="G73" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H73" s="30" t="str">
+      <c r="H73" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I73" s="30" t="str">
+      <c r="I73" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J73" s="30" t="str">
+      <c r="J73" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="74" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="G74" s="30" t="str">
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="G74" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H74" s="30" t="str">
+      <c r="H74" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I74" s="30" t="str">
+      <c r="I74" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J74" s="30" t="str">
+      <c r="J74" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
-      <c r="G75" s="30" t="str">
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="G75" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H75" s="30" t="str">
+      <c r="H75" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I75" s="30" t="str">
+      <c r="I75" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J75" s="30" t="str">
+      <c r="J75" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="76" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="G76" s="30" t="str">
+      <c r="C76" s="28"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="G76" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H76" s="30" t="str">
+      <c r="H76" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I76" s="30" t="str">
+      <c r="I76" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J76" s="30" t="str">
+      <c r="J76" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="G77" s="30" t="str">
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
+      <c r="G77" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H77" s="30" t="str">
+      <c r="H77" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I77" s="30" t="str">
+      <c r="I77" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J77" s="30" t="str">
+      <c r="J77" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C78" s="29"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="29"/>
-      <c r="G78" s="30" t="str">
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="G78" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H78" s="30" t="str">
+      <c r="H78" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I78" s="30" t="str">
+      <c r="I78" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J78" s="30" t="str">
+      <c r="J78" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
-      <c r="G79" s="30" t="str">
+      <c r="C79" s="28"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="G79" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H79" s="30" t="str">
+      <c r="H79" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I79" s="30" t="str">
+      <c r="I79" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J79" s="30" t="str">
+      <c r="J79" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C80" s="29"/>
-      <c r="D80" s="29"/>
-      <c r="E80" s="29"/>
-      <c r="G80" s="30" t="str">
+      <c r="C80" s="28"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="28"/>
+      <c r="G80" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H80" s="30" t="str">
+      <c r="H80" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I80" s="30" t="str">
+      <c r="I80" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J80" s="30" t="str">
+      <c r="J80" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
-      <c r="E81" s="29"/>
-      <c r="G81" s="30" t="str">
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
+      <c r="G81" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H81" s="30" t="str">
+      <c r="H81" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I81" s="30" t="str">
+      <c r="I81" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J81" s="30" t="str">
+      <c r="J81" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C82" s="29"/>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="G82" s="30" t="str">
+      <c r="C82" s="28"/>
+      <c r="D82" s="28"/>
+      <c r="E82" s="28"/>
+      <c r="G82" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H82" s="30" t="str">
+      <c r="H82" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I82" s="30" t="str">
+      <c r="I82" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J82" s="30" t="str">
+      <c r="J82" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="G83" s="30" t="str">
+      <c r="C83" s="28"/>
+      <c r="D83" s="28"/>
+      <c r="E83" s="28"/>
+      <c r="G83" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H83" s="30" t="str">
+      <c r="H83" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I83" s="30" t="str">
+      <c r="I83" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J83" s="30" t="str">
+      <c r="J83" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C84" s="29"/>
-      <c r="D84" s="29"/>
-      <c r="E84" s="29"/>
-      <c r="G84" s="30" t="str">
+      <c r="C84" s="28"/>
+      <c r="D84" s="28"/>
+      <c r="E84" s="28"/>
+      <c r="G84" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H84" s="30" t="str">
+      <c r="H84" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I84" s="30" t="str">
+      <c r="I84" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J84" s="30" t="str">
+      <c r="J84" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
-      <c r="G85" s="30" t="str">
+      <c r="C85" s="28"/>
+      <c r="D85" s="28"/>
+      <c r="E85" s="28"/>
+      <c r="G85" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H85" s="30" t="str">
+      <c r="H85" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I85" s="30" t="str">
+      <c r="I85" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J85" s="30" t="str">
+      <c r="J85" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="86" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C86" s="29"/>
-      <c r="D86" s="29"/>
-      <c r="E86" s="29"/>
-      <c r="G86" s="30" t="str">
+      <c r="C86" s="28"/>
+      <c r="D86" s="28"/>
+      <c r="E86" s="28"/>
+      <c r="G86" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H86" s="30" t="str">
+      <c r="H86" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I86" s="30" t="str">
+      <c r="I86" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J86" s="30" t="str">
+      <c r="J86" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="87" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C87" s="29"/>
-      <c r="D87" s="29"/>
-      <c r="E87" s="29"/>
-      <c r="G87" s="30" t="str">
+      <c r="C87" s="28"/>
+      <c r="D87" s="28"/>
+      <c r="E87" s="28"/>
+      <c r="G87" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H87" s="30" t="str">
+      <c r="H87" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I87" s="30" t="str">
+      <c r="I87" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J87" s="30" t="str">
+      <c r="J87" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="88" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C88" s="29"/>
-      <c r="D88" s="29"/>
-      <c r="E88" s="29"/>
-      <c r="G88" s="30" t="str">
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
+      <c r="G88" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H88" s="30" t="str">
+      <c r="H88" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I88" s="30" t="str">
+      <c r="I88" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J88" s="30" t="str">
+      <c r="J88" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="89" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C89" s="29"/>
-      <c r="D89" s="29"/>
-      <c r="E89" s="29"/>
-      <c r="G89" s="30" t="str">
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="G89" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H89" s="30" t="str">
+      <c r="H89" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I89" s="30" t="str">
+      <c r="I89" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J89" s="30" t="str">
+      <c r="J89" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="90" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C90" s="29"/>
-      <c r="D90" s="29"/>
-      <c r="E90" s="29"/>
-      <c r="G90" s="30" t="str">
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="G90" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H90" s="30" t="str">
+      <c r="H90" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I90" s="30" t="str">
+      <c r="I90" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J90" s="30" t="str">
+      <c r="J90" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="91" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
-      <c r="E91" s="29"/>
-      <c r="G91" s="30" t="str">
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="28"/>
+      <c r="G91" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H91" s="30" t="str">
+      <c r="H91" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I91" s="30" t="str">
+      <c r="I91" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J91" s="30" t="str">
+      <c r="J91" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="92" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C92" s="29"/>
-      <c r="D92" s="29"/>
-      <c r="E92" s="29"/>
-      <c r="G92" s="30" t="str">
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
+      <c r="G92" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H92" s="30" t="str">
+      <c r="H92" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I92" s="30" t="str">
+      <c r="I92" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J92" s="30" t="str">
+      <c r="J92" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="93" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="29"/>
-      <c r="G93" s="30" t="str">
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="G93" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H93" s="30" t="str">
+      <c r="H93" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I93" s="30" t="str">
+      <c r="I93" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J93" s="30" t="str">
+      <c r="J93" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="94" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C94" s="29"/>
-      <c r="D94" s="29"/>
-      <c r="E94" s="29"/>
-      <c r="G94" s="30" t="str">
+      <c r="C94" s="28"/>
+      <c r="D94" s="28"/>
+      <c r="E94" s="28"/>
+      <c r="G94" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H94" s="30" t="str">
+      <c r="H94" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I94" s="30" t="str">
+      <c r="I94" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J94" s="30" t="str">
+      <c r="J94" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C95" s="29"/>
-      <c r="D95" s="29"/>
-      <c r="E95" s="29"/>
-      <c r="G95" s="30" t="str">
+      <c r="C95" s="28"/>
+      <c r="D95" s="28"/>
+      <c r="E95" s="28"/>
+      <c r="G95" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H95" s="30" t="str">
+      <c r="H95" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I95" s="30" t="str">
+      <c r="I95" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J95" s="30" t="str">
+      <c r="J95" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="96" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C96" s="29"/>
-      <c r="D96" s="29"/>
-      <c r="E96" s="29"/>
-      <c r="G96" s="30" t="str">
+      <c r="C96" s="28"/>
+      <c r="D96" s="28"/>
+      <c r="E96" s="28"/>
+      <c r="G96" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H96" s="30" t="str">
+      <c r="H96" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I96" s="30" t="str">
+      <c r="I96" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J96" s="30" t="str">
+      <c r="J96" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="97" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C97" s="29"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="29"/>
-      <c r="G97" s="30" t="str">
+      <c r="C97" s="28"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="28"/>
+      <c r="G97" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H97" s="30" t="str">
+      <c r="H97" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I97" s="30" t="str">
+      <c r="I97" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J97" s="30" t="str">
+      <c r="J97" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="98" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C98" s="29"/>
-      <c r="D98" s="29"/>
-      <c r="E98" s="29"/>
-      <c r="G98" s="30" t="str">
+      <c r="C98" s="28"/>
+      <c r="D98" s="28"/>
+      <c r="E98" s="28"/>
+      <c r="G98" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H98" s="30" t="str">
+      <c r="H98" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I98" s="30" t="str">
+      <c r="I98" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J98" s="30" t="str">
+      <c r="J98" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="99" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C99" s="29"/>
-      <c r="D99" s="29"/>
-      <c r="E99" s="29"/>
-      <c r="G99" s="30" t="str">
+      <c r="C99" s="28"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="28"/>
+      <c r="G99" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H99" s="30" t="str">
+      <c r="H99" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I99" s="30" t="str">
+      <c r="I99" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J99" s="30" t="str">
+      <c r="J99" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="100" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C100" s="29"/>
-      <c r="D100" s="29"/>
-      <c r="E100" s="29"/>
-      <c r="G100" s="30" t="str">
+      <c r="C100" s="28"/>
+      <c r="D100" s="28"/>
+      <c r="E100" s="28"/>
+      <c r="G100" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H100" s="30" t="str">
+      <c r="H100" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I100" s="30" t="str">
+      <c r="I100" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J100" s="30" t="str">
+      <c r="J100" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="101" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C101" s="29"/>
-      <c r="D101" s="29"/>
-      <c r="E101" s="29"/>
-      <c r="G101" s="30" t="str">
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="G101" s="29" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="H101" s="30" t="str">
+      <c r="H101" s="29" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="I101" s="30" t="str">
+      <c r="I101" s="29" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J101" s="30" t="str">
+      <c r="J101" s="29" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="102" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C102" s="29"/>
-      <c r="D102" s="29"/>
-      <c r="E102" s="29"/>
-      <c r="G102" s="30" t="str">
+      <c r="C102" s="28"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="28"/>
+      <c r="G102" s="29" t="str">
         <f t="shared" ref="G102:G165" ca="1" si="13">IF(C102="","",IF(F102="Recebido",E102-C102,TODAY()-C102))</f>
         <v/>
       </c>
-      <c r="H102" s="30" t="str">
+      <c r="H102" s="29" t="str">
         <f t="shared" ref="H102:H165" ca="1" si="14">IF(D102="","",IF(F102="Recebido",E102-D102,TODAY()-D102))</f>
         <v/>
       </c>
-      <c r="I102" s="30" t="str">
+      <c r="I102" s="29" t="str">
         <f t="shared" ref="I102:I165" si="15">IF(OR(C102="",D102=""),"",D102-C102)</f>
         <v/>
       </c>
-      <c r="J102" s="30" t="str">
+      <c r="J102" s="29" t="str">
         <f t="shared" ref="J102:J165" si="16">IF(OR(D102="",E102=""),"",E102-D102)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C103" s="29"/>
-      <c r="D103" s="29"/>
-      <c r="E103" s="29"/>
-      <c r="G103" s="30" t="str">
+      <c r="C103" s="28"/>
+      <c r="D103" s="28"/>
+      <c r="E103" s="28"/>
+      <c r="G103" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H103" s="30" t="str">
+      <c r="H103" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I103" s="30" t="str">
+      <c r="I103" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J103" s="30" t="str">
+      <c r="J103" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="104" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C104" s="29"/>
-      <c r="D104" s="29"/>
-      <c r="E104" s="29"/>
-      <c r="G104" s="30" t="str">
+      <c r="C104" s="28"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="28"/>
+      <c r="G104" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H104" s="30" t="str">
+      <c r="H104" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I104" s="30" t="str">
+      <c r="I104" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J104" s="30" t="str">
+      <c r="J104" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="105" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C105" s="29"/>
-      <c r="D105" s="29"/>
-      <c r="E105" s="29"/>
-      <c r="G105" s="30" t="str">
+      <c r="C105" s="28"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="28"/>
+      <c r="G105" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H105" s="30" t="str">
+      <c r="H105" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I105" s="30" t="str">
+      <c r="I105" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J105" s="30" t="str">
+      <c r="J105" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="106" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C106" s="29"/>
-      <c r="D106" s="29"/>
-      <c r="E106" s="29"/>
-      <c r="G106" s="30" t="str">
+      <c r="C106" s="28"/>
+      <c r="D106" s="28"/>
+      <c r="E106" s="28"/>
+      <c r="G106" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H106" s="30" t="str">
+      <c r="H106" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I106" s="30" t="str">
+      <c r="I106" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J106" s="30" t="str">
+      <c r="J106" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="107" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C107" s="29"/>
-      <c r="D107" s="29"/>
-      <c r="E107" s="29"/>
-      <c r="G107" s="30" t="str">
+      <c r="C107" s="28"/>
+      <c r="D107" s="28"/>
+      <c r="E107" s="28"/>
+      <c r="G107" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H107" s="30" t="str">
+      <c r="H107" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I107" s="30" t="str">
+      <c r="I107" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J107" s="30" t="str">
+      <c r="J107" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="108" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C108" s="29"/>
-      <c r="D108" s="29"/>
-      <c r="E108" s="29"/>
-      <c r="G108" s="30" t="str">
+      <c r="C108" s="28"/>
+      <c r="D108" s="28"/>
+      <c r="E108" s="28"/>
+      <c r="G108" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H108" s="30" t="str">
+      <c r="H108" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I108" s="30" t="str">
+      <c r="I108" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J108" s="30" t="str">
+      <c r="J108" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="109" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C109" s="29"/>
-      <c r="D109" s="29"/>
-      <c r="E109" s="29"/>
-      <c r="G109" s="30" t="str">
+      <c r="C109" s="28"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="28"/>
+      <c r="G109" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H109" s="30" t="str">
+      <c r="H109" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I109" s="30" t="str">
+      <c r="I109" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J109" s="30" t="str">
+      <c r="J109" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C110" s="29"/>
-      <c r="D110" s="29"/>
-      <c r="E110" s="29"/>
-      <c r="G110" s="30" t="str">
+      <c r="C110" s="28"/>
+      <c r="D110" s="28"/>
+      <c r="E110" s="28"/>
+      <c r="G110" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H110" s="30" t="str">
+      <c r="H110" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I110" s="30" t="str">
+      <c r="I110" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J110" s="30" t="str">
+      <c r="J110" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="111" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C111" s="29"/>
-      <c r="D111" s="29"/>
-      <c r="E111" s="29"/>
-      <c r="G111" s="30" t="str">
+      <c r="C111" s="28"/>
+      <c r="D111" s="28"/>
+      <c r="E111" s="28"/>
+      <c r="G111" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H111" s="30" t="str">
+      <c r="H111" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I111" s="30" t="str">
+      <c r="I111" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J111" s="30" t="str">
+      <c r="J111" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="112" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
-      <c r="E112" s="29"/>
-      <c r="G112" s="30" t="str">
+      <c r="C112" s="28"/>
+      <c r="D112" s="28"/>
+      <c r="E112" s="28"/>
+      <c r="G112" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H112" s="30" t="str">
+      <c r="H112" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I112" s="30" t="str">
+      <c r="I112" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J112" s="30" t="str">
+      <c r="J112" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="113" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C113" s="29"/>
-      <c r="D113" s="29"/>
-      <c r="E113" s="29"/>
-      <c r="G113" s="30" t="str">
+      <c r="C113" s="28"/>
+      <c r="D113" s="28"/>
+      <c r="E113" s="28"/>
+      <c r="G113" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H113" s="30" t="str">
+      <c r="H113" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I113" s="30" t="str">
+      <c r="I113" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J113" s="30" t="str">
+      <c r="J113" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="114" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C114" s="29"/>
-      <c r="D114" s="29"/>
-      <c r="E114" s="29"/>
-      <c r="G114" s="30" t="str">
+      <c r="C114" s="28"/>
+      <c r="D114" s="28"/>
+      <c r="E114" s="28"/>
+      <c r="G114" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H114" s="30" t="str">
+      <c r="H114" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I114" s="30" t="str">
+      <c r="I114" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J114" s="30" t="str">
+      <c r="J114" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="115" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C115" s="29"/>
-      <c r="D115" s="29"/>
-      <c r="E115" s="29"/>
-      <c r="G115" s="30" t="str">
+      <c r="C115" s="28"/>
+      <c r="D115" s="28"/>
+      <c r="E115" s="28"/>
+      <c r="G115" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H115" s="30" t="str">
+      <c r="H115" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I115" s="30" t="str">
+      <c r="I115" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J115" s="30" t="str">
+      <c r="J115" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="116" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C116" s="29"/>
-      <c r="D116" s="29"/>
-      <c r="E116" s="29"/>
-      <c r="G116" s="30" t="str">
+      <c r="C116" s="28"/>
+      <c r="D116" s="28"/>
+      <c r="E116" s="28"/>
+      <c r="G116" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H116" s="30" t="str">
+      <c r="H116" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I116" s="30" t="str">
+      <c r="I116" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J116" s="30" t="str">
+      <c r="J116" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="117" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C117" s="29"/>
-      <c r="D117" s="29"/>
-      <c r="E117" s="29"/>
-      <c r="G117" s="30" t="str">
+      <c r="C117" s="28"/>
+      <c r="D117" s="28"/>
+      <c r="E117" s="28"/>
+      <c r="G117" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H117" s="30" t="str">
+      <c r="H117" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I117" s="30" t="str">
+      <c r="I117" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J117" s="30" t="str">
+      <c r="J117" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="118" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C118" s="29"/>
-      <c r="D118" s="29"/>
-      <c r="E118" s="29"/>
-      <c r="G118" s="30" t="str">
+      <c r="C118" s="28"/>
+      <c r="D118" s="28"/>
+      <c r="E118" s="28"/>
+      <c r="G118" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H118" s="30" t="str">
+      <c r="H118" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I118" s="30" t="str">
+      <c r="I118" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J118" s="30" t="str">
+      <c r="J118" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="119" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C119" s="29"/>
-      <c r="D119" s="29"/>
-      <c r="E119" s="29"/>
-      <c r="G119" s="30" t="str">
+      <c r="C119" s="28"/>
+      <c r="D119" s="28"/>
+      <c r="E119" s="28"/>
+      <c r="G119" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H119" s="30" t="str">
+      <c r="H119" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I119" s="30" t="str">
+      <c r="I119" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J119" s="30" t="str">
+      <c r="J119" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="120" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C120" s="29"/>
-      <c r="D120" s="29"/>
-      <c r="E120" s="29"/>
-      <c r="G120" s="30" t="str">
+      <c r="C120" s="28"/>
+      <c r="D120" s="28"/>
+      <c r="E120" s="28"/>
+      <c r="G120" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H120" s="30" t="str">
+      <c r="H120" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I120" s="30" t="str">
+      <c r="I120" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J120" s="30" t="str">
+      <c r="J120" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="121" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C121" s="29"/>
-      <c r="D121" s="29"/>
-      <c r="E121" s="29"/>
-      <c r="G121" s="30" t="str">
+      <c r="C121" s="28"/>
+      <c r="D121" s="28"/>
+      <c r="E121" s="28"/>
+      <c r="G121" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H121" s="30" t="str">
+      <c r="H121" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I121" s="30" t="str">
+      <c r="I121" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J121" s="30" t="str">
+      <c r="J121" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="122" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C122" s="29"/>
-      <c r="D122" s="29"/>
-      <c r="E122" s="29"/>
-      <c r="G122" s="30" t="str">
+      <c r="C122" s="28"/>
+      <c r="D122" s="28"/>
+      <c r="E122" s="28"/>
+      <c r="G122" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H122" s="30" t="str">
+      <c r="H122" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I122" s="30" t="str">
+      <c r="I122" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J122" s="30" t="str">
+      <c r="J122" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="123" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C123" s="29"/>
-      <c r="D123" s="29"/>
-      <c r="E123" s="29"/>
-      <c r="G123" s="30" t="str">
+      <c r="C123" s="28"/>
+      <c r="D123" s="28"/>
+      <c r="E123" s="28"/>
+      <c r="G123" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H123" s="30" t="str">
+      <c r="H123" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I123" s="30" t="str">
+      <c r="I123" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J123" s="30" t="str">
+      <c r="J123" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="124" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C124" s="29"/>
-      <c r="D124" s="29"/>
-      <c r="E124" s="29"/>
-      <c r="G124" s="30" t="str">
+      <c r="C124" s="28"/>
+      <c r="D124" s="28"/>
+      <c r="E124" s="28"/>
+      <c r="G124" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H124" s="30" t="str">
+      <c r="H124" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I124" s="30" t="str">
+      <c r="I124" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J124" s="30" t="str">
+      <c r="J124" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="125" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C125" s="29"/>
-      <c r="D125" s="29"/>
-      <c r="E125" s="29"/>
-      <c r="G125" s="30" t="str">
+      <c r="C125" s="28"/>
+      <c r="D125" s="28"/>
+      <c r="E125" s="28"/>
+      <c r="G125" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H125" s="30" t="str">
+      <c r="H125" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I125" s="30" t="str">
+      <c r="I125" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J125" s="30" t="str">
+      <c r="J125" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="126" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C126" s="29"/>
-      <c r="D126" s="29"/>
-      <c r="E126" s="29"/>
-      <c r="G126" s="30" t="str">
+      <c r="C126" s="28"/>
+      <c r="D126" s="28"/>
+      <c r="E126" s="28"/>
+      <c r="G126" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H126" s="30" t="str">
+      <c r="H126" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I126" s="30" t="str">
+      <c r="I126" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J126" s="30" t="str">
+      <c r="J126" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="127" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C127" s="29"/>
-      <c r="D127" s="29"/>
-      <c r="E127" s="29"/>
-      <c r="G127" s="30" t="str">
+      <c r="C127" s="28"/>
+      <c r="D127" s="28"/>
+      <c r="E127" s="28"/>
+      <c r="G127" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H127" s="30" t="str">
+      <c r="H127" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I127" s="30" t="str">
+      <c r="I127" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J127" s="30" t="str">
+      <c r="J127" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="128" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C128" s="29"/>
-      <c r="D128" s="29"/>
-      <c r="E128" s="29"/>
-      <c r="G128" s="30" t="str">
+      <c r="C128" s="28"/>
+      <c r="D128" s="28"/>
+      <c r="E128" s="28"/>
+      <c r="G128" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H128" s="30" t="str">
+      <c r="H128" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I128" s="30" t="str">
+      <c r="I128" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J128" s="30" t="str">
+      <c r="J128" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="129" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C129" s="29"/>
-      <c r="D129" s="29"/>
-      <c r="E129" s="29"/>
-      <c r="G129" s="30" t="str">
+      <c r="C129" s="28"/>
+      <c r="D129" s="28"/>
+      <c r="E129" s="28"/>
+      <c r="G129" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H129" s="30" t="str">
+      <c r="H129" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I129" s="30" t="str">
+      <c r="I129" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J129" s="30" t="str">
+      <c r="J129" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="130" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C130" s="29"/>
-      <c r="D130" s="29"/>
-      <c r="E130" s="29"/>
-      <c r="G130" s="30" t="str">
+      <c r="C130" s="28"/>
+      <c r="D130" s="28"/>
+      <c r="E130" s="28"/>
+      <c r="G130" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H130" s="30" t="str">
+      <c r="H130" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I130" s="30" t="str">
+      <c r="I130" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J130" s="30" t="str">
+      <c r="J130" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="131" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C131" s="29"/>
-      <c r="D131" s="29"/>
-      <c r="E131" s="29"/>
-      <c r="G131" s="30" t="str">
+      <c r="C131" s="28"/>
+      <c r="D131" s="28"/>
+      <c r="E131" s="28"/>
+      <c r="G131" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H131" s="30" t="str">
+      <c r="H131" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I131" s="30" t="str">
+      <c r="I131" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J131" s="30" t="str">
+      <c r="J131" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="132" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C132" s="29"/>
-      <c r="D132" s="29"/>
-      <c r="E132" s="29"/>
-      <c r="G132" s="30" t="str">
+      <c r="C132" s="28"/>
+      <c r="D132" s="28"/>
+      <c r="E132" s="28"/>
+      <c r="G132" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H132" s="30" t="str">
+      <c r="H132" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I132" s="30" t="str">
+      <c r="I132" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J132" s="30" t="str">
+      <c r="J132" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="133" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C133" s="29"/>
-      <c r="D133" s="29"/>
-      <c r="E133" s="29"/>
-      <c r="G133" s="30" t="str">
+      <c r="C133" s="28"/>
+      <c r="D133" s="28"/>
+      <c r="E133" s="28"/>
+      <c r="G133" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H133" s="30" t="str">
+      <c r="H133" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I133" s="30" t="str">
+      <c r="I133" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J133" s="30" t="str">
+      <c r="J133" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="134" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C134" s="29"/>
-      <c r="D134" s="29"/>
-      <c r="E134" s="29"/>
-      <c r="G134" s="30" t="str">
+      <c r="C134" s="28"/>
+      <c r="D134" s="28"/>
+      <c r="E134" s="28"/>
+      <c r="G134" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H134" s="30" t="str">
+      <c r="H134" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I134" s="30" t="str">
+      <c r="I134" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J134" s="30" t="str">
+      <c r="J134" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="135" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C135" s="29"/>
-      <c r="D135" s="29"/>
-      <c r="E135" s="29"/>
-      <c r="G135" s="30" t="str">
+      <c r="C135" s="28"/>
+      <c r="D135" s="28"/>
+      <c r="E135" s="28"/>
+      <c r="G135" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H135" s="30" t="str">
+      <c r="H135" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I135" s="30" t="str">
+      <c r="I135" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J135" s="30" t="str">
+      <c r="J135" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="136" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C136" s="29"/>
-      <c r="D136" s="29"/>
-      <c r="E136" s="29"/>
-      <c r="G136" s="30" t="str">
+      <c r="C136" s="28"/>
+      <c r="D136" s="28"/>
+      <c r="E136" s="28"/>
+      <c r="G136" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H136" s="30" t="str">
+      <c r="H136" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I136" s="30" t="str">
+      <c r="I136" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J136" s="30" t="str">
+      <c r="J136" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="137" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C137" s="29"/>
-      <c r="D137" s="29"/>
-      <c r="E137" s="29"/>
-      <c r="G137" s="30" t="str">
+      <c r="C137" s="28"/>
+      <c r="D137" s="28"/>
+      <c r="E137" s="28"/>
+      <c r="G137" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H137" s="30" t="str">
+      <c r="H137" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I137" s="30" t="str">
+      <c r="I137" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J137" s="30" t="str">
+      <c r="J137" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="138" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C138" s="29"/>
-      <c r="D138" s="29"/>
-      <c r="E138" s="29"/>
-      <c r="G138" s="30" t="str">
+      <c r="C138" s="28"/>
+      <c r="D138" s="28"/>
+      <c r="E138" s="28"/>
+      <c r="G138" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H138" s="30" t="str">
+      <c r="H138" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I138" s="30" t="str">
+      <c r="I138" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J138" s="30" t="str">
+      <c r="J138" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="139" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C139" s="29"/>
-      <c r="D139" s="29"/>
-      <c r="E139" s="29"/>
-      <c r="G139" s="30" t="str">
+      <c r="C139" s="28"/>
+      <c r="D139" s="28"/>
+      <c r="E139" s="28"/>
+      <c r="G139" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H139" s="30" t="str">
+      <c r="H139" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I139" s="30" t="str">
+      <c r="I139" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J139" s="30" t="str">
+      <c r="J139" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="140" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C140" s="29"/>
-      <c r="D140" s="29"/>
-      <c r="E140" s="29"/>
-      <c r="G140" s="30" t="str">
+      <c r="C140" s="28"/>
+      <c r="D140" s="28"/>
+      <c r="E140" s="28"/>
+      <c r="G140" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H140" s="30" t="str">
+      <c r="H140" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I140" s="30" t="str">
+      <c r="I140" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J140" s="30" t="str">
+      <c r="J140" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="141" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C141" s="29"/>
-      <c r="D141" s="29"/>
-      <c r="E141" s="29"/>
-      <c r="G141" s="30" t="str">
+      <c r="C141" s="28"/>
+      <c r="D141" s="28"/>
+      <c r="E141" s="28"/>
+      <c r="G141" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H141" s="30" t="str">
+      <c r="H141" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I141" s="30" t="str">
+      <c r="I141" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J141" s="30" t="str">
+      <c r="J141" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="142" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C142" s="29"/>
-      <c r="D142" s="29"/>
-      <c r="E142" s="29"/>
-      <c r="G142" s="30" t="str">
+      <c r="C142" s="28"/>
+      <c r="D142" s="28"/>
+      <c r="E142" s="28"/>
+      <c r="G142" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H142" s="30" t="str">
+      <c r="H142" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I142" s="30" t="str">
+      <c r="I142" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J142" s="30" t="str">
+      <c r="J142" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="143" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C143" s="29"/>
-      <c r="D143" s="29"/>
-      <c r="E143" s="29"/>
-      <c r="G143" s="30" t="str">
+      <c r="C143" s="28"/>
+      <c r="D143" s="28"/>
+      <c r="E143" s="28"/>
+      <c r="G143" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H143" s="30" t="str">
+      <c r="H143" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I143" s="30" t="str">
+      <c r="I143" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J143" s="30" t="str">
+      <c r="J143" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="144" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C144" s="29"/>
-      <c r="D144" s="29"/>
-      <c r="E144" s="29"/>
-      <c r="G144" s="30" t="str">
+      <c r="C144" s="28"/>
+      <c r="D144" s="28"/>
+      <c r="E144" s="28"/>
+      <c r="G144" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H144" s="30" t="str">
+      <c r="H144" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I144" s="30" t="str">
+      <c r="I144" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J144" s="30" t="str">
+      <c r="J144" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="145" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C145" s="29"/>
-      <c r="D145" s="29"/>
-      <c r="E145" s="29"/>
-      <c r="G145" s="30" t="str">
+      <c r="C145" s="28"/>
+      <c r="D145" s="28"/>
+      <c r="E145" s="28"/>
+      <c r="G145" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H145" s="30" t="str">
+      <c r="H145" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I145" s="30" t="str">
+      <c r="I145" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J145" s="30" t="str">
+      <c r="J145" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="146" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C146" s="29"/>
-      <c r="D146" s="29"/>
-      <c r="E146" s="29"/>
-      <c r="G146" s="30" t="str">
+      <c r="C146" s="28"/>
+      <c r="D146" s="28"/>
+      <c r="E146" s="28"/>
+      <c r="G146" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H146" s="30" t="str">
+      <c r="H146" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I146" s="30" t="str">
+      <c r="I146" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J146" s="30" t="str">
+      <c r="J146" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="147" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C147" s="29"/>
-      <c r="D147" s="29"/>
-      <c r="E147" s="29"/>
-      <c r="G147" s="30" t="str">
+      <c r="C147" s="28"/>
+      <c r="D147" s="28"/>
+      <c r="E147" s="28"/>
+      <c r="G147" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H147" s="30" t="str">
+      <c r="H147" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I147" s="30" t="str">
+      <c r="I147" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J147" s="30" t="str">
+      <c r="J147" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="148" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C148" s="29"/>
-      <c r="D148" s="29"/>
-      <c r="E148" s="29"/>
-      <c r="G148" s="30" t="str">
+      <c r="C148" s="28"/>
+      <c r="D148" s="28"/>
+      <c r="E148" s="28"/>
+      <c r="G148" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H148" s="30" t="str">
+      <c r="H148" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I148" s="30" t="str">
+      <c r="I148" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J148" s="30" t="str">
+      <c r="J148" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="149" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C149" s="29"/>
-      <c r="D149" s="29"/>
-      <c r="E149" s="29"/>
-      <c r="G149" s="30" t="str">
+      <c r="C149" s="28"/>
+      <c r="D149" s="28"/>
+      <c r="E149" s="28"/>
+      <c r="G149" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H149" s="30" t="str">
+      <c r="H149" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I149" s="30" t="str">
+      <c r="I149" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J149" s="30" t="str">
+      <c r="J149" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="150" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C150" s="29"/>
-      <c r="D150" s="29"/>
-      <c r="E150" s="29"/>
-      <c r="G150" s="30" t="str">
+      <c r="C150" s="28"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="28"/>
+      <c r="G150" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H150" s="30" t="str">
+      <c r="H150" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I150" s="30" t="str">
+      <c r="I150" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J150" s="30" t="str">
+      <c r="J150" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="151" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C151" s="29"/>
-      <c r="D151" s="29"/>
-      <c r="E151" s="29"/>
-      <c r="G151" s="30" t="str">
+      <c r="C151" s="28"/>
+      <c r="D151" s="28"/>
+      <c r="E151" s="28"/>
+      <c r="G151" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H151" s="30" t="str">
+      <c r="H151" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I151" s="30" t="str">
+      <c r="I151" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J151" s="30" t="str">
+      <c r="J151" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="152" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C152" s="29"/>
-      <c r="D152" s="29"/>
-      <c r="E152" s="29"/>
-      <c r="G152" s="30" t="str">
+      <c r="C152" s="28"/>
+      <c r="D152" s="28"/>
+      <c r="E152" s="28"/>
+      <c r="G152" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H152" s="30" t="str">
+      <c r="H152" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I152" s="30" t="str">
+      <c r="I152" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J152" s="30" t="str">
+      <c r="J152" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="153" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C153" s="29"/>
-      <c r="D153" s="29"/>
-      <c r="E153" s="29"/>
-      <c r="G153" s="30" t="str">
+      <c r="C153" s="28"/>
+      <c r="D153" s="28"/>
+      <c r="E153" s="28"/>
+      <c r="G153" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H153" s="30" t="str">
+      <c r="H153" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I153" s="30" t="str">
+      <c r="I153" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J153" s="30" t="str">
+      <c r="J153" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="154" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C154" s="29"/>
-      <c r="D154" s="29"/>
-      <c r="E154" s="29"/>
-      <c r="G154" s="30" t="str">
+      <c r="C154" s="28"/>
+      <c r="D154" s="28"/>
+      <c r="E154" s="28"/>
+      <c r="G154" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H154" s="30" t="str">
+      <c r="H154" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I154" s="30" t="str">
+      <c r="I154" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J154" s="30" t="str">
+      <c r="J154" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="155" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C155" s="29"/>
-      <c r="D155" s="29"/>
-      <c r="E155" s="29"/>
-      <c r="G155" s="30" t="str">
+      <c r="C155" s="28"/>
+      <c r="D155" s="28"/>
+      <c r="E155" s="28"/>
+      <c r="G155" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H155" s="30" t="str">
+      <c r="H155" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I155" s="30" t="str">
+      <c r="I155" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J155" s="30" t="str">
+      <c r="J155" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="156" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C156" s="29"/>
-      <c r="D156" s="29"/>
-      <c r="E156" s="29"/>
-      <c r="G156" s="30" t="str">
+      <c r="C156" s="28"/>
+      <c r="D156" s="28"/>
+      <c r="E156" s="28"/>
+      <c r="G156" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H156" s="30" t="str">
+      <c r="H156" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I156" s="30" t="str">
+      <c r="I156" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J156" s="30" t="str">
+      <c r="J156" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="157" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C157" s="29"/>
-      <c r="D157" s="29"/>
-      <c r="E157" s="29"/>
-      <c r="G157" s="30" t="str">
+      <c r="C157" s="28"/>
+      <c r="D157" s="28"/>
+      <c r="E157" s="28"/>
+      <c r="G157" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H157" s="30" t="str">
+      <c r="H157" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I157" s="30" t="str">
+      <c r="I157" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J157" s="30" t="str">
+      <c r="J157" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="158" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C158" s="29"/>
-      <c r="D158" s="29"/>
-      <c r="E158" s="29"/>
-      <c r="G158" s="30" t="str">
+      <c r="C158" s="28"/>
+      <c r="D158" s="28"/>
+      <c r="E158" s="28"/>
+      <c r="G158" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H158" s="30" t="str">
+      <c r="H158" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I158" s="30" t="str">
+      <c r="I158" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J158" s="30" t="str">
+      <c r="J158" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="159" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C159" s="29"/>
-      <c r="D159" s="29"/>
-      <c r="E159" s="29"/>
-      <c r="G159" s="30" t="str">
+      <c r="C159" s="28"/>
+      <c r="D159" s="28"/>
+      <c r="E159" s="28"/>
+      <c r="G159" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H159" s="30" t="str">
+      <c r="H159" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I159" s="30" t="str">
+      <c r="I159" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J159" s="30" t="str">
+      <c r="J159" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="160" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C160" s="29"/>
-      <c r="D160" s="29"/>
-      <c r="E160" s="29"/>
-      <c r="G160" s="30" t="str">
+      <c r="C160" s="28"/>
+      <c r="D160" s="28"/>
+      <c r="E160" s="28"/>
+      <c r="G160" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H160" s="30" t="str">
+      <c r="H160" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I160" s="30" t="str">
+      <c r="I160" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J160" s="30" t="str">
+      <c r="J160" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="161" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C161" s="29"/>
-      <c r="D161" s="29"/>
-      <c r="E161" s="29"/>
-      <c r="G161" s="30" t="str">
+      <c r="C161" s="28"/>
+      <c r="D161" s="28"/>
+      <c r="E161" s="28"/>
+      <c r="G161" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H161" s="30" t="str">
+      <c r="H161" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I161" s="30" t="str">
+      <c r="I161" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J161" s="30" t="str">
+      <c r="J161" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="162" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C162" s="29"/>
-      <c r="D162" s="29"/>
-      <c r="E162" s="29"/>
-      <c r="G162" s="30" t="str">
+      <c r="C162" s="28"/>
+      <c r="D162" s="28"/>
+      <c r="E162" s="28"/>
+      <c r="G162" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H162" s="30" t="str">
+      <c r="H162" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I162" s="30" t="str">
+      <c r="I162" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J162" s="30" t="str">
+      <c r="J162" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="163" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C163" s="29"/>
-      <c r="D163" s="29"/>
-      <c r="E163" s="29"/>
-      <c r="G163" s="30" t="str">
+      <c r="C163" s="28"/>
+      <c r="D163" s="28"/>
+      <c r="E163" s="28"/>
+      <c r="G163" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H163" s="30" t="str">
+      <c r="H163" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I163" s="30" t="str">
+      <c r="I163" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J163" s="30" t="str">
+      <c r="J163" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="164" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C164" s="29"/>
-      <c r="D164" s="29"/>
-      <c r="E164" s="29"/>
-      <c r="G164" s="30" t="str">
+      <c r="C164" s="28"/>
+      <c r="D164" s="28"/>
+      <c r="E164" s="28"/>
+      <c r="G164" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H164" s="30" t="str">
+      <c r="H164" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I164" s="30" t="str">
+      <c r="I164" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J164" s="30" t="str">
+      <c r="J164" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="165" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C165" s="29"/>
-      <c r="D165" s="29"/>
-      <c r="E165" s="29"/>
-      <c r="G165" s="30" t="str">
+      <c r="C165" s="28"/>
+      <c r="D165" s="28"/>
+      <c r="E165" s="28"/>
+      <c r="G165" s="29" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="H165" s="30" t="str">
+      <c r="H165" s="29" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="I165" s="30" t="str">
+      <c r="I165" s="29" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J165" s="30" t="str">
+      <c r="J165" s="29" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="166" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C166" s="29"/>
-      <c r="D166" s="29"/>
-      <c r="E166" s="29"/>
-      <c r="G166" s="30" t="str">
+      <c r="C166" s="28"/>
+      <c r="D166" s="28"/>
+      <c r="E166" s="28"/>
+      <c r="G166" s="29" t="str">
         <f t="shared" ref="G166:G208" ca="1" si="17">IF(C166="","",IF(F166="Recebido",E166-C166,TODAY()-C166))</f>
         <v/>
       </c>
-      <c r="H166" s="30" t="str">
+      <c r="H166" s="29" t="str">
         <f t="shared" ref="H166:H208" ca="1" si="18">IF(D166="","",IF(F166="Recebido",E166-D166,TODAY()-D166))</f>
         <v/>
       </c>
-      <c r="I166" s="30" t="str">
+      <c r="I166" s="29" t="str">
         <f t="shared" ref="I166:I208" si="19">IF(OR(C166="",D166=""),"",D166-C166)</f>
         <v/>
       </c>
-      <c r="J166" s="30" t="str">
+      <c r="J166" s="29" t="str">
         <f t="shared" ref="J166:J208" si="20">IF(OR(D166="",E166=""),"",E166-D166)</f>
         <v/>
       </c>
     </row>
     <row r="167" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C167" s="29"/>
-      <c r="D167" s="29"/>
-      <c r="E167" s="29"/>
-      <c r="G167" s="30" t="str">
+      <c r="C167" s="28"/>
+      <c r="D167" s="28"/>
+      <c r="E167" s="28"/>
+      <c r="G167" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H167" s="30" t="str">
+      <c r="H167" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I167" s="30" t="str">
+      <c r="I167" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J167" s="30" t="str">
+      <c r="J167" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="168" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C168" s="29"/>
-      <c r="D168" s="29"/>
-      <c r="E168" s="29"/>
-      <c r="G168" s="30" t="str">
+      <c r="C168" s="28"/>
+      <c r="D168" s="28"/>
+      <c r="E168" s="28"/>
+      <c r="G168" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H168" s="30" t="str">
+      <c r="H168" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I168" s="30" t="str">
+      <c r="I168" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J168" s="30" t="str">
+      <c r="J168" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="169" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C169" s="29"/>
-      <c r="D169" s="29"/>
-      <c r="E169" s="29"/>
-      <c r="G169" s="30" t="str">
+      <c r="C169" s="28"/>
+      <c r="D169" s="28"/>
+      <c r="E169" s="28"/>
+      <c r="G169" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H169" s="30" t="str">
+      <c r="H169" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I169" s="30" t="str">
+      <c r="I169" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J169" s="30" t="str">
+      <c r="J169" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="170" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C170" s="29"/>
-      <c r="D170" s="29"/>
-      <c r="E170" s="29"/>
-      <c r="G170" s="30" t="str">
+      <c r="C170" s="28"/>
+      <c r="D170" s="28"/>
+      <c r="E170" s="28"/>
+      <c r="G170" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H170" s="30" t="str">
+      <c r="H170" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I170" s="30" t="str">
+      <c r="I170" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J170" s="30" t="str">
+      <c r="J170" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="171" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C171" s="29"/>
-      <c r="D171" s="29"/>
-      <c r="E171" s="29"/>
-      <c r="G171" s="30" t="str">
+      <c r="C171" s="28"/>
+      <c r="D171" s="28"/>
+      <c r="E171" s="28"/>
+      <c r="G171" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H171" s="30" t="str">
+      <c r="H171" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I171" s="30" t="str">
+      <c r="I171" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J171" s="30" t="str">
+      <c r="J171" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="172" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C172" s="29"/>
-      <c r="D172" s="29"/>
-      <c r="E172" s="29"/>
-      <c r="G172" s="30" t="str">
+      <c r="C172" s="28"/>
+      <c r="D172" s="28"/>
+      <c r="E172" s="28"/>
+      <c r="G172" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H172" s="30" t="str">
+      <c r="H172" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I172" s="30" t="str">
+      <c r="I172" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J172" s="30" t="str">
+      <c r="J172" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="173" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C173" s="29"/>
-      <c r="D173" s="29"/>
-      <c r="E173" s="29"/>
-      <c r="G173" s="30" t="str">
+      <c r="C173" s="28"/>
+      <c r="D173" s="28"/>
+      <c r="E173" s="28"/>
+      <c r="G173" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H173" s="30" t="str">
+      <c r="H173" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I173" s="30" t="str">
+      <c r="I173" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J173" s="30" t="str">
+      <c r="J173" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="174" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C174" s="29"/>
-      <c r="D174" s="29"/>
-      <c r="E174" s="29"/>
-      <c r="G174" s="30" t="str">
+      <c r="C174" s="28"/>
+      <c r="D174" s="28"/>
+      <c r="E174" s="28"/>
+      <c r="G174" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H174" s="30" t="str">
+      <c r="H174" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I174" s="30" t="str">
+      <c r="I174" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J174" s="30" t="str">
+      <c r="J174" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="175" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C175" s="29"/>
-      <c r="D175" s="29"/>
-      <c r="E175" s="29"/>
-      <c r="G175" s="30" t="str">
+      <c r="C175" s="28"/>
+      <c r="D175" s="28"/>
+      <c r="E175" s="28"/>
+      <c r="G175" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H175" s="30" t="str">
+      <c r="H175" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I175" s="30" t="str">
+      <c r="I175" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J175" s="30" t="str">
+      <c r="J175" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="176" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C176" s="29"/>
-      <c r="D176" s="29"/>
-      <c r="E176" s="29"/>
-      <c r="G176" s="30" t="str">
+      <c r="C176" s="28"/>
+      <c r="D176" s="28"/>
+      <c r="E176" s="28"/>
+      <c r="G176" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H176" s="30" t="str">
+      <c r="H176" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I176" s="30" t="str">
+      <c r="I176" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J176" s="30" t="str">
+      <c r="J176" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="177" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C177" s="29"/>
-      <c r="D177" s="29"/>
-      <c r="E177" s="29"/>
-      <c r="G177" s="30" t="str">
+      <c r="C177" s="28"/>
+      <c r="D177" s="28"/>
+      <c r="E177" s="28"/>
+      <c r="G177" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H177" s="30" t="str">
+      <c r="H177" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I177" s="30" t="str">
+      <c r="I177" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J177" s="30" t="str">
+      <c r="J177" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="178" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C178" s="29"/>
-      <c r="D178" s="29"/>
-      <c r="E178" s="29"/>
-      <c r="G178" s="30" t="str">
+      <c r="C178" s="28"/>
+      <c r="D178" s="28"/>
+      <c r="E178" s="28"/>
+      <c r="G178" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H178" s="30" t="str">
+      <c r="H178" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I178" s="30" t="str">
+      <c r="I178" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J178" s="30" t="str">
+      <c r="J178" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="179" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C179" s="29"/>
-      <c r="D179" s="29"/>
-      <c r="E179" s="29"/>
-      <c r="G179" s="30" t="str">
+      <c r="C179" s="28"/>
+      <c r="D179" s="28"/>
+      <c r="E179" s="28"/>
+      <c r="G179" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H179" s="30" t="str">
+      <c r="H179" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I179" s="30" t="str">
+      <c r="I179" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J179" s="30" t="str">
+      <c r="J179" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="180" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C180" s="29"/>
-      <c r="D180" s="29"/>
-      <c r="E180" s="29"/>
-      <c r="G180" s="30" t="str">
+      <c r="C180" s="28"/>
+      <c r="D180" s="28"/>
+      <c r="E180" s="28"/>
+      <c r="G180" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H180" s="30" t="str">
+      <c r="H180" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I180" s="30" t="str">
+      <c r="I180" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J180" s="30" t="str">
+      <c r="J180" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="181" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C181" s="29"/>
-      <c r="D181" s="29"/>
-      <c r="E181" s="29"/>
-      <c r="G181" s="30" t="str">
+      <c r="C181" s="28"/>
+      <c r="D181" s="28"/>
+      <c r="E181" s="28"/>
+      <c r="G181" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H181" s="30" t="str">
+      <c r="H181" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I181" s="30" t="str">
+      <c r="I181" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J181" s="30" t="str">
+      <c r="J181" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="182" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C182" s="29"/>
-      <c r="D182" s="29"/>
-      <c r="E182" s="29"/>
-      <c r="G182" s="30" t="str">
+      <c r="C182" s="28"/>
+      <c r="D182" s="28"/>
+      <c r="E182" s="28"/>
+      <c r="G182" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H182" s="30" t="str">
+      <c r="H182" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I182" s="30" t="str">
+      <c r="I182" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J182" s="30" t="str">
+      <c r="J182" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="183" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C183" s="29"/>
-      <c r="D183" s="29"/>
-      <c r="E183" s="29"/>
-      <c r="G183" s="30" t="str">
+      <c r="C183" s="28"/>
+      <c r="D183" s="28"/>
+      <c r="E183" s="28"/>
+      <c r="G183" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H183" s="30" t="str">
+      <c r="H183" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I183" s="30" t="str">
+      <c r="I183" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J183" s="30" t="str">
+      <c r="J183" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="184" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C184" s="29"/>
-      <c r="D184" s="29"/>
-      <c r="E184" s="29"/>
-      <c r="G184" s="30" t="str">
+      <c r="C184" s="28"/>
+      <c r="D184" s="28"/>
+      <c r="E184" s="28"/>
+      <c r="G184" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H184" s="30" t="str">
+      <c r="H184" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I184" s="30" t="str">
+      <c r="I184" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J184" s="30" t="str">
+      <c r="J184" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="185" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C185" s="29"/>
-      <c r="D185" s="29"/>
-      <c r="E185" s="29"/>
-      <c r="G185" s="30" t="str">
+      <c r="C185" s="28"/>
+      <c r="D185" s="28"/>
+      <c r="E185" s="28"/>
+      <c r="G185" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H185" s="30" t="str">
+      <c r="H185" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I185" s="30" t="str">
+      <c r="I185" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J185" s="30" t="str">
+      <c r="J185" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="186" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C186" s="29"/>
-      <c r="D186" s="29"/>
-      <c r="E186" s="29"/>
-      <c r="G186" s="30" t="str">
+      <c r="C186" s="28"/>
+      <c r="D186" s="28"/>
+      <c r="E186" s="28"/>
+      <c r="G186" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H186" s="30" t="str">
+      <c r="H186" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I186" s="30" t="str">
+      <c r="I186" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J186" s="30" t="str">
+      <c r="J186" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="187" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C187" s="29"/>
-      <c r="D187" s="29"/>
-      <c r="E187" s="29"/>
-      <c r="G187" s="30" t="str">
+      <c r="C187" s="28"/>
+      <c r="D187" s="28"/>
+      <c r="E187" s="28"/>
+      <c r="G187" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H187" s="30" t="str">
+      <c r="H187" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I187" s="30" t="str">
+      <c r="I187" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J187" s="30" t="str">
+      <c r="J187" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="188" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C188" s="29"/>
-      <c r="D188" s="29"/>
-      <c r="E188" s="29"/>
-      <c r="G188" s="30" t="str">
+      <c r="C188" s="28"/>
+      <c r="D188" s="28"/>
+      <c r="E188" s="28"/>
+      <c r="G188" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H188" s="30" t="str">
+      <c r="H188" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I188" s="30" t="str">
+      <c r="I188" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J188" s="30" t="str">
+      <c r="J188" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="189" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C189" s="29"/>
-      <c r="D189" s="29"/>
-      <c r="E189" s="29"/>
-      <c r="G189" s="30" t="str">
+      <c r="C189" s="28"/>
+      <c r="D189" s="28"/>
+      <c r="E189" s="28"/>
+      <c r="G189" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H189" s="30" t="str">
+      <c r="H189" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I189" s="30" t="str">
+      <c r="I189" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J189" s="30" t="str">
+      <c r="J189" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="190" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C190" s="29"/>
-      <c r="D190" s="29"/>
-      <c r="E190" s="29"/>
-      <c r="G190" s="30" t="str">
+      <c r="C190" s="28"/>
+      <c r="D190" s="28"/>
+      <c r="E190" s="28"/>
+      <c r="G190" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H190" s="30" t="str">
+      <c r="H190" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I190" s="30" t="str">
+      <c r="I190" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J190" s="30" t="str">
+      <c r="J190" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="191" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C191" s="29"/>
-      <c r="D191" s="29"/>
-      <c r="E191" s="29"/>
-      <c r="G191" s="30" t="str">
+      <c r="C191" s="28"/>
+      <c r="D191" s="28"/>
+      <c r="E191" s="28"/>
+      <c r="G191" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H191" s="30" t="str">
+      <c r="H191" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I191" s="30" t="str">
+      <c r="I191" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J191" s="30" t="str">
+      <c r="J191" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="192" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C192" s="29"/>
-      <c r="D192" s="29"/>
-      <c r="E192" s="29"/>
-      <c r="G192" s="30" t="str">
+      <c r="C192" s="28"/>
+      <c r="D192" s="28"/>
+      <c r="E192" s="28"/>
+      <c r="G192" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H192" s="30" t="str">
+      <c r="H192" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I192" s="30" t="str">
+      <c r="I192" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J192" s="30" t="str">
+      <c r="J192" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="193" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C193" s="29"/>
-      <c r="D193" s="29"/>
-      <c r="E193" s="29"/>
-      <c r="G193" s="30" t="str">
+      <c r="C193" s="28"/>
+      <c r="D193" s="28"/>
+      <c r="E193" s="28"/>
+      <c r="G193" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H193" s="30" t="str">
+      <c r="H193" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I193" s="30" t="str">
+      <c r="I193" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J193" s="30" t="str">
+      <c r="J193" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="194" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C194" s="29"/>
-      <c r="D194" s="29"/>
-      <c r="E194" s="29"/>
-      <c r="G194" s="30" t="str">
+      <c r="C194" s="28"/>
+      <c r="D194" s="28"/>
+      <c r="E194" s="28"/>
+      <c r="G194" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H194" s="30" t="str">
+      <c r="H194" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I194" s="30" t="str">
+      <c r="I194" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J194" s="30" t="str">
+      <c r="J194" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="195" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C195" s="29"/>
-      <c r="D195" s="29"/>
-      <c r="E195" s="29"/>
-      <c r="G195" s="30" t="str">
+      <c r="C195" s="28"/>
+      <c r="D195" s="28"/>
+      <c r="E195" s="28"/>
+      <c r="G195" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H195" s="30" t="str">
+      <c r="H195" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I195" s="30" t="str">
+      <c r="I195" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J195" s="30" t="str">
+      <c r="J195" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="196" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C196" s="29"/>
-      <c r="D196" s="29"/>
-      <c r="E196" s="29"/>
-      <c r="G196" s="30" t="str">
+      <c r="C196" s="28"/>
+      <c r="D196" s="28"/>
+      <c r="E196" s="28"/>
+      <c r="G196" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H196" s="30" t="str">
+      <c r="H196" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I196" s="30" t="str">
+      <c r="I196" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J196" s="30" t="str">
+      <c r="J196" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="197" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C197" s="29"/>
-      <c r="D197" s="29"/>
-      <c r="E197" s="29"/>
-      <c r="G197" s="30" t="str">
+      <c r="C197" s="28"/>
+      <c r="D197" s="28"/>
+      <c r="E197" s="28"/>
+      <c r="G197" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H197" s="30" t="str">
+      <c r="H197" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I197" s="30" t="str">
+      <c r="I197" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J197" s="30" t="str">
+      <c r="J197" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="198" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C198" s="29"/>
-      <c r="D198" s="29"/>
-      <c r="E198" s="29"/>
-      <c r="G198" s="30" t="str">
+      <c r="C198" s="28"/>
+      <c r="D198" s="28"/>
+      <c r="E198" s="28"/>
+      <c r="G198" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H198" s="30" t="str">
+      <c r="H198" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I198" s="30" t="str">
+      <c r="I198" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J198" s="30" t="str">
+      <c r="J198" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="199" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C199" s="29"/>
-      <c r="D199" s="29"/>
-      <c r="E199" s="29"/>
-      <c r="G199" s="30" t="str">
+      <c r="C199" s="28"/>
+      <c r="D199" s="28"/>
+      <c r="E199" s="28"/>
+      <c r="G199" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H199" s="30" t="str">
+      <c r="H199" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I199" s="30" t="str">
+      <c r="I199" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J199" s="30" t="str">
+      <c r="J199" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="200" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C200" s="29"/>
-      <c r="D200" s="29"/>
-      <c r="E200" s="29"/>
-      <c r="G200" s="30" t="str">
+      <c r="C200" s="28"/>
+      <c r="D200" s="28"/>
+      <c r="E200" s="28"/>
+      <c r="G200" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H200" s="30" t="str">
+      <c r="H200" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I200" s="30" t="str">
+      <c r="I200" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J200" s="30" t="str">
+      <c r="J200" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="201" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C201" s="29"/>
-      <c r="D201" s="29"/>
-      <c r="E201" s="29"/>
-      <c r="G201" s="30" t="str">
+      <c r="C201" s="28"/>
+      <c r="D201" s="28"/>
+      <c r="E201" s="28"/>
+      <c r="G201" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H201" s="30" t="str">
+      <c r="H201" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I201" s="30" t="str">
+      <c r="I201" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J201" s="30" t="str">
+      <c r="J201" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="202" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C202" s="29"/>
-      <c r="D202" s="29"/>
-      <c r="E202" s="29"/>
-      <c r="G202" s="30" t="str">
+      <c r="C202" s="28"/>
+      <c r="D202" s="28"/>
+      <c r="E202" s="28"/>
+      <c r="G202" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H202" s="30" t="str">
+      <c r="H202" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I202" s="30" t="str">
+      <c r="I202" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J202" s="30" t="str">
+      <c r="J202" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="203" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C203" s="29"/>
-      <c r="D203" s="29"/>
-      <c r="E203" s="29"/>
-      <c r="G203" s="30" t="str">
+      <c r="C203" s="28"/>
+      <c r="D203" s="28"/>
+      <c r="E203" s="28"/>
+      <c r="G203" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H203" s="30" t="str">
+      <c r="H203" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I203" s="30" t="str">
+      <c r="I203" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J203" s="30" t="str">
+      <c r="J203" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="204" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C204" s="29"/>
-      <c r="D204" s="29"/>
-      <c r="E204" s="29"/>
-      <c r="G204" s="30" t="str">
+      <c r="C204" s="28"/>
+      <c r="D204" s="28"/>
+      <c r="E204" s="28"/>
+      <c r="G204" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H204" s="30" t="str">
+      <c r="H204" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I204" s="30" t="str">
+      <c r="I204" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J204" s="30" t="str">
+      <c r="J204" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="205" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C205" s="29"/>
-      <c r="D205" s="29"/>
-      <c r="E205" s="29"/>
-      <c r="G205" s="30" t="str">
+      <c r="C205" s="28"/>
+      <c r="D205" s="28"/>
+      <c r="E205" s="28"/>
+      <c r="G205" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H205" s="30" t="str">
+      <c r="H205" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I205" s="30" t="str">
+      <c r="I205" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J205" s="30" t="str">
+      <c r="J205" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="206" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C206" s="29"/>
-      <c r="D206" s="29"/>
-      <c r="E206" s="29"/>
-      <c r="G206" s="30" t="str">
+      <c r="C206" s="28"/>
+      <c r="D206" s="28"/>
+      <c r="E206" s="28"/>
+      <c r="G206" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H206" s="30" t="str">
+      <c r="H206" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I206" s="30" t="str">
+      <c r="I206" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J206" s="30" t="str">
+      <c r="J206" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="207" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C207" s="29"/>
-      <c r="D207" s="29"/>
-      <c r="E207" s="29"/>
-      <c r="G207" s="30" t="str">
+      <c r="C207" s="28"/>
+      <c r="D207" s="28"/>
+      <c r="E207" s="28"/>
+      <c r="G207" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H207" s="30" t="str">
+      <c r="H207" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I207" s="30" t="str">
+      <c r="I207" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J207" s="30" t="str">
+      <c r="J207" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="208" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C208" s="29"/>
-      <c r="D208" s="29"/>
-      <c r="E208" s="29"/>
-      <c r="G208" s="30" t="str">
+      <c r="C208" s="28"/>
+      <c r="D208" s="28"/>
+      <c r="E208" s="28"/>
+      <c r="G208" s="29" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="H208" s="30" t="str">
+      <c r="H208" s="29" t="str">
         <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
-      <c r="I208" s="30" t="str">
+      <c r="I208" s="29" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J208" s="30" t="str">
+      <c r="J208" s="29" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -6031,627 +6032,736 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:G37"/>
+  <dimension ref="C2:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="25"/>
-    <col min="3" max="3" width="12" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.7109375" style="31" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="2" width="9.140625" style="12"/>
+    <col min="3" max="3" width="12" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="30" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C2" s="25" t="s">
+    <row r="2" spans="3:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C2" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="F2" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="G2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="H2" s="30" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C3" s="25" t="s">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="F3" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="25">
+      <c r="G3" s="12">
         <v>1</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="H3" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C4" s="25" t="s">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="F4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="25">
+      <c r="G4" s="12">
         <v>1</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="H4" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C5" s="25" t="s">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="F5" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="25">
+      <c r="G5" s="12">
         <v>1</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="H5" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C6" s="25" t="s">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="F6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="25">
+      <c r="G6" s="12">
         <v>1</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="H6" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C7" s="25" t="s">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="F7" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="25">
+      <c r="G7" s="12">
         <v>1</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="H7" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C8" s="25" t="s">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="F8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="25">
+      <c r="G8" s="12">
         <v>1</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="H8" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C9" s="25" t="s">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="F9" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="25">
+      <c r="G9" s="12">
         <v>1</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="H9" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C10" s="25" t="s">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="F10" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="25">
+      <c r="G10" s="12">
         <v>1</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="H10" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="25" t="s">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="F11" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="25">
+      <c r="G11" s="12">
         <v>1</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="H11" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="25" t="s">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="F12" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="25">
+      <c r="G12" s="12">
         <v>1</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="H12" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="3:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="C13" s="25" t="s">
+    <row r="13" spans="3:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="F13" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="25">
+      <c r="G13" s="12">
         <v>1</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="H13" s="30" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="3:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="C14" s="25" t="s">
+    <row r="14" spans="3:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C14" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="25">
+      <c r="G14" s="12">
         <v>1</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="H14" s="30" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C15" s="25" t="s">
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="F15" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="25">
+      <c r="G15" s="12">
         <v>1</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="H15" s="30" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="3:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="C16" s="25" t="s">
+    <row r="16" spans="3:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="C16" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="F16" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="25">
+      <c r="G16" s="12">
         <v>1</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="H16" s="30" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="3:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="C17" s="25" t="s">
+    <row r="17" spans="3:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C17" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="F17" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="25">
+      <c r="G17" s="12">
         <v>1</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="H17" s="30" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C18" s="25" t="s">
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C18" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="F18" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="25">
+      <c r="G18" s="12">
         <v>1</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="H18" s="30" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="3:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="C19" s="25" t="s">
+    <row r="19" spans="3:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C19" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="F19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="25">
+      <c r="G19" s="12">
         <v>1</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="H19" s="30" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="3:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="C20" s="25" t="s">
+    <row r="20" spans="3:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C20" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="F20" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="25">
+      <c r="G20" s="12">
         <v>1</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="H20" s="30" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="3:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="C21" s="25" t="s">
+    <row r="21" spans="3:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C21" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="F21" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="25">
+      <c r="G21" s="12">
         <v>1</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="H21" s="30" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C22" s="25" t="s">
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C22" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="25">
+      <c r="F22" s="12">
         <v>24</v>
       </c>
-      <c r="F22" s="25">
+      <c r="G22" s="12">
         <v>1</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="H22" s="30" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="3:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="C23" s="25">
+    <row r="23" spans="3:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="C23" s="12">
         <v>37</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="F23" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="25">
+      <c r="G23" s="12">
         <v>1</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="H23" s="30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="3:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="C24" s="25">
+    <row r="24" spans="3:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="C24" s="12">
         <v>37</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="F24" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="25">
+      <c r="G24" s="12">
         <v>1</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="H24" s="30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="3:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="C25" s="25">
+    <row r="25" spans="3:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="C25" s="12">
         <v>37</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="F25" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="25">
+      <c r="G25" s="12">
         <v>1</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="H25" s="30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="3:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="C26" s="25">
+    <row r="26" spans="3:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="C26" s="12">
         <v>37</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="F26" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="25">
+      <c r="G26" s="12">
         <v>1</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="H26" s="30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="3:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="C27" s="25">
+    <row r="27" spans="3:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="C27" s="12">
         <v>37</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="F27" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F27" s="25">
+      <c r="G27" s="12">
         <v>1</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="H27" s="30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="25" t="s">
+    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C28" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="F28" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="25">
+      <c r="G28" s="12">
         <v>1</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="H28" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="25" t="s">
+    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C29" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="D29" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="F29" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F29" s="25">
+      <c r="G29" s="12">
         <v>1</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="H29" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C30" s="25" t="s">
+    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C30" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="F30" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="25">
+      <c r="G30" s="12">
         <v>1</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="H30" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C31" s="25" t="s">
+    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C31" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D31" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="F31" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="25">
+      <c r="G31" s="12">
         <v>1</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="H31" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C32" s="25" t="s">
+    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C32" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D32" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="F32" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="25">
+      <c r="G32" s="12">
         <v>1</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="H32" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C33" s="25" t="s">
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C33" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="F33" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="25">
+      <c r="G33" s="12">
         <v>1</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="H33" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C34" s="25" t="s">
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C34" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="F34" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="25">
+      <c r="G34" s="12">
         <v>1</v>
       </c>
-      <c r="G34" s="31" t="s">
+      <c r="H34" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C35" s="25" t="s">
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C35" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="F35" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="25">
+      <c r="G35" s="12">
         <v>1</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="H35" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C36" s="25" t="s">
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="E36" s="25" t="s">
+      <c r="F36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="25">
+      <c r="G36" s="12">
         <v>1</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="H36" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C37" s="25" t="s">
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C37" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="F37" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="25">
+      <c r="G37" s="12">
         <v>1</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="H37" s="30" t="s">
         <v>61</v>
       </c>
     </row>

--- a/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
+++ b/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="93">
   <si>
     <t>PEDIDOS DE CAMISAS 2026</t>
   </si>
@@ -189,9 +189,6 @@
     <t>LZ369979625CN</t>
   </si>
   <si>
-    <t xml:space="preserve">Pacote </t>
-  </si>
-  <si>
     <t>Camisa</t>
   </si>
   <si>
@@ -303,7 +300,7 @@
     <t>Vasco Branca 2026</t>
   </si>
   <si>
-    <t>QUANT</t>
+    <t>Qta</t>
   </si>
 </sst>
 </file>
@@ -754,14 +751,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela3" displayName="Tabela3" ref="C2:H37" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="C2:H37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela3" displayName="Tabela3" ref="A1:F36" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:F36"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Pacote " dataDxfId="7"/>
+    <tableColumn id="1" name="Pacote" dataDxfId="7"/>
     <tableColumn id="6" name="Código de Rastreio" dataDxfId="6"/>
     <tableColumn id="2" name="Camisa" dataDxfId="5"/>
     <tableColumn id="3" name="Tamanho" dataDxfId="4"/>
-    <tableColumn id="5" name="QUANT" dataDxfId="3"/>
+    <tableColumn id="5" name="Qta" dataDxfId="3"/>
     <tableColumn id="4" name="Cliente" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6032,737 +6029,736 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:H37"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="12"/>
-    <col min="3" max="3" width="12" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="30" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="12" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" style="30" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="C2" s="12" t="s">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="30" t="s">
+      <c r="D1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="E1" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H2" s="30" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="30" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C3" s="12" t="s">
+      <c r="D2" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="12">
+        <v>1</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>41</v>
       </c>
+      <c r="B3" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>58</v>
+      </c>
       <c r="D3" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="12">
+        <v>1</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="C4" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="12">
+        <v>1</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="12">
+        <v>1</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="E14" s="12">
+        <v>1</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="12">
+        <v>1</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="12">
+        <v>1</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="12">
+        <v>24</v>
+      </c>
+      <c r="E21" s="12">
+        <v>1</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>37</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="12">
+        <v>1</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <v>37</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <v>37</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="12">
+        <v>1</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <v>37</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="12">
+        <v>1</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <v>37</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="12">
+        <v>1</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="12">
+        <v>1</v>
+      </c>
+      <c r="F27" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="12">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="12">
         <v>1</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="F28" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="12" t="s">
+      <c r="E29" s="12">
+        <v>1</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="12">
+      <c r="E30" s="12">
         <v>1</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="F30" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="12">
+        <v>1</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="12" t="s">
+      <c r="E32" s="12">
+        <v>1</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="12">
+        <v>1</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="12">
+      <c r="E34" s="12">
         <v>1</v>
       </c>
-      <c r="H5" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="F34" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="12">
+      <c r="E35" s="12">
         <v>1</v>
       </c>
-      <c r="H6" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="F35" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="12">
+      <c r="E36" s="12">
         <v>1</v>
       </c>
-      <c r="H7" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C8" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="12">
-        <v>1</v>
-      </c>
-      <c r="H8" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="12">
-        <v>1</v>
-      </c>
-      <c r="H9" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="12">
-        <v>1</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="12">
-        <v>1</v>
-      </c>
-      <c r="H11" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="12">
-        <v>1</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="C13" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="12">
-        <v>1</v>
-      </c>
-      <c r="H13" s="30" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="C14" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="12">
-        <v>1</v>
-      </c>
-      <c r="H14" s="30" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="12" t="s">
+      <c r="F36" s="30" t="s">
         <v>60</v>
-      </c>
-      <c r="G15" s="12">
-        <v>1</v>
-      </c>
-      <c r="H15" s="30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="C16" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="12">
-        <v>1</v>
-      </c>
-      <c r="H16" s="30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="3:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="C17" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="12">
-        <v>1</v>
-      </c>
-      <c r="H17" s="30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C18" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="12">
-        <v>1</v>
-      </c>
-      <c r="H18" s="30" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="C19" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="12">
-        <v>1</v>
-      </c>
-      <c r="H19" s="30" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="3:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="C20" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="12">
-        <v>1</v>
-      </c>
-      <c r="H20" s="30" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="C21" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" s="12">
-        <v>1</v>
-      </c>
-      <c r="H21" s="30" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C22" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="12">
-        <v>24</v>
-      </c>
-      <c r="G22" s="12">
-        <v>1</v>
-      </c>
-      <c r="H22" s="30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="3:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="C23" s="12">
-        <v>37</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" s="12">
-        <v>1</v>
-      </c>
-      <c r="H23" s="30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="3:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="C24" s="12">
-        <v>37</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="12">
-        <v>1</v>
-      </c>
-      <c r="H24" s="30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="3:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="C25" s="12">
-        <v>37</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="12">
-        <v>1</v>
-      </c>
-      <c r="H25" s="30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="3:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="C26" s="12">
-        <v>37</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="12">
-        <v>1</v>
-      </c>
-      <c r="H26" s="30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="3:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="C27" s="12">
-        <v>37</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27" s="12">
-        <v>1</v>
-      </c>
-      <c r="H27" s="30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C28" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="12">
-        <v>1</v>
-      </c>
-      <c r="H28" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C29" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29" s="12">
-        <v>1</v>
-      </c>
-      <c r="H29" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C30" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" s="12">
-        <v>1</v>
-      </c>
-      <c r="H30" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C31" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G31" s="12">
-        <v>1</v>
-      </c>
-      <c r="H31" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C32" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="12">
-        <v>1</v>
-      </c>
-      <c r="H32" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C33" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33" s="12">
-        <v>1</v>
-      </c>
-      <c r="H33" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C34" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34" s="12">
-        <v>1</v>
-      </c>
-      <c r="H34" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C35" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G35" s="12">
-        <v>1</v>
-      </c>
-      <c r="H35" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C36" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G36" s="12">
-        <v>1</v>
-      </c>
-      <c r="H36" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G37" s="12">
-        <v>1</v>
-      </c>
-      <c r="H37" s="30" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
+++ b/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
@@ -300,7 +300,7 @@
     <t>Vasco Branca 2026</t>
   </si>
   <si>
-    <t>Qta</t>
+    <t>Qtd</t>
   </si>
 </sst>
 </file>
@@ -758,7 +758,7 @@
     <tableColumn id="6" name="Código de Rastreio" dataDxfId="6"/>
     <tableColumn id="2" name="Camisa" dataDxfId="5"/>
     <tableColumn id="3" name="Tamanho" dataDxfId="4"/>
-    <tableColumn id="5" name="Qta" dataDxfId="3"/>
+    <tableColumn id="5" name="Qtd" dataDxfId="3"/>
     <tableColumn id="4" name="Cliente" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -990,7 +990,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,12 +1021,12 @@
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <f ca="1">F3-B3</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19">
         <f ca="1">F3-D3</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="20">
         <v>46058</v>
@@ -1065,7 +1065,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="11">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       <c r="A12" s="17"/>
       <c r="B12" s="18">
         <f ca="1">F9-B9</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19">
         <f ca="1">F9-D9</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" s="20">
         <v>46065</v>
@@ -1140,7 +1140,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="11">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1171,12 +1171,12 @@
       <c r="A18" s="17"/>
       <c r="B18" s="18">
         <f ca="1">F15-B15</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="19">
         <f ca="1">F15-D15</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="20"/>
       <c r="F18" s="21" t="str">
@@ -1213,7 +1213,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="11">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1244,12 +1244,12 @@
       <c r="A24" s="17"/>
       <c r="B24" s="18">
         <f ca="1">F21-B21</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19">
         <f ca="1">F21-D21</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="20"/>
       <c r="F24" s="21" t="str">
@@ -1286,7 +1286,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="11">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1317,12 +1317,12 @@
       <c r="A30" s="17"/>
       <c r="B30" s="18">
         <f ca="1">F27-B27</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19">
         <f ca="1">F27-D27</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="20"/>
       <c r="F30" s="21" t="str">
@@ -1359,7 +1359,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="11">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1390,12 +1390,12 @@
       <c r="A36" s="17"/>
       <c r="B36" s="18">
         <f ca="1">F33-B33</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="19">
         <f ca="1">F33-D33</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="20"/>
       <c r="F36" s="21" t="str">
@@ -1432,7 +1432,7 @@
       <c r="E39" s="9"/>
       <c r="F39" s="11">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1463,12 +1463,12 @@
       <c r="A42" s="17"/>
       <c r="B42" s="18">
         <f ca="1">F39-B39</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="19">
         <f ca="1">F39-D39</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E42" s="20">
         <v>46073</v>
@@ -1622,11 +1622,11 @@
       </c>
       <c r="G4" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="27">
         <f t="shared" si="3"/>
@@ -1657,11 +1657,11 @@
       </c>
       <c r="G5" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5" s="27">
         <f t="shared" si="3"/>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="G6" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" s="27">
         <f t="shared" si="3"/>
@@ -1727,11 +1727,11 @@
       </c>
       <c r="G7" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" s="27">
         <f t="shared" si="3"/>
@@ -1762,11 +1762,11 @@
       </c>
       <c r="G8" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H8" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" s="27">
         <f t="shared" si="3"/>
@@ -1797,11 +1797,11 @@
       </c>
       <c r="G9" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I9" s="27">
         <f t="shared" si="3"/>
@@ -1832,11 +1832,11 @@
       </c>
       <c r="G10" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H10" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I10" s="27">
         <f t="shared" si="3"/>

--- a/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
+++ b/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="12315" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="12315" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ORIGINAL" sheetId="1" r:id="rId1"/>
@@ -640,12 +640,6 @@
   </cellStyles>
   <dxfs count="21">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -662,6 +656,36 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -694,30 +718,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -732,34 +732,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaPacotes" displayName="TabelaPacotes" ref="A1:J11" headerRowDxfId="11" dataDxfId="9" totalsRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaPacotes" displayName="TabelaPacotes" ref="A1:J11" headerRowDxfId="20" dataDxfId="19" totalsRowDxfId="18">
   <autoFilter ref="A1:J11"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="Pacote" dataDxfId="20"/>
-    <tableColumn id="10" name="Código de Rastreio" dataDxfId="8"/>
-    <tableColumn id="2" name="Data do pedido" dataDxfId="19"/>
-    <tableColumn id="3" name="Data do envio" dataDxfId="18"/>
-    <tableColumn id="4" name="Data de recebimento" dataDxfId="17"/>
-    <tableColumn id="5" name="Status" dataDxfId="16"/>
-    <tableColumn id="6" name="Dias desde pedido" dataDxfId="15"/>
-    <tableColumn id="7" name="Dias desde envio" dataDxfId="14"/>
-    <tableColumn id="8" name="Dias pedido→envio" dataDxfId="13"/>
-    <tableColumn id="9" name="Duração importação (envio→receb.)" dataDxfId="12"/>
+    <tableColumn id="1" name="Pacote" dataDxfId="17"/>
+    <tableColumn id="10" name="Código de Rastreio" dataDxfId="16"/>
+    <tableColumn id="2" name="Data do pedido" dataDxfId="15"/>
+    <tableColumn id="3" name="Data do envio" dataDxfId="14"/>
+    <tableColumn id="4" name="Data de recebimento" dataDxfId="13"/>
+    <tableColumn id="5" name="Status" dataDxfId="12"/>
+    <tableColumn id="6" name="Dias desde pedido" dataDxfId="11"/>
+    <tableColumn id="7" name="Dias desde envio" dataDxfId="10"/>
+    <tableColumn id="8" name="Dias pedido→envio" dataDxfId="9"/>
+    <tableColumn id="9" name="Duração importação (envio→receb.)" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela3" displayName="Tabela3" ref="A1:F36" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela3" displayName="Tabela3" ref="A1:F36" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:F36"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Pacote" dataDxfId="7"/>
-    <tableColumn id="6" name="Código de Rastreio" dataDxfId="6"/>
-    <tableColumn id="2" name="Camisa" dataDxfId="5"/>
-    <tableColumn id="3" name="Tamanho" dataDxfId="4"/>
-    <tableColumn id="5" name="Qtd" dataDxfId="3"/>
-    <tableColumn id="4" name="Cliente" dataDxfId="2"/>
+    <tableColumn id="1" name="Pacote" dataDxfId="5"/>
+    <tableColumn id="6" name="Código de Rastreio" dataDxfId="4"/>
+    <tableColumn id="2" name="Camisa" dataDxfId="3"/>
+    <tableColumn id="3" name="Tamanho" dataDxfId="2"/>
+    <tableColumn id="5" name="Qtd" dataDxfId="1"/>
+    <tableColumn id="4" name="Cliente" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -990,7 +990,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,12 +1021,12 @@
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <f ca="1">F3-B3</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19">
         <f ca="1">F3-D3</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" s="20">
         <v>46058</v>
@@ -1065,7 +1065,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="11">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       <c r="A12" s="17"/>
       <c r="B12" s="18">
         <f ca="1">F9-B9</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19">
         <f ca="1">F9-D9</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="20">
         <v>46065</v>
@@ -1140,7 +1140,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="11">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1171,12 +1171,12 @@
       <c r="A18" s="17"/>
       <c r="B18" s="18">
         <f ca="1">F15-B15</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="19">
         <f ca="1">F15-D15</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E18" s="20"/>
       <c r="F18" s="21" t="str">
@@ -1213,7 +1213,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="11">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1244,12 +1244,12 @@
       <c r="A24" s="17"/>
       <c r="B24" s="18">
         <f ca="1">F21-B21</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19">
         <f ca="1">F21-D21</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24" s="20"/>
       <c r="F24" s="21" t="str">
@@ -1286,7 +1286,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="11">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1317,12 +1317,12 @@
       <c r="A30" s="17"/>
       <c r="B30" s="18">
         <f ca="1">F27-B27</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19">
         <f ca="1">F27-D27</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E30" s="20"/>
       <c r="F30" s="21" t="str">
@@ -1359,7 +1359,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="11">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1390,12 +1390,12 @@
       <c r="A36" s="17"/>
       <c r="B36" s="18">
         <f ca="1">F33-B33</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="19">
         <f ca="1">F33-D33</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36" s="20"/>
       <c r="F36" s="21" t="str">
@@ -1432,7 +1432,7 @@
       <c r="E39" s="9"/>
       <c r="F39" s="11">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1463,12 +1463,12 @@
       <c r="A42" s="17"/>
       <c r="B42" s="18">
         <f ca="1">F39-B39</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="19">
         <f ca="1">F39-D39</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E42" s="20">
         <v>46073</v>
@@ -1622,11 +1622,11 @@
       </c>
       <c r="G4" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" s="27">
         <f t="shared" si="3"/>
@@ -1657,11 +1657,11 @@
       </c>
       <c r="G5" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I5" s="27">
         <f t="shared" si="3"/>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="G6" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="27">
         <f t="shared" si="3"/>
@@ -1727,11 +1727,11 @@
       </c>
       <c r="G7" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7" s="27">
         <f t="shared" si="3"/>
@@ -1762,11 +1762,11 @@
       </c>
       <c r="G8" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" s="27">
         <f t="shared" si="3"/>
@@ -1790,26 +1790,28 @@
       <c r="D9" s="26">
         <v>46052</v>
       </c>
-      <c r="E9" s="26"/>
+      <c r="E9" s="26">
+        <v>46079</v>
+      </c>
       <c r="F9" s="25" t="str">
         <f t="shared" si="0"/>
-        <v>Em trânsito</v>
+        <v>Recebido</v>
       </c>
       <c r="G9" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I9" s="27">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J9" s="27" t="str">
+      <c r="J9" s="27">
         <f t="shared" si="4"/>
-        <v/>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1825,26 +1827,28 @@
       <c r="D10" s="26">
         <v>46052</v>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="26">
+        <v>46079</v>
+      </c>
       <c r="F10" s="25" t="str">
         <f t="shared" si="0"/>
-        <v>Em trânsito</v>
+        <v>Recebido</v>
       </c>
       <c r="G10" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I10" s="27">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J10" s="27" t="str">
+      <c r="J10" s="27">
         <f t="shared" si="4"/>
-        <v/>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">

--- a/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
+++ b/CONTROLE_LOGISTICO_FORMATADO_COM_FORMULAS.xlsx
@@ -990,7 +990,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,12 +1021,12 @@
       <c r="A6" s="17"/>
       <c r="B6" s="18">
         <f ca="1">F3-B3</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19">
         <f ca="1">F3-D3</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E6" s="20">
         <v>46058</v>
@@ -1065,7 +1065,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="11">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       <c r="A12" s="17"/>
       <c r="B12" s="18">
         <f ca="1">F9-B9</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19">
         <f ca="1">F9-D9</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E12" s="20">
         <v>46065</v>
@@ -1140,7 +1140,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="11">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1171,12 +1171,12 @@
       <c r="A18" s="17"/>
       <c r="B18" s="18">
         <f ca="1">F15-B15</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="19">
         <f ca="1">F15-D15</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E18" s="20"/>
       <c r="F18" s="21" t="str">
@@ -1213,7 +1213,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="11">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1244,12 +1244,12 @@
       <c r="A24" s="17"/>
       <c r="B24" s="18">
         <f ca="1">F21-B21</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19">
         <f ca="1">F21-D21</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E24" s="20"/>
       <c r="F24" s="21" t="str">
@@ -1286,7 +1286,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="11">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1317,12 +1317,12 @@
       <c r="A30" s="17"/>
       <c r="B30" s="18">
         <f ca="1">F27-B27</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19">
         <f ca="1">F27-D27</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E30" s="20"/>
       <c r="F30" s="21" t="str">
@@ -1359,7 +1359,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="11">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1390,12 +1390,12 @@
       <c r="A36" s="17"/>
       <c r="B36" s="18">
         <f ca="1">F33-B33</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="19">
         <f ca="1">F33-D33</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E36" s="20"/>
       <c r="F36" s="21" t="str">
@@ -1432,7 +1432,7 @@
       <c r="E39" s="9"/>
       <c r="F39" s="11">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1463,12 +1463,12 @@
       <c r="A42" s="17"/>
       <c r="B42" s="18">
         <f ca="1">F39-B39</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="19">
         <f ca="1">F39-D39</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E42" s="20">
         <v>46073</v>
@@ -1622,11 +1622,11 @@
       </c>
       <c r="G4" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H4" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I4" s="27">
         <f t="shared" si="3"/>
@@ -1657,11 +1657,11 @@
       </c>
       <c r="G5" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H5" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I5" s="27">
         <f t="shared" si="3"/>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="G6" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H6" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I6" s="27">
         <f t="shared" si="3"/>
@@ -1727,11 +1727,11 @@
       </c>
       <c r="G7" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H7" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I7" s="27">
         <f t="shared" si="3"/>
@@ -1762,11 +1762,11 @@
       </c>
       <c r="G8" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H8" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I8" s="27">
         <f t="shared" si="3"/>
@@ -1887,23 +1887,33 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="G12" s="29" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="H12" s="29" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="I12" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J12" s="29" t="str">
-        <f t="shared" si="4"/>
+      <c r="A12" s="25">
+        <v>40</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="C12" s="26">
+        <v>46079</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="25" t="str">
+        <f t="shared" ref="F12" si="5">IF(E12="","Em trânsito","Recebido")</f>
+        <v>Em trânsito</v>
+      </c>
+      <c r="G12" s="27">
+        <f t="shared" ref="G12" ca="1" si="6">IF(C12="","",IF(F12="Recebido",E12-C12,TODAY()-C12))</f>
+        <v>3</v>
+      </c>
+      <c r="H12" s="27" t="str">
+        <f t="shared" ref="H12" ca="1" si="7">IF(D12="","",IF(F12="Recebido",E12-D12,TODAY()-D12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="27" t="str">
+        <f t="shared" ref="I12" si="8">IF(OR(C12="",D12=""),"",D12-C12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="27" t="str">
+        <f t="shared" ref="J12" si="9">IF(OR(D12="",E12=""),"",E12-D12)</f>
         <v/>
       </c>
     </row>
@@ -1912,19 +1922,19 @@
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
       <c r="G13" s="29" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="5">IF(C13="","",IF(F13="Recebido",E13-C13,TODAY()-C13))</f>
+        <f t="shared" ref="G13:G37" ca="1" si="10">IF(C13="","",IF(F13="Recebido",E13-C13,TODAY()-C13))</f>
         <v/>
       </c>
       <c r="H13" s="29" t="str">
-        <f t="shared" ref="H13:H37" ca="1" si="6">IF(D13="","",IF(F13="Recebido",E13-D13,TODAY()-D13))</f>
+        <f t="shared" ref="H13:H37" ca="1" si="11">IF(D13="","",IF(F13="Recebido",E13-D13,TODAY()-D13))</f>
         <v/>
       </c>
       <c r="I13" s="29" t="str">
-        <f t="shared" ref="I13:I37" si="7">IF(OR(C13="",D13=""),"",D13-C13)</f>
+        <f t="shared" ref="I13:I37" si="12">IF(OR(C13="",D13=""),"",D13-C13)</f>
         <v/>
       </c>
       <c r="J13" s="29" t="str">
-        <f t="shared" ref="J13:J37" si="8">IF(OR(D13="",E13=""),"",E13-D13)</f>
+        <f t="shared" ref="J13:J37" si="13">IF(OR(D13="",E13=""),"",E13-D13)</f>
         <v/>
       </c>
     </row>
@@ -1933,19 +1943,19 @@
       <c r="D14" s="28"/>
       <c r="E14" s="28"/>
       <c r="G14" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H14" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I14" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J14" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -1954,19 +1964,19 @@
       <c r="D15" s="28"/>
       <c r="E15" s="28"/>
       <c r="G15" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H15" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I15" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J15" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -1975,19 +1985,19 @@
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
       <c r="G16" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H16" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I16" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J16" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -1996,19 +2006,19 @@
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
       <c r="G17" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H17" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I17" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J17" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2017,19 +2027,19 @@
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
       <c r="G18" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H18" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I18" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J18" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2038,19 +2048,19 @@
       <c r="D19" s="28"/>
       <c r="E19" s="28"/>
       <c r="G19" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H19" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I19" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J19" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2059,19 +2069,19 @@
       <c r="D20" s="28"/>
       <c r="E20" s="28"/>
       <c r="G20" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H20" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I20" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J20" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2080,19 +2090,19 @@
       <c r="D21" s="28"/>
       <c r="E21" s="28"/>
       <c r="G21" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H21" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I21" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J21" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2101,19 +2111,19 @@
       <c r="D22" s="28"/>
       <c r="E22" s="28"/>
       <c r="G22" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H22" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I22" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J22" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2122,19 +2132,19 @@
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
       <c r="G23" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H23" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I23" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J23" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2143,19 +2153,19 @@
       <c r="D24" s="28"/>
       <c r="E24" s="28"/>
       <c r="G24" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H24" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I24" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J24" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2164,19 +2174,19 @@
       <c r="D25" s="28"/>
       <c r="E25" s="28"/>
       <c r="G25" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H25" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I25" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J25" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2185,19 +2195,19 @@
       <c r="D26" s="28"/>
       <c r="E26" s="28"/>
       <c r="G26" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H26" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I26" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J26" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2206,19 +2216,19 @@
       <c r="D27" s="28"/>
       <c r="E27" s="28"/>
       <c r="G27" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H27" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I27" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J27" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2227,19 +2237,19 @@
       <c r="D28" s="28"/>
       <c r="E28" s="28"/>
       <c r="G28" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H28" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I28" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J28" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2248,19 +2258,19 @@
       <c r="D29" s="28"/>
       <c r="E29" s="28"/>
       <c r="G29" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H29" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I29" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J29" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2269,19 +2279,19 @@
       <c r="D30" s="28"/>
       <c r="E30" s="28"/>
       <c r="G30" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H30" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I30" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J30" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2290,19 +2300,19 @@
       <c r="D31" s="28"/>
       <c r="E31" s="28"/>
       <c r="G31" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H31" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I31" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J31" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2311,19 +2321,19 @@
       <c r="D32" s="28"/>
       <c r="E32" s="28"/>
       <c r="G32" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H32" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I32" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J32" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2332,19 +2342,19 @@
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
       <c r="G33" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H33" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I33" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J33" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2353,19 +2363,19 @@
       <c r="D34" s="28"/>
       <c r="E34" s="28"/>
       <c r="G34" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H34" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I34" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J34" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2374,19 +2384,19 @@
       <c r="D35" s="28"/>
       <c r="E35" s="28"/>
       <c r="G35" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H35" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I35" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J35" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2395,19 +2405,19 @@
       <c r="D36" s="28"/>
       <c r="E36" s="28"/>
       <c r="G36" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H36" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I36" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J36" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2416,19 +2426,19 @@
       <c r="D37" s="28"/>
       <c r="E37" s="28"/>
       <c r="G37" s="29" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="H37" s="29" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="I37" s="29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J37" s="29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -2437,19 +2447,19 @@
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="G38" s="29" t="str">
-        <f t="shared" ref="G38:G101" ca="1" si="9">IF(C38="","",IF(F38="Recebido",E38-C38,TODAY()-C38))</f>
+        <f t="shared" ref="G38:G101" ca="1" si="14">IF(C38="","",IF(F38="Recebido",E38-C38,TODAY()-C38))</f>
         <v/>
       </c>
       <c r="H38" s="29" t="str">
-        <f t="shared" ref="H38:H101" ca="1" si="10">IF(D38="","",IF(F38="Recebido",E38-D38,TODAY()-D38))</f>
+        <f t="shared" ref="H38:H101" ca="1" si="15">IF(D38="","",IF(F38="Recebido",E38-D38,TODAY()-D38))</f>
         <v/>
       </c>
       <c r="I38" s="29" t="str">
-        <f t="shared" ref="I38:I101" si="11">IF(OR(C38="",D38=""),"",D38-C38)</f>
+        <f t="shared" ref="I38:I101" si="16">IF(OR(C38="",D38=""),"",D38-C38)</f>
         <v/>
       </c>
       <c r="J38" s="29" t="str">
-        <f t="shared" ref="J38:J101" si="12">IF(OR(D38="",E38=""),"",E38-D38)</f>
+        <f t="shared" ref="J38:J101" si="17">IF(OR(D38="",E38=""),"",E38-D38)</f>
         <v/>
       </c>
     </row>
@@ -2458,19 +2468,19 @@
       <c r="D39" s="28"/>
       <c r="E39" s="28"/>
       <c r="G39" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H39" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I39" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J39" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2479,19 +2489,19 @@
       <c r="D40" s="28"/>
       <c r="E40" s="28"/>
       <c r="G40" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H40" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I40" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J40" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2500,19 +2510,19 @@
       <c r="D41" s="28"/>
       <c r="E41" s="28"/>
       <c r="G41" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H41" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I41" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J41" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2521,19 +2531,19 @@
       <c r="D42" s="28"/>
       <c r="E42" s="28"/>
       <c r="G42" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H42" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I42" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J42" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2542,19 +2552,19 @@
       <c r="D43" s="28"/>
       <c r="E43" s="28"/>
       <c r="G43" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H43" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I43" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J43" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2563,19 +2573,19 @@
       <c r="D44" s="28"/>
       <c r="E44" s="28"/>
       <c r="G44" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H44" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I44" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J44" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2584,19 +2594,19 @@
       <c r="D45" s="28"/>
       <c r="E45" s="28"/>
       <c r="G45" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H45" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I45" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J45" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2605,19 +2615,19 @@
       <c r="D46" s="28"/>
       <c r="E46" s="28"/>
       <c r="G46" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H46" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I46" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J46" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2626,19 +2636,19 @@
       <c r="D47" s="28"/>
       <c r="E47" s="28"/>
       <c r="G47" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H47" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I47" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J47" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2647,19 +2657,19 @@
       <c r="D48" s="28"/>
       <c r="E48" s="28"/>
       <c r="G48" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H48" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I48" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J48" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2668,19 +2678,19 @@
       <c r="D49" s="28"/>
       <c r="E49" s="28"/>
       <c r="G49" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H49" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I49" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J49" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2689,19 +2699,19 @@
       <c r="D50" s="28"/>
       <c r="E50" s="28"/>
       <c r="G50" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H50" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I50" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J50" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2710,19 +2720,19 @@
       <c r="D51" s="28"/>
       <c r="E51" s="28"/>
       <c r="G51" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H51" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I51" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J51" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2731,19 +2741,19 @@
       <c r="D52" s="28"/>
       <c r="E52" s="28"/>
       <c r="G52" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H52" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I52" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J52" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2752,19 +2762,19 @@
       <c r="D53" s="28"/>
       <c r="E53" s="28"/>
       <c r="G53" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H53" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I53" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J53" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2773,19 +2783,19 @@
       <c r="D54" s="28"/>
       <c r="E54" s="28"/>
       <c r="G54" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H54" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I54" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J54" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2794,19 +2804,19 @@
       <c r="D55" s="28"/>
       <c r="E55" s="28"/>
       <c r="G55" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H55" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I55" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J55" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2815,19 +2825,19 @@
       <c r="D56" s="28"/>
       <c r="E56" s="28"/>
       <c r="G56" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H56" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I56" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J56" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2836,19 +2846,19 @@
       <c r="D57" s="28"/>
       <c r="E57" s="28"/>
       <c r="G57" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H57" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I57" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J57" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2857,19 +2867,19 @@
       <c r="D58" s="28"/>
       <c r="E58" s="28"/>
       <c r="G58" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H58" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I58" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J58" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2878,19 +2888,19 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28"/>
       <c r="G59" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H59" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I59" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J59" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2899,19 +2909,19 @@
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
       <c r="G60" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H60" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I60" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J60" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2920,19 +2930,19 @@
       <c r="D61" s="28"/>
       <c r="E61" s="28"/>
       <c r="G61" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H61" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I61" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J61" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2941,19 +2951,19 @@
       <c r="D62" s="28"/>
       <c r="E62" s="28"/>
       <c r="G62" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H62" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I62" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J62" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2962,19 +2972,19 @@
       <c r="D63" s="28"/>
       <c r="E63" s="28"/>
       <c r="G63" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H63" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I63" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J63" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -2983,19 +2993,19 @@
       <c r="D64" s="28"/>
       <c r="E64" s="28"/>
       <c r="G64" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H64" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I64" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J64" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3004,19 +3014,19 @@
       <c r="D65" s="28"/>
       <c r="E65" s="28"/>
       <c r="G65" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H65" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I65" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J65" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3025,19 +3035,19 @@
       <c r="D66" s="28"/>
       <c r="E66" s="28"/>
       <c r="G66" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H66" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I66" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J66" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3046,19 +3056,19 @@
       <c r="D67" s="28"/>
       <c r="E67" s="28"/>
       <c r="G67" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H67" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I67" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J67" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3067,19 +3077,19 @@
       <c r="D68" s="28"/>
       <c r="E68" s="28"/>
       <c r="G68" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H68" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I68" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J68" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3088,19 +3098,19 @@
       <c r="D69" s="28"/>
       <c r="E69" s="28"/>
       <c r="G69" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H69" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I69" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J69" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3109,19 +3119,19 @@
       <c r="D70" s="28"/>
       <c r="E70" s="28"/>
       <c r="G70" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H70" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I70" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J70" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3130,19 +3140,19 @@
       <c r="D71" s="28"/>
       <c r="E71" s="28"/>
       <c r="G71" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H71" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I71" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J71" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3151,19 +3161,19 @@
       <c r="D72" s="28"/>
       <c r="E72" s="28"/>
       <c r="G72" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H72" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I72" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J72" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3172,19 +3182,19 @@
       <c r="D73" s="28"/>
       <c r="E73" s="28"/>
       <c r="G73" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H73" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I73" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J73" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3193,19 +3203,19 @@
       <c r="D74" s="28"/>
       <c r="E74" s="28"/>
       <c r="G74" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H74" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I74" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J74" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3214,19 +3224,19 @@
       <c r="D75" s="28"/>
       <c r="E75" s="28"/>
       <c r="G75" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H75" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I75" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J75" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3235,19 +3245,19 @@
       <c r="D76" s="28"/>
       <c r="E76" s="28"/>
       <c r="G76" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H76" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I76" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J76" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3256,19 +3266,19 @@
       <c r="D77" s="28"/>
       <c r="E77" s="28"/>
       <c r="G77" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H77" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I77" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J77" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3277,19 +3287,19 @@
       <c r="D78" s="28"/>
       <c r="E78" s="28"/>
       <c r="G78" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H78" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I78" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J78" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3298,19 +3308,19 @@
       <c r="D79" s="28"/>
       <c r="E79" s="28"/>
       <c r="G79" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H79" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I79" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J79" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3319,19 +3329,19 @@
       <c r="D80" s="28"/>
       <c r="E80" s="28"/>
       <c r="G80" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H80" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I80" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J80" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3340,19 +3350,19 @@
       <c r="D81" s="28"/>
       <c r="E81" s="28"/>
       <c r="G81" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H81" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I81" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J81" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3361,19 +3371,19 @@
       <c r="D82" s="28"/>
       <c r="E82" s="28"/>
       <c r="G82" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H82" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I82" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J82" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3382,19 +3392,19 @@
       <c r="D83" s="28"/>
       <c r="E83" s="28"/>
       <c r="G83" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H83" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I83" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J83" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3403,19 +3413,19 @@
       <c r="D84" s="28"/>
       <c r="E84" s="28"/>
       <c r="G84" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H84" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I84" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J84" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3424,19 +3434,19 @@
       <c r="D85" s="28"/>
       <c r="E85" s="28"/>
       <c r="G85" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H85" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I85" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J85" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3445,19 +3455,19 @@
       <c r="D86" s="28"/>
       <c r="E86" s="28"/>
       <c r="G86" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H86" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I86" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J86" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3466,19 +3476,19 @@
       <c r="D87" s="28"/>
       <c r="E87" s="28"/>
       <c r="G87" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H87" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I87" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J87" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3487,19 +3497,19 @@
       <c r="D88" s="28"/>
       <c r="E88" s="28"/>
       <c r="G88" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H88" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I88" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J88" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3508,19 +3518,19 @@
       <c r="D89" s="28"/>
       <c r="E89" s="28"/>
       <c r="G89" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H89" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I89" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J89" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3529,19 +3539,19 @@
       <c r="D90" s="28"/>
       <c r="E90" s="28"/>
       <c r="G90" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H90" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I90" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J90" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3550,19 +3560,19 @@
       <c r="D91" s="28"/>
       <c r="E91" s="28"/>
       <c r="G91" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H91" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I91" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J91" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3571,19 +3581,19 @@
       <c r="D92" s="28"/>
       <c r="E92" s="28"/>
       <c r="G92" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H92" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I92" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J92" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3592,19 +3602,19 @@
       <c r="D93" s="28"/>
       <c r="E93" s="28"/>
       <c r="G93" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H93" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I93" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J93" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3613,19 +3623,19 @@
       <c r="D94" s="28"/>
       <c r="E94" s="28"/>
       <c r="G94" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H94" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I94" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J94" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3634,19 +3644,19 @@
       <c r="D95" s="28"/>
       <c r="E95" s="28"/>
       <c r="G95" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H95" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I95" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J95" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3655,19 +3665,19 @@
       <c r="D96" s="28"/>
       <c r="E96" s="28"/>
       <c r="G96" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H96" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I96" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J96" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3676,19 +3686,19 @@
       <c r="D97" s="28"/>
       <c r="E97" s="28"/>
       <c r="G97" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H97" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I97" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J97" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3697,19 +3707,19 @@
       <c r="D98" s="28"/>
       <c r="E98" s="28"/>
       <c r="G98" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H98" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I98" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J98" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3718,19 +3728,19 @@
       <c r="D99" s="28"/>
       <c r="E99" s="28"/>
       <c r="G99" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H99" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I99" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J99" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3739,19 +3749,19 @@
       <c r="D100" s="28"/>
       <c r="E100" s="28"/>
       <c r="G100" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H100" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I100" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J100" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3760,19 +3770,19 @@
       <c r="D101" s="28"/>
       <c r="E101" s="28"/>
       <c r="G101" s="29" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="H101" s="29" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="I101" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J101" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -3781,19 +3791,19 @@
       <c r="D102" s="28"/>
       <c r="E102" s="28"/>
       <c r="G102" s="29" t="str">
-        <f t="shared" ref="G102:G165" ca="1" si="13">IF(C102="","",IF(F102="Recebido",E102-C102,TODAY()-C102))</f>
+        <f t="shared" ref="G102:G165" ca="1" si="18">IF(C102="","",IF(F102="Recebido",E102-C102,TODAY()-C102))</f>
         <v/>
       </c>
       <c r="H102" s="29" t="str">
-        <f t="shared" ref="H102:H165" ca="1" si="14">IF(D102="","",IF(F102="Recebido",E102-D102,TODAY()-D102))</f>
+        <f t="shared" ref="H102:H165" ca="1" si="19">IF(D102="","",IF(F102="Recebido",E102-D102,TODAY()-D102))</f>
         <v/>
       </c>
       <c r="I102" s="29" t="str">
-        <f t="shared" ref="I102:I165" si="15">IF(OR(C102="",D102=""),"",D102-C102)</f>
+        <f t="shared" ref="I102:I165" si="20">IF(OR(C102="",D102=""),"",D102-C102)</f>
         <v/>
       </c>
       <c r="J102" s="29" t="str">
-        <f t="shared" ref="J102:J165" si="16">IF(OR(D102="",E102=""),"",E102-D102)</f>
+        <f t="shared" ref="J102:J165" si="21">IF(OR(D102="",E102=""),"",E102-D102)</f>
         <v/>
       </c>
     </row>
@@ -3802,19 +3812,19 @@
       <c r="D103" s="28"/>
       <c r="E103" s="28"/>
       <c r="G103" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H103" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I103" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J103" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3823,19 +3833,19 @@
       <c r="D104" s="28"/>
       <c r="E104" s="28"/>
       <c r="G104" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H104" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I104" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J104" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3844,19 +3854,19 @@
       <c r="D105" s="28"/>
       <c r="E105" s="28"/>
       <c r="G105" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H105" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I105" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J105" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3865,19 +3875,19 @@
       <c r="D106" s="28"/>
       <c r="E106" s="28"/>
       <c r="G106" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H106" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I106" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J106" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3886,19 +3896,19 @@
       <c r="D107" s="28"/>
       <c r="E107" s="28"/>
       <c r="G107" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H107" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I107" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J107" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3907,19 +3917,19 @@
       <c r="D108" s="28"/>
       <c r="E108" s="28"/>
       <c r="G108" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H108" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I108" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J108" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3928,19 +3938,19 @@
       <c r="D109" s="28"/>
       <c r="E109" s="28"/>
       <c r="G109" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H109" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I109" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J109" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3949,19 +3959,19 @@
       <c r="D110" s="28"/>
       <c r="E110" s="28"/>
       <c r="G110" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H110" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I110" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J110" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3970,19 +3980,19 @@
       <c r="D111" s="28"/>
       <c r="E111" s="28"/>
       <c r="G111" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H111" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I111" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J111" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -3991,19 +4001,19 @@
       <c r="D112" s="28"/>
       <c r="E112" s="28"/>
       <c r="G112" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H112" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I112" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J112" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4012,19 +4022,19 @@
       <c r="D113" s="28"/>
       <c r="E113" s="28"/>
       <c r="G113" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H113" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I113" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J113" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4033,19 +4043,19 @@
       <c r="D114" s="28"/>
       <c r="E114" s="28"/>
       <c r="G114" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H114" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I114" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J114" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4054,19 +4064,19 @@
       <c r="D115" s="28"/>
       <c r="E115" s="28"/>
       <c r="G115" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H115" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I115" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J115" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4075,19 +4085,19 @@
       <c r="D116" s="28"/>
       <c r="E116" s="28"/>
       <c r="G116" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H116" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I116" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J116" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4096,19 +4106,19 @@
       <c r="D117" s="28"/>
       <c r="E117" s="28"/>
       <c r="G117" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H117" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I117" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J117" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4117,19 +4127,19 @@
       <c r="D118" s="28"/>
       <c r="E118" s="28"/>
       <c r="G118" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H118" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I118" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J118" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4138,19 +4148,19 @@
       <c r="D119" s="28"/>
       <c r="E119" s="28"/>
       <c r="G119" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H119" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I119" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J119" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4159,19 +4169,19 @@
       <c r="D120" s="28"/>
       <c r="E120" s="28"/>
       <c r="G120" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H120" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I120" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J120" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4180,19 +4190,19 @@
       <c r="D121" s="28"/>
       <c r="E121" s="28"/>
       <c r="G121" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H121" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I121" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J121" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4201,19 +4211,19 @@
       <c r="D122" s="28"/>
       <c r="E122" s="28"/>
       <c r="G122" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H122" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I122" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J122" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4222,19 +4232,19 @@
       <c r="D123" s="28"/>
       <c r="E123" s="28"/>
       <c r="G123" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H123" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I123" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J123" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4243,19 +4253,19 @@
       <c r="D124" s="28"/>
       <c r="E124" s="28"/>
       <c r="G124" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H124" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I124" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J124" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4264,19 +4274,19 @@
       <c r="D125" s="28"/>
       <c r="E125" s="28"/>
       <c r="G125" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H125" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I125" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J125" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4285,19 +4295,19 @@
       <c r="D126" s="28"/>
       <c r="E126" s="28"/>
       <c r="G126" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H126" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I126" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J126" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4306,19 +4316,19 @@
       <c r="D127" s="28"/>
       <c r="E127" s="28"/>
       <c r="G127" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H127" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I127" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J127" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4327,19 +4337,19 @@
       <c r="D128" s="28"/>
       <c r="E128" s="28"/>
       <c r="G128" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H128" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I128" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J128" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4348,19 +4358,19 @@
       <c r="D129" s="28"/>
       <c r="E129" s="28"/>
       <c r="G129" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H129" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I129" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J129" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4369,19 +4379,19 @@
       <c r="D130" s="28"/>
       <c r="E130" s="28"/>
       <c r="G130" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H130" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I130" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J130" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4390,19 +4400,19 @@
       <c r="D131" s="28"/>
       <c r="E131" s="28"/>
       <c r="G131" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H131" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I131" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J131" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4411,19 +4421,19 @@
       <c r="D132" s="28"/>
       <c r="E132" s="28"/>
       <c r="G132" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H132" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I132" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J132" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4432,19 +4442,19 @@
       <c r="D133" s="28"/>
       <c r="E133" s="28"/>
       <c r="G133" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H133" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I133" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J133" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4453,19 +4463,19 @@
       <c r="D134" s="28"/>
       <c r="E134" s="28"/>
       <c r="G134" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H134" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I134" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J134" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4474,19 +4484,19 @@
       <c r="D135" s="28"/>
       <c r="E135" s="28"/>
       <c r="G135" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H135" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I135" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J135" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4495,19 +4505,19 @@
       <c r="D136" s="28"/>
       <c r="E136" s="28"/>
       <c r="G136" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H136" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I136" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J136" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4516,19 +4526,19 @@
       <c r="D137" s="28"/>
       <c r="E137" s="28"/>
       <c r="G137" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H137" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I137" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J137" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4537,19 +4547,19 @@
       <c r="D138" s="28"/>
       <c r="E138" s="28"/>
       <c r="G138" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H138" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I138" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J138" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4558,19 +4568,19 @@
       <c r="D139" s="28"/>
       <c r="E139" s="28"/>
       <c r="G139" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H139" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I139" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J139" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4579,19 +4589,19 @@
       <c r="D140" s="28"/>
       <c r="E140" s="28"/>
       <c r="G140" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H140" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I140" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J140" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4600,19 +4610,19 @@
       <c r="D141" s="28"/>
       <c r="E141" s="28"/>
       <c r="G141" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H141" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I141" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J141" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4621,19 +4631,19 @@
       <c r="D142" s="28"/>
       <c r="E142" s="28"/>
       <c r="G142" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H142" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I142" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J142" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4642,19 +4652,19 @@
       <c r="D143" s="28"/>
       <c r="E143" s="28"/>
       <c r="G143" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H143" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I143" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J143" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4663,19 +4673,19 @@
       <c r="D144" s="28"/>
       <c r="E144" s="28"/>
       <c r="G144" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H144" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I144" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J144" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4684,19 +4694,19 @@
       <c r="D145" s="28"/>
       <c r="E145" s="28"/>
       <c r="G145" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H145" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I145" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J145" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4705,19 +4715,19 @@
       <c r="D146" s="28"/>
       <c r="E146" s="28"/>
       <c r="G146" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H146" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I146" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J146" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4726,19 +4736,19 @@
       <c r="D147" s="28"/>
       <c r="E147" s="28"/>
       <c r="G147" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H147" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I147" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J147" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4747,19 +4757,19 @@
       <c r="D148" s="28"/>
       <c r="E148" s="28"/>
       <c r="G148" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H148" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I148" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J148" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4768,19 +4778,19 @@
       <c r="D149" s="28"/>
       <c r="E149" s="28"/>
       <c r="G149" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H149" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I149" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J149" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4789,19 +4799,19 @@
       <c r="D150" s="28"/>
       <c r="E150" s="28"/>
       <c r="G150" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H150" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I150" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J150" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4810,19 +4820,19 @@
       <c r="D151" s="28"/>
       <c r="E151" s="28"/>
       <c r="G151" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H151" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I151" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J151" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4831,19 +4841,19 @@
       <c r="D152" s="28"/>
       <c r="E152" s="28"/>
       <c r="G152" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H152" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I152" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J152" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4852,19 +4862,19 @@
       <c r="D153" s="28"/>
       <c r="E153" s="28"/>
       <c r="G153" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H153" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I153" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J153" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4873,19 +4883,19 @@
       <c r="D154" s="28"/>
       <c r="E154" s="28"/>
       <c r="G154" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H154" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I154" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J154" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4894,19 +4904,19 @@
       <c r="D155" s="28"/>
       <c r="E155" s="28"/>
       <c r="G155" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H155" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I155" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J155" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4915,19 +4925,19 @@
       <c r="D156" s="28"/>
       <c r="E156" s="28"/>
       <c r="G156" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H156" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I156" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J156" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4936,19 +4946,19 @@
       <c r="D157" s="28"/>
       <c r="E157" s="28"/>
       <c r="G157" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H157" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I157" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J157" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4957,19 +4967,19 @@
       <c r="D158" s="28"/>
       <c r="E158" s="28"/>
       <c r="G158" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H158" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I158" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J158" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4978,19 +4988,19 @@
       <c r="D159" s="28"/>
       <c r="E159" s="28"/>
       <c r="G159" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H159" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I159" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J159" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -4999,19 +5009,19 @@
       <c r="D160" s="28"/>
       <c r="E160" s="28"/>
       <c r="G160" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H160" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I160" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J160" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5020,19 +5030,19 @@
       <c r="D161" s="28"/>
       <c r="E161" s="28"/>
       <c r="G161" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H161" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I161" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J161" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5041,19 +5051,19 @@
       <c r="D162" s="28"/>
       <c r="E162" s="28"/>
       <c r="G162" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H162" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I162" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J162" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5062,19 +5072,19 @@
       <c r="D163" s="28"/>
       <c r="E163" s="28"/>
       <c r="G163" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H163" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I163" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J163" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5083,19 +5093,19 @@
       <c r="D164" s="28"/>
       <c r="E164" s="28"/>
       <c r="G164" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H164" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I164" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J164" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5104,19 +5114,19 @@
       <c r="D165" s="28"/>
       <c r="E165" s="28"/>
       <c r="G165" s="29" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="H165" s="29" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="I165" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J165" s="29" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5125,19 +5135,19 @@
       <c r="D166" s="28"/>
       <c r="E166" s="28"/>
       <c r="G166" s="29" t="str">
-        <f t="shared" ref="G166:G208" ca="1" si="17">IF(C166="","",IF(F166="Recebido",E166-C166,TODAY()-C166))</f>
+        <f t="shared" ref="G166:G208" ca="1" si="22">IF(C166="","",IF(F166="Recebido",E166-C166,TODAY()-C166))</f>
         <v/>
       </c>
       <c r="H166" s="29" t="str">
-        <f t="shared" ref="H166:H208" ca="1" si="18">IF(D166="","",IF(F166="Recebido",E166-D166,TODAY()-D166))</f>
+        <f t="shared" ref="H166:H208" ca="1" si="23">IF(D166="","",IF(F166="Recebido",E166-D166,TODAY()-D166))</f>
         <v/>
       </c>
       <c r="I166" s="29" t="str">
-        <f t="shared" ref="I166:I208" si="19">IF(OR(C166="",D166=""),"",D166-C166)</f>
+        <f t="shared" ref="I166:I208" si="24">IF(OR(C166="",D166=""),"",D166-C166)</f>
         <v/>
       </c>
       <c r="J166" s="29" t="str">
-        <f t="shared" ref="J166:J208" si="20">IF(OR(D166="",E166=""),"",E166-D166)</f>
+        <f t="shared" ref="J166:J208" si="25">IF(OR(D166="",E166=""),"",E166-D166)</f>
         <v/>
       </c>
     </row>
@@ -5146,19 +5156,19 @@
       <c r="D167" s="28"/>
       <c r="E167" s="28"/>
       <c r="G167" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H167" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I167" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J167" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5167,19 +5177,19 @@
       <c r="D168" s="28"/>
       <c r="E168" s="28"/>
       <c r="G168" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H168" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I168" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J168" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5188,19 +5198,19 @@
       <c r="D169" s="28"/>
       <c r="E169" s="28"/>
       <c r="G169" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H169" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I169" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J169" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5209,19 +5219,19 @@
       <c r="D170" s="28"/>
       <c r="E170" s="28"/>
       <c r="G170" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H170" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I170" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J170" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5230,19 +5240,19 @@
       <c r="D171" s="28"/>
       <c r="E171" s="28"/>
       <c r="G171" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H171" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I171" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J171" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5251,19 +5261,19 @@
       <c r="D172" s="28"/>
       <c r="E172" s="28"/>
       <c r="G172" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H172" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I172" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J172" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5272,19 +5282,19 @@
       <c r="D173" s="28"/>
       <c r="E173" s="28"/>
       <c r="G173" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H173" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I173" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J173" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5293,19 +5303,19 @@
       <c r="D174" s="28"/>
       <c r="E174" s="28"/>
       <c r="G174" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H174" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I174" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J174" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5314,19 +5324,19 @@
       <c r="D175" s="28"/>
       <c r="E175" s="28"/>
       <c r="G175" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H175" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I175" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J175" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5335,19 +5345,19 @@
       <c r="D176" s="28"/>
       <c r="E176" s="28"/>
       <c r="G176" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H176" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I176" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J176" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5356,19 +5366,19 @@
       <c r="D177" s="28"/>
       <c r="E177" s="28"/>
       <c r="G177" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H177" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I177" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J177" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5377,19 +5387,19 @@
       <c r="D178" s="28"/>
       <c r="E178" s="28"/>
       <c r="G178" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H178" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I178" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J178" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5398,19 +5408,19 @@
       <c r="D179" s="28"/>
       <c r="E179" s="28"/>
       <c r="G179" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H179" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I179" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J179" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5419,19 +5429,19 @@
       <c r="D180" s="28"/>
       <c r="E180" s="28"/>
       <c r="G180" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H180" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I180" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J180" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5440,19 +5450,19 @@
       <c r="D181" s="28"/>
       <c r="E181" s="28"/>
       <c r="G181" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H181" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I181" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J181" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5461,19 +5471,19 @@
       <c r="D182" s="28"/>
       <c r="E182" s="28"/>
       <c r="G182" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H182" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I182" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J182" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5482,19 +5492,19 @@
       <c r="D183" s="28"/>
       <c r="E183" s="28"/>
       <c r="G183" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H183" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I183" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J183" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5503,19 +5513,19 @@
       <c r="D184" s="28"/>
       <c r="E184" s="28"/>
       <c r="G184" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H184" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I184" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J184" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5524,19 +5534,19 @@
       <c r="D185" s="28"/>
       <c r="E185" s="28"/>
       <c r="G185" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H185" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I185" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J185" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5545,19 +5555,19 @@
       <c r="D186" s="28"/>
       <c r="E186" s="28"/>
       <c r="G186" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H186" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I186" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J186" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5566,19 +5576,19 @@
       <c r="D187" s="28"/>
       <c r="E187" s="28"/>
       <c r="G187" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H187" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I187" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J187" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5587,19 +5597,19 @@
       <c r="D188" s="28"/>
       <c r="E188" s="28"/>
       <c r="G188" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H188" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I188" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J188" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5608,19 +5618,19 @@
       <c r="D189" s="28"/>
       <c r="E189" s="28"/>
       <c r="G189" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H189" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I189" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J189" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5629,19 +5639,19 @@
       <c r="D190" s="28"/>
       <c r="E190" s="28"/>
       <c r="G190" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H190" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I190" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J190" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5650,19 +5660,19 @@
       <c r="D191" s="28"/>
       <c r="E191" s="28"/>
       <c r="G191" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H191" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I191" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J191" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5671,19 +5681,19 @@
       <c r="D192" s="28"/>
       <c r="E192" s="28"/>
       <c r="G192" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H192" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I192" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J192" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5692,19 +5702,19 @@
       <c r="D193" s="28"/>
       <c r="E193" s="28"/>
       <c r="G193" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H193" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I193" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J193" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5713,19 +5723,19 @@
       <c r="D194" s="28"/>
       <c r="E194" s="28"/>
       <c r="G194" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H194" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I194" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J194" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5734,19 +5744,19 @@
       <c r="D195" s="28"/>
       <c r="E195" s="28"/>
       <c r="G195" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H195" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I195" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J195" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5755,19 +5765,19 @@
       <c r="D196" s="28"/>
       <c r="E196" s="28"/>
       <c r="G196" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H196" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I196" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J196" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5776,19 +5786,19 @@
       <c r="D197" s="28"/>
       <c r="E197" s="28"/>
       <c r="G197" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H197" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I197" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J197" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5797,19 +5807,19 @@
       <c r="D198" s="28"/>
       <c r="E198" s="28"/>
       <c r="G198" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H198" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I198" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J198" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5818,19 +5828,19 @@
       <c r="D199" s="28"/>
       <c r="E199" s="28"/>
       <c r="G199" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H199" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I199" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J199" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5839,19 +5849,19 @@
       <c r="D200" s="28"/>
       <c r="E200" s="28"/>
       <c r="G200" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H200" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I200" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J200" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5860,19 +5870,19 @@
       <c r="D201" s="28"/>
       <c r="E201" s="28"/>
       <c r="G201" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H201" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I201" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J201" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5881,19 +5891,19 @@
       <c r="D202" s="28"/>
       <c r="E202" s="28"/>
       <c r="G202" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H202" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I202" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J202" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5902,19 +5912,19 @@
       <c r="D203" s="28"/>
       <c r="E203" s="28"/>
       <c r="G203" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H203" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I203" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J203" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5923,19 +5933,19 @@
       <c r="D204" s="28"/>
       <c r="E204" s="28"/>
       <c r="G204" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H204" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I204" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J204" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5944,19 +5954,19 @@
       <c r="D205" s="28"/>
       <c r="E205" s="28"/>
       <c r="G205" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H205" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I205" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J205" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5965,19 +5975,19 @@
       <c r="D206" s="28"/>
       <c r="E206" s="28"/>
       <c r="G206" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H206" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I206" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J206" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -5986,19 +5996,19 @@
       <c r="D207" s="28"/>
       <c r="E207" s="28"/>
       <c r="G207" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H207" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I207" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J207" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -6007,19 +6017,19 @@
       <c r="D208" s="28"/>
       <c r="E208" s="28"/>
       <c r="G208" s="29" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="H208" s="29" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="I208" s="29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J208" s="29" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
